--- a/Results/Hydrogen/hydrogen human toxicity carcinogenic results.xlsx
+++ b/Results/Hydrogen/hydrogen human toxicity carcinogenic results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.299546510563455e-08</v>
+        <v>1.299546510563524e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>8.580419078195543e-09</v>
+        <v>8.580419078195497e-09</v>
       </c>
       <c r="D2" t="n">
         <v>1.509441795517441e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>8.580419078195543e-09</v>
+        <v>8.580419078195497e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>8.580419078195543e-09</v>
+        <v>8.580419078195497e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.246447976248612e-08</v>
+        <v>1.246447976248571e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.565290456453585e-08</v>
+        <v>2.565290456453549e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>8.580419078195543e-09</v>
+        <v>8.580419078195497e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.36732012995922e-08</v>
+        <v>1.367320129959203e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.055521772573507e-08</v>
+        <v>1.055521772573474e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.056744720014587e-08</v>
+        <v>1.090040074072369e-08</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.06690506368455e-09</v>
+        <v>1.066905063684551e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>1.052805798886893e-09</v>
+        <v>1.052805798886896e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.06690506368455e-09</v>
+        <v>1.066905063684551e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>1.059234533997166e-09</v>
+        <v>1.059234533997173e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.059234533997165e-09</v>
+        <v>1.059234533997169e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.066635895851764e-09</v>
+        <v>1.066635895851769e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>1.06690506368455e-09</v>
+        <v>1.066905063684551e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>1.066408517584692e-09</v>
+        <v>1.066408517584701e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>1.06690506368455e-09</v>
+        <v>1.066905063684551e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>1.06690506368455e-09</v>
+        <v>1.066905063684551e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>1.06690506368455e-09</v>
+        <v>1.066905063684551e-09</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.789841880453216e-09</v>
+        <v>1.642253693357425e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.632858079981071e-09</v>
+        <v>1.632858079981069e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.649377298367111e-09</v>
+        <v>1.649378816961288e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.609866355836159e-09</v>
+        <v>1.609866355836165e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.641813903005794e-09</v>
+        <v>1.641813903005798e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.789572712620434e-09</v>
+        <v>3.789572712620436e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.773948477211249e-09</v>
+        <v>3.773948477211241e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.789345334353363e-09</v>
+        <v>1.641757147257575e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.706311851253057e-09</v>
+        <v>1.706311851253122e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.640430573383068e-09</v>
+        <v>1.640430573383067e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.648814904429589e-09</v>
+        <v>1.648814904429585e-09</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.234532964107399e-09</v>
+        <v>6.234532964107388e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>6.234036418007545e-09</v>
+        <v>6.234036418007548e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>6.234335687057966e-09</v>
+        <v>6.234335687057964e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>6.233754290479964e-09</v>
+        <v>6.233754290479969e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>6.233754290479964e-09</v>
+        <v>6.233754290479969e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>6.234263796274614e-09</v>
+        <v>6.234263796274608e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>6.234532964107399e-09</v>
+        <v>6.234532964107388e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>6.234036418007545e-09</v>
+        <v>6.234036418007548e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>6.234532964107399e-09</v>
+        <v>6.234532964107388e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>6.234532964107399e-09</v>
+        <v>6.234532964107388e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>6.234532964107399e-09</v>
+        <v>6.234532964107388e-09</v>
       </c>
     </row>
     <row r="6">
@@ -678,34 +678,34 @@
         <v>6.111760113646136e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>9.754950721179236e-09</v>
+        <v>9.754950721179241e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.051015225595223e-08</v>
+        <v>1.051015225595225e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>8.758499611803901e-09</v>
+        <v>8.758499611803911e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>6.226690224070023e-09</v>
+        <v>6.226690224070032e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>9.754484618213569e-09</v>
+        <v>9.754484618213572e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>9.754753786046326e-09</v>
+        <v>9.754753786046348e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>9.754257239946492e-09</v>
+        <v>9.754257239946504e-09</v>
       </c>
       <c r="J6" t="n">
         <v>9.755469739210855e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>6.044089635823458e-09</v>
+        <v>6.044089635823462e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.356016529952756e-08</v>
+        <v>1.356016529952759e-08</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.933311445719949e-09</v>
+        <v>4.933311445719947e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>6.192533572007999e-09</v>
+        <v>6.192533572008003e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>6.19303143904305e-09</v>
+        <v>6.19303143904304e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>7.646222081669611e-09</v>
+        <v>7.646222081669607e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>6.192532514390801e-09</v>
+        <v>6.192532514390753e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>6.192760950275064e-09</v>
+        <v>6.192760950275076e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>6.193030118107823e-09</v>
+        <v>6.193030118107848e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>6.192533572007999e-09</v>
+        <v>6.192533572008003e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>6.193030118107823e-09</v>
+        <v>6.193030118107848e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.606819108225804e-09</v>
+        <v>5.463144727609648e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>6.193030118107823e-09</v>
+        <v>6.193030118107848e-09</v>
       </c>
     </row>
     <row r="8">
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.449147922548352e-09</v>
+        <v>1.449147922548444e-09</v>
       </c>
       <c r="C8" t="n">
         <v>1.458616191296106e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.409388575243885e-09</v>
+        <v>1.409388575243884e-09</v>
       </c>
       <c r="E8" t="n">
         <v>1.458616191296106e-09</v>
@@ -770,22 +770,22 @@
         <v>1.458616191296106e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.466925974400097e-09</v>
+        <v>1.466925974400105e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.24140894926544e-09</v>
+        <v>1.241408949265437e-09</v>
       </c>
       <c r="I8" t="n">
         <v>1.458616191296106e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.452869524231941e-09</v>
+        <v>1.45286952423194e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.50684146677725e-09</v>
+        <v>1.506841466777256e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.518345503244037e-09</v>
+        <v>1.518345503244036e-09</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.554380129104458e-09</v>
+        <v>1.554380129104455e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.511356355991735e-09</v>
+        <v>1.511356355991734e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.538193117392922e-09</v>
+        <v>1.538193117392924e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.511356355991735e-09</v>
+        <v>1.511356355991734e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.511356355991735e-09</v>
+        <v>1.511356355991734e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.559475828875567e-09</v>
+        <v>1.559475828875569e-09</v>
       </c>
       <c r="H9" t="n">
         <v>1.470160843131607e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.511356355991735e-09</v>
+        <v>1.511356355991734e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.555975648302644e-09</v>
+        <v>1.555975648302643e-09</v>
       </c>
       <c r="K9" t="n">
         <v>1.577886559753926e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.582671015503592e-09</v>
+        <v>1.582671015503594e-09</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.152655218333453e-09</v>
+        <v>6.152655218333415e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.44642049937548e-09</v>
+        <v>6.446420499375381e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>6.845144606231502e-09</v>
+        <v>6.845144606231498e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.44642049937548e-09</v>
+        <v>6.446420499375381e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.44642049937548e-09</v>
+        <v>6.446420499375381e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.934582966240526e-09</v>
+        <v>6.934582966240333e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>7.507415735920828e-09</v>
+        <v>7.507415735920814e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.44642049937548e-09</v>
+        <v>6.446420499375381e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.394480882034654e-08</v>
+        <v>1.394480882034655e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>6.40577397472656e-09</v>
+        <v>6.40577397472666e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>7.672330844098981e-09</v>
+        <v>8.851639360415435e-09</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.889668644824058e-10</v>
+        <v>8.889668644823997e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>8.811532021808791e-10</v>
+        <v>8.811532021808685e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>8.889668644824058e-10</v>
+        <v>8.889668644823997e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>8.861357667445825e-10</v>
+        <v>8.861357667445717e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>8.861357667445823e-10</v>
+        <v>8.86135766744573e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>8.887242380017185e-10</v>
+        <v>8.887242380017149e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>8.889668644824058e-10</v>
+        <v>8.889668644823997e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>8.88613537001451e-10</v>
+        <v>8.886135370014414e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>8.889668644824058e-10</v>
+        <v>8.889668644823997e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.889668644824058e-10</v>
+        <v>8.889668644823997e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>8.889668644824058e-10</v>
+        <v>8.889668644823997e-10</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.217215332623253e-09</v>
+        <v>3.217215332623246e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.42009838179245e-09</v>
+        <v>1.420098381792436e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.423395524514078e-09</v>
+        <v>3.217628277491022e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.400534192846546e-09</v>
+        <v>1.400534192846538e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.423525783400486e-09</v>
+        <v>1.423525783400475e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.21697270614256e-09</v>
+        <v>1.422976581640222e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.20683599701228e-09</v>
+        <v>3.206835997012277e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.422865880639956e-09</v>
+        <v>1.422865880639948e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.211019968679955e-09</v>
+        <v>3.211019968679948e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.422595012091086e-09</v>
+        <v>1.422595012091081e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.423943741970443e-09</v>
+        <v>1.42394374197044e-09</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.136544478668701e-09</v>
+        <v>5.136544478668683e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.136191151187753e-09</v>
+        <v>5.136191151187722e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.13637563144638e-09</v>
+        <v>5.13637563144636e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.136568389627601e-09</v>
+        <v>5.136568389627579e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.136568389627601e-09</v>
+        <v>5.136568389627579e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.136301852188024e-09</v>
+        <v>5.136301852188007e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.136544478668701e-09</v>
+        <v>5.136544478668683e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.136191151187753e-09</v>
+        <v>5.136191151187722e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.136544478668701e-09</v>
+        <v>5.136544478668683e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.136544478668701e-09</v>
+        <v>5.136544478668683e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.136544478668701e-09</v>
+        <v>5.136544478668683e-09</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.79034009490592e-09</v>
+        <v>4.790340094905887e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>7.604772162161014e-09</v>
+        <v>7.604772162160947e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.187430656144968e-09</v>
+        <v>8.187430656144934e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>6.835097743513826e-09</v>
+        <v>6.835097743513777e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>4.879501206806947e-09</v>
+        <v>4.879501206806925e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>7.6037573283869e-09</v>
+        <v>7.60375732838685e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>7.603999954867451e-09</v>
+        <v>7.603999954867413e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>7.603646627386628e-09</v>
+        <v>7.603646627386593e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>7.604552920000296e-09</v>
+        <v>7.604552920000272e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.738074918444998e-09</v>
+        <v>4.738074918444988e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.054310295332837e-08</v>
+        <v>1.054310295332831e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.564266935396456e-09</v>
+        <v>3.564266935396425e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.449491128659605e-09</v>
+        <v>4.449491128659568e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.449845641746121e-09</v>
+        <v>4.449845641746074e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.47142910507654e-09</v>
+        <v>5.471429105076496e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.449490507053261e-09</v>
+        <v>4.449490507053227e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.449601829659875e-09</v>
+        <v>4.449601829659831e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.449844456140558e-09</v>
+        <v>4.449844456140535e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.449491128659605e-09</v>
+        <v>4.449491128659568e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.449844456140558e-09</v>
+        <v>4.449844456140535e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.936737861351324e-09</v>
+        <v>3.936737861351295e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.449844456140558e-09</v>
+        <v>4.449844456140535e-09</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.39277408958269e-09</v>
+        <v>1.392774089582685e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.257617455384261e-09</v>
+        <v>1.257617455384255e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.374841642141162e-09</v>
+        <v>1.374841642141155e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.257617455384261e-09</v>
+        <v>1.257617455384255e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.257617455384261e-09</v>
+        <v>1.257617455384255e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.372312248365965e-09</v>
+        <v>1.372312248365966e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.375739125118937e-09</v>
+        <v>1.375739125118934e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.257617455384261e-09</v>
+        <v>1.257617455384255e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.217356284659514e-09</v>
+        <v>1.21735628465951e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.383253901965224e-09</v>
+        <v>1.383253901965218e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.368698032593766e-09</v>
+        <v>1.352287649721632e-09</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.423523815810608e-09</v>
+        <v>1.423523815810604e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.299395075227925e-09</v>
+        <v>1.299395075227922e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.416222731516224e-09</v>
+        <v>1.416222731516217e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.299395075227925e-09</v>
+        <v>1.299395075227922e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.299395075227925e-09</v>
+        <v>1.299395075227922e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.413329972647168e-09</v>
+        <v>1.413329972647159e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.416678444071882e-09</v>
+        <v>1.416678444071879e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.299395075227925e-09</v>
+        <v>1.299395075227922e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.352175725815946e-09</v>
+        <v>1.35217572581594e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.419651196318878e-09</v>
+        <v>1.419651196318879e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.413797498142893e-09</v>
+        <v>1.413797498142886e-09</v>
       </c>
     </row>
   </sheetData>
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.705149371202231e-09</v>
+        <v>4.705149371202262e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>8.147422426420952e-09</v>
+        <v>8.147422426420962e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.074514259321803e-08</v>
+        <v>1.074514259321788e-08</v>
       </c>
       <c r="E2" t="n">
         <v>7.60850330561166e-09</v>
@@ -1322,22 +1322,22 @@
         <v>7.60850330561166e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>8.661931898979403e-09</v>
+        <v>8.661931898979365e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.493546653471018e-08</v>
+        <v>1.493546653471012e-08</v>
       </c>
       <c r="I2" t="n">
         <v>7.60850330561166e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>9.776903941730593e-09</v>
+        <v>9.776903941730595e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>7.861496014293336e-09</v>
+        <v>7.861496014293394e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.059028494736101e-08</v>
+        <v>1.059028494736098e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.991114687471764e-10</v>
+        <v>9.991114687471688e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.718564113222614e-10</v>
+        <v>9.71856411322261e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.991114687471764e-10</v>
+        <v>9.991114687471688e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.925040086332934e-10</v>
+        <v>9.925040086332841e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.925040086332949e-10</v>
+        <v>9.925040086332845e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.988703473128579e-10</v>
+        <v>9.988703473128448e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.991114687471764e-10</v>
+        <v>9.991114687471688e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.988007546303758e-10</v>
+        <v>9.988007546303605e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.991114687471727e-10</v>
+        <v>9.991114687471688e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.991114687471764e-10</v>
+        <v>9.991114687471688e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.991114687471764e-10</v>
+        <v>9.991114687471688e-10</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.445097611726895e-09</v>
+        <v>1.513551906175092e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.507797421790875e-09</v>
+        <v>1.507797421790874e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.519381318877186e-09</v>
+        <v>1.519382176297955e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.488557985439437e-09</v>
+        <v>1.48855798543944e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.513665206806097e-09</v>
+        <v>1.513665206806101e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.444856490292575e-09</v>
+        <v>3.444856490292572e-09</v>
       </c>
       <c r="H4" t="n">
         <v>3.492187545975846e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.444786897610084e-09</v>
+        <v>3.444786897610086e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.474888784139444e-09</v>
+        <v>3.474888784139446e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.513974938790864e-09</v>
+        <v>1.513974938790862e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.514684300234087e-09</v>
+        <v>1.514684300234091e-09</v>
       </c>
     </row>
     <row r="5">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.759421579209071e-09</v>
+        <v>5.759421579209073e-09</v>
       </c>
       <c r="C5" t="n">
         <v>5.756915729426632e-09</v>
@@ -1436,28 +1436,28 @@
         <v>5.759244312346005e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.759076999020355e-09</v>
+        <v>5.759076999020352e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.759076999020355e-09</v>
+        <v>5.759076999020352e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.759180457774745e-09</v>
+        <v>5.759180457774747e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.759421579209071e-09</v>
+        <v>5.759421579209073e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.759110865092267e-09</v>
+        <v>5.759110865092265e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.759421579209071e-09</v>
+        <v>5.759421579209073e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.759421579209071e-09</v>
+        <v>5.759421579209073e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.759421579209071e-09</v>
+        <v>5.759421579209073e-09</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.641320112042494e-09</v>
+        <v>5.641320112042488e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.997025964592345e-09</v>
+        <v>8.997025964599104e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.69485293658687e-09</v>
+        <v>9.694852936586845e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>8.080876281627698e-09</v>
+        <v>8.08087628162768e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.747518132956386e-09</v>
+        <v>5.747518132956369e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.998440943087503e-09</v>
+        <v>8.998440943087498e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.998682064523342e-09</v>
+        <v>8.998682064523325e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.998371350405025e-09</v>
+        <v>8.998371350405011e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.99934188282039e-09</v>
+        <v>8.99934188282037e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.578955390062206e-09</v>
+        <v>5.578955390062195e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.250572736237575e-08</v>
+        <v>1.250572736237573e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.308813937324309e-09</v>
+        <v>4.308813937324305e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.399099199333494e-09</v>
+        <v>5.399099199333492e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.401606322867909e-09</v>
+        <v>5.401606322867907e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.6623522124908e-09</v>
+        <v>6.66235221249081e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.401293498161747e-09</v>
+        <v>5.401293498161743e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.401363927681609e-09</v>
+        <v>5.401363927681608e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.401605049115934e-09</v>
+        <v>5.401605049115929e-09</v>
       </c>
       <c r="I7" t="n">
         <v>5.401294334999126e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.401605049115934e-09</v>
+        <v>5.401605049115929e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.025585646717638e-09</v>
+        <v>4.768438122957247e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.401605049115934e-09</v>
+        <v>5.401605049115929e-09</v>
       </c>
     </row>
     <row r="8">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.977658719212759e-09</v>
+        <v>1.977658719212757e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.38596218949638e-10</v>
+        <v>9.385962189496375e-10</v>
       </c>
       <c r="D8" t="n">
-        <v>1.310921830494818e-09</v>
+        <v>1.31092183049482e-09</v>
       </c>
       <c r="E8" t="n">
         <v>1.327091377002484e-09</v>
@@ -1562,7 +1562,7 @@
         <v>1.327091377002484e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.264924162552471e-09</v>
+        <v>1.264924162552472e-09</v>
       </c>
       <c r="H8" t="n">
         <v>1.250220062239468e-09</v>
@@ -1571,13 +1571,13 @@
         <v>1.327091377002484e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.623013354628266e-09</v>
+        <v>1.623013354628265e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.488245033429883e-09</v>
+        <v>2.488245033429887e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.31402505912804e-09</v>
+        <v>1.314025059128039e-09</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.000093063168894e-09</v>
+        <v>2.000093063168893e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.000132503472137e-09</v>
+        <v>1.000132503472135e-09</v>
       </c>
       <c r="D9" t="n">
         <v>1.398358473803638e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.371471782740229e-09</v>
+        <v>1.371471782740227e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.371471782740229e-09</v>
+        <v>1.371471782740227e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.323067266626244e-09</v>
+        <v>1.323067266626242e-09</v>
       </c>
       <c r="H9" t="n">
         <v>1.37385317404573e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.371471782740229e-09</v>
+        <v>1.371471782740227e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.687255038479303e-09</v>
+        <v>1.687255038479305e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>2.518451495935841e-09</v>
+        <v>2.518451495935849e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.383252865846121e-09</v>
+        <v>1.38325286584612e-09</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.649903507523079e-09</v>
+        <v>3.649903507523066e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.936980283221736e-09</v>
+        <v>6.93698028322169e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>8.976720864376835e-09</v>
+        <v>8.976720864376812e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.977181543024394e-09</v>
+        <v>6.977181543024369e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.977181543024394e-09</v>
+        <v>6.977181543024369e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>7.233579185441162e-09</v>
+        <v>7.233579185440783e-09</v>
       </c>
       <c r="H2" t="n">
         <v>1.069220189058074e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>6.977181543024394e-09</v>
+        <v>6.977181543024369e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>7.666036525938871e-09</v>
+        <v>7.666036525938873e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>6.339543512911576e-09</v>
+        <v>6.339543512911574e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>7.614449101890365e-09</v>
+        <v>7.614449101890323e-09</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.765260641460048e-10</v>
+        <v>9.765260641460083e-10</v>
       </c>
       <c r="C3" t="n">
         <v>9.494980151763179e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.765260641460048e-10</v>
+        <v>9.765260641460083e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.725795616776073e-10</v>
+        <v>9.725795616776001e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.725795616776067e-10</v>
+        <v>9.725795616776053e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.763138236583613e-10</v>
+        <v>9.763138236583471e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.765260641460048e-10</v>
+        <v>9.765260641460083e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.76401022026077e-10</v>
+        <v>9.764010220260764e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.765260641460048e-10</v>
+        <v>9.765260641460079e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.765260641460048e-10</v>
+        <v>9.765260641460083e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.765260641460048e-10</v>
+        <v>9.765260641460083e-10</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.289663938983832e-09</v>
+        <v>3.289663938983805e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.447845580769034e-09</v>
+        <v>1.447845580769019e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.458211128040206e-09</v>
+        <v>3.325963151022565e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.431253825608552e-09</v>
+        <v>1.431253825608549e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.454199004332871e-09</v>
+        <v>1.454199004332865e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.453300183569593e-09</v>
+        <v>1.453300183569573e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.342014412302717e-09</v>
+        <v>3.342014412302737e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.453387381937304e-09</v>
+        <v>1.4533873819373e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.508341155347825e-09</v>
+        <v>1.50834115534782e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.453351040025356e-09</v>
+        <v>1.45335104002534e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.454048535458821e-09</v>
+        <v>1.454048535458812e-09</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.50603144633998e-09</v>
+        <v>5.506031446339973e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.503541525510982e-09</v>
+        <v>5.503541525510985e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.505863787879713e-09</v>
+        <v>5.505863787879716e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.506410929939199e-09</v>
+        <v>5.506410929939195e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.506410929939199e-09</v>
+        <v>5.506410929939195e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.505819205852336e-09</v>
+        <v>5.505819205852344e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.50603144633998e-09</v>
+        <v>5.506031446339973e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.505906404220049e-09</v>
+        <v>5.505906404220051e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.50603144633998e-09</v>
+        <v>5.506031446339973e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.50603144633998e-09</v>
+        <v>5.506031446339973e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.50603144633998e-09</v>
+        <v>5.506031446339973e-09</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.39932514421907e-09</v>
+        <v>5.399325144219035e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.60191159592599e-09</v>
+        <v>8.601911595933428e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.267398692935126e-09</v>
+        <v>9.267398692935114e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.727894566077791e-09</v>
+        <v>7.727894566077776e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.501155154726305e-09</v>
+        <v>5.501155154726291e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.602867140832927e-09</v>
+        <v>8.602867140832919e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.603079381324505e-09</v>
+        <v>8.603079381324469e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.60295433920064e-09</v>
+        <v>8.60295433920063e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.603709011247971e-09</v>
+        <v>8.603709011247954e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.339813764417771e-09</v>
+        <v>5.339813764417741e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.194966857594985e-08</v>
+        <v>1.19496685759498e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.968987594808174e-09</v>
+        <v>3.968987594808143e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.965374762127118e-09</v>
+        <v>4.965374762127111e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.967865912470084e-09</v>
+        <v>4.967865912470071e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.12042280476867e-09</v>
+        <v>6.120422804768667e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.967738898732316e-09</v>
+        <v>4.967738898732302e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.967652442468479e-09</v>
+        <v>4.967652442468465e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.967864682956118e-09</v>
+        <v>4.967864682956086e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.967739640836188e-09</v>
+        <v>4.967739640836181e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.967864682956118e-09</v>
+        <v>4.967864682956086e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.389111892319077e-09</v>
+        <v>4.389111892319054e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.967864682956118e-09</v>
+        <v>4.967864682956086e-09</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.99724314749846e-09</v>
+        <v>1.997243147498467e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.582119719737388e-10</v>
+        <v>9.5821197197374e-10</v>
       </c>
       <c r="D8" t="n">
-        <v>1.343855619169022e-09</v>
+        <v>1.34385561916903e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.33764880876779e-09</v>
+        <v>1.337648808767791e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.33764880876779e-09</v>
+        <v>1.337648808767791e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.288588812052965e-09</v>
+        <v>1.288588812052954e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.328131748020771e-09</v>
+        <v>1.328131748020758e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.33764880876779e-09</v>
+        <v>1.337648808767791e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.665612086077074e-09</v>
+        <v>1.665612086077054e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.51511160301209e-09</v>
+        <v>2.515111603012066e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.36977931607148e-09</v>
+        <v>1.369779316071469e-09</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.008126107495974e-09</v>
+        <v>2.008126107495971e-09</v>
       </c>
       <c r="C9" t="n">
         <v>1.008504897226529e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.413622250570649e-09</v>
+        <v>1.413622250570657e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.37842594274856e-09</v>
+        <v>1.378425942748561e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.37842594274856e-09</v>
+        <v>1.378425942748561e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.332851670397739e-09</v>
+        <v>1.332851670397735e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.407367321446785e-09</v>
+        <v>1.407367321446775e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.37842594274856e-09</v>
+        <v>1.378425942748561e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.707626244891426e-09</v>
+        <v>1.707626244891428e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>2.529134395768908e-09</v>
+        <v>2.529134395768891e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.408470866420012e-09</v>
+        <v>1.408470866420014e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.27872468700711e-09</v>
+        <v>3.278724687007102e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.255136845954082e-09</v>
+        <v>6.255136845954077e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>8.015934967764576e-09</v>
+        <v>8.015934967764511e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.816720254253866e-09</v>
+        <v>6.816720254253664e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.816720254253866e-09</v>
+        <v>6.816720254253664e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.619960314773536e-09</v>
+        <v>6.619960314773386e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>8.747127956377287e-09</v>
+        <v>8.747127956377234e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.816720254253866e-09</v>
+        <v>6.816720254253664e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>6.114269869759904e-09</v>
+        <v>6.114269869759888e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>5.843367797364233e-09</v>
+        <v>5.84336779736422e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>7.298337715844226e-09</v>
+        <v>7.298337715844217e-09</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.743286397400275e-10</v>
+        <v>9.743286397400256e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.455034819507166e-10</v>
+        <v>9.45503481950717e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.743286397400275e-10</v>
+        <v>9.743286397400254e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.716589691762655e-10</v>
+        <v>9.716589691762428e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.716589691762655e-10</v>
+        <v>9.716589691762428e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.741277792721161e-10</v>
+        <v>9.741277792721136e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.743286397400275e-10</v>
+        <v>9.743286397400254e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.742772915730159e-10</v>
+        <v>9.742772915730463e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.743286397400275e-10</v>
+        <v>9.743286397400256e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.743286397400275e-10</v>
+        <v>9.743286397400254e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.743286397400275e-10</v>
+        <v>9.743286397400254e-10</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.28723073956625e-09</v>
+        <v>1.453518488667855e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.44714480830733e-09</v>
+        <v>1.447144808306883e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.457338705010536e-09</v>
+        <v>1.457338705010312e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.432015446432305e-09</v>
+        <v>1.432015446432316e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.454481491560351e-09</v>
+        <v>1.454481491560357e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.453317628199959e-09</v>
+        <v>3.287029879098328e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.345905935290315e-09</v>
+        <v>3.345905935290291e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.453467140500859e-09</v>
+        <v>3.287179391399254e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.507931814827764e-09</v>
+        <v>3.318020900627606e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.453303232084345e-09</v>
+        <v>1.453303232084335e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.454003292498771e-09</v>
+        <v>1.454003292498777e-09</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.488348667206634e-09</v>
+        <v>5.488348667206621e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.485858510910749e-09</v>
+        <v>5.485858510910742e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.488181372592614e-09</v>
+        <v>5.488181372592599e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.489130968878852e-09</v>
+        <v>5.489130968878827e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.489130968878852e-09</v>
+        <v>5.489130968878827e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.488147806738722e-09</v>
+        <v>5.488147806738708e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.488348667206634e-09</v>
+        <v>5.488348667206621e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.488297319039684e-09</v>
+        <v>5.488297319039641e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.488348667206634e-09</v>
+        <v>5.488348667206621e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.488348667206634e-09</v>
+        <v>5.488348667206621e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.488348667206634e-09</v>
+        <v>5.488348667206621e-09</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.375966186106698e-09</v>
+        <v>5.375966186106686e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.563317250348355e-09</v>
+        <v>8.563317250339026e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.225269645414144e-09</v>
+        <v>9.225269645414141e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.693592958236444e-09</v>
+        <v>7.69359295823644e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.477573214069225e-09</v>
+        <v>5.477573214069215e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.563973127880066e-09</v>
+        <v>8.563973127880044e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.56417398835362e-09</v>
+        <v>8.564173988353617e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.564122640180976e-09</v>
+        <v>8.564122640180972e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.564800562914555e-09</v>
+        <v>8.564800562914552e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.316743589315979e-09</v>
+        <v>5.31674358931597e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.189452363176303e-08</v>
+        <v>1.189452363176304e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.84385918774561e-09</v>
+        <v>3.843859187745596e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.805334608812407e-09</v>
+        <v>4.805334608812381e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.807826006566587e-09</v>
+        <v>4.807826006566553e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.920169485072899e-09</v>
+        <v>5.920169485072866e-09</v>
       </c>
       <c r="F7" t="n">
         <v>4.807772704120849e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.807623904640401e-09</v>
+        <v>4.807623904640344e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.80782476510827e-09</v>
+        <v>4.807824765108251e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.807773416941304e-09</v>
+        <v>4.807773416941278e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.80782476510827e-09</v>
+        <v>4.807824765108251e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.226639734091715e-09</v>
+        <v>3.594019714202433e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.80782476510827e-09</v>
+        <v>4.807824765108251e-09</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.998494164711012e-09</v>
+        <v>1.998494164711013e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.64643319610551e-10</v>
+        <v>9.646433196105503e-10</v>
       </c>
       <c r="D8" t="n">
-        <v>1.354867847548695e-09</v>
+        <v>1.354867847548696e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.329083206937375e-09</v>
+        <v>1.329083206937385e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.329083206937375e-09</v>
+        <v>1.329083206937385e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.291634241660452e-09</v>
+        <v>1.291634241660457e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.357554590878291e-09</v>
+        <v>1.357554590878293e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.329083206937375e-09</v>
+        <v>1.329083206937385e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.686097740776565e-09</v>
+        <v>1.686097740776567e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.511972117959663e-09</v>
+        <v>2.511972117959646e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.365256959596999e-09</v>
+        <v>1.365256959596997e-09</v>
       </c>
     </row>
     <row r="9">
@@ -2379,34 +2379,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.004258658094454e-09</v>
+        <v>2.004258658094451e-09</v>
       </c>
       <c r="C9" t="n">
         <v>1.005445227813259e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.410907972819263e-09</v>
+        <v>1.410907972819261e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.367734247687279e-09</v>
+        <v>1.36773424768728e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.367734247687279e-09</v>
+        <v>1.36773424768728e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.327434793417424e-09</v>
+        <v>1.327434793417425e-09</v>
       </c>
       <c r="H9" t="n">
         <v>1.412113178416871e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.367734247687279e-09</v>
+        <v>1.36773424768728e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.707008969497893e-09</v>
+        <v>1.707008969497892e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>2.519060791053325e-09</v>
+        <v>2.519060791053317e-09</v>
       </c>
       <c r="L9" t="n">
         <v>1.400140922227839e-09</v>
@@ -2495,13 +2495,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.488558305098446e-09</v>
+        <v>3.48855830509844e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.010511810274736e-09</v>
+        <v>5.010511810274743e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>8.821852987044119e-09</v>
+        <v>8.821852987044107e-09</v>
       </c>
       <c r="E2" t="n">
         <v>6.919490253056248e-09</v>
@@ -2510,22 +2510,22 @@
         <v>6.919490253056248e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>7.68628895887344e-09</v>
+        <v>7.686288958873125e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.310345096219868e-08</v>
+        <v>1.310345096219854e-08</v>
       </c>
       <c r="I2" t="n">
         <v>6.919490253056248e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>9.683785272213639e-09</v>
+        <v>9.683785272213604e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>7.089871711000034e-09</v>
+        <v>7.089871711000007e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.097471332451793e-08</v>
+        <v>1.097471332451792e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.884448483082782e-10</v>
+        <v>9.884448483082751e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.59875748064912e-10</v>
+        <v>9.598757480649155e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.884448483082782e-10</v>
+        <v>9.884448483082751e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.849655590049437e-10</v>
+        <v>9.849655590049324e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.849655590049408e-10</v>
+        <v>9.849655590049346e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.882099466609172e-10</v>
+        <v>9.882099466609153e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.884448483082782e-10</v>
+        <v>9.884448483082751e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.881683792960239e-10</v>
+        <v>9.88168379296019e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.884448483082782e-10</v>
+        <v>9.884448483082751e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.884448483082782e-10</v>
+        <v>9.884448483082751e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.884448483082782e-10</v>
+        <v>9.884448483082751e-10</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.420111337843262e-09</v>
+        <v>1.494435148086263e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.484526607282444e-09</v>
+        <v>1.484526607282435e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.498275212159187e-09</v>
+        <v>1.498275212159185e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.470971172262236e-09</v>
+        <v>1.470971172262227e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.494969129336289e-09</v>
+        <v>1.494969129336287e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.494200246438902e-09</v>
+        <v>1.494200246438897e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.465271155177424e-09</v>
+        <v>3.465271155177409e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.419834868830999e-09</v>
+        <v>1.494158679074003e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.449470756321262e-09</v>
+        <v>3.449470756321255e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.495082363933214e-09</v>
+        <v>1.495082363933207e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.496078528855972e-09</v>
+        <v>1.49607852885597e-09</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.738006266485305e-09</v>
+        <v>5.738006266485289e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.735457482590579e-09</v>
+        <v>5.735457482590568e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.737829368691309e-09</v>
+        <v>5.737829368691298e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.73850784084771e-09</v>
+        <v>5.738507840847689e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.73850784084771e-09</v>
+        <v>5.738507840847689e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.737771364837942e-09</v>
+        <v>5.737771364837928e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.738006266485305e-09</v>
+        <v>5.738006266485289e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.737729797473047e-09</v>
+        <v>5.737729797473037e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.738006266485305e-09</v>
+        <v>5.738006266485289e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.738006266485305e-09</v>
+        <v>5.738006266485289e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.738006266485305e-09</v>
+        <v>5.738006266485289e-09</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.606708352189265e-09</v>
+        <v>5.60670835218926e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.946471700679032e-09</v>
+        <v>8.946471700678989e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.640112563632068e-09</v>
+        <v>9.640112563632025e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>8.034877422130611e-09</v>
+        <v>8.034877422130596e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.712896276187674e-09</v>
+        <v>5.712896276187662e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.947163763069198e-09</v>
+        <v>8.947163763069173e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.947398664717872e-09</v>
+        <v>8.947398664717842e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.947122195704304e-09</v>
+        <v>8.947122195704281e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.948055206565808e-09</v>
+        <v>8.948055206565799e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.544653314480083e-09</v>
+        <v>5.544653314480071e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.243702904058538e-08</v>
+        <v>1.243702904058533e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.251868851098272e-09</v>
+        <v>4.251868851098278e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.328678384510652e-09</v>
+        <v>5.328678384510623e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.331228451259042e-09</v>
+        <v>5.331228451259019e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.576507469379148e-09</v>
+        <v>6.576507469379149e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.330949897980168e-09</v>
+        <v>5.330949897980135e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.330992266757994e-09</v>
+        <v>5.330992266757988e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.331227168405374e-09</v>
+        <v>5.33122716840535e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.330950699393126e-09</v>
+        <v>5.330950699393092e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.331227168405374e-09</v>
+        <v>5.33122716840535e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.972122049649489e-09</v>
+        <v>3.972122049649472e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.331227168405374e-09</v>
+        <v>5.33122716840535e-09</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.041277281156251e-09</v>
+        <v>2.04127728115625e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.896256896939163e-10</v>
+        <v>9.896256896939139e-10</v>
       </c>
       <c r="D8" t="n">
-        <v>1.332574282523662e-09</v>
+        <v>1.332574282523663e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.322134369892251e-09</v>
+        <v>1.322134369892249e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.322134369892251e-09</v>
+        <v>1.322134369892249e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.275402992214557e-09</v>
+        <v>1.27540299221455e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.264791681253995e-09</v>
+        <v>1.264791681253988e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.322134369892251e-09</v>
+        <v>1.322134369892249e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.59944731905274e-09</v>
+        <v>1.599447319052738e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.487465154962112e-09</v>
+        <v>2.48746515496206e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.289464848172473e-09</v>
+        <v>1.289464848172471e-09</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.047079185945225e-09</v>
+        <v>2.047079185945222e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.009792155418818e-09</v>
+        <v>1.009792155418816e-09</v>
       </c>
       <c r="D9" t="n">
         <v>1.394132141105584e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.357606884877645e-09</v>
+        <v>1.35760688487765e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.357606884877645e-09</v>
+        <v>1.35760688487765e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.320855296597363e-09</v>
+        <v>1.320855296597361e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.366709395054844e-09</v>
+        <v>1.366709395054845e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.357606884877645e-09</v>
+        <v>1.35760688487765e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.662981201715728e-09</v>
+        <v>1.662981201715723e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>2.507545320031909e-09</v>
+        <v>2.507545320031853e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.363606382273129e-09</v>
+        <v>1.363606382273125e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.295826026468637e-09</v>
+        <v>3.295826026468649e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.054963698712063e-09</v>
+        <v>5.054963698712071e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>6.724885518417447e-09</v>
+        <v>6.724885518417455e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.837377314594723e-09</v>
+        <v>6.837377314594718e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.837377314594723e-09</v>
+        <v>6.837377314594718e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.149421928549042e-09</v>
+        <v>6.149421928549153e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>7.052599614001297e-09</v>
+        <v>7.052599614001296e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.837377314594723e-09</v>
+        <v>6.837377314594718e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>7.425673824494424e-09</v>
+        <v>7.425673824494428e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>5.693503731545537e-09</v>
+        <v>5.693503731545534e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>7.898683848843454e-09</v>
+        <v>7.898683848843452e-09</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.489173536884129e-10</v>
+        <v>9.489173536884156e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.226823990634995e-10</v>
+        <v>9.226823990634976e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.489173536884129e-10</v>
+        <v>9.489173536884156e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.476397947509978e-10</v>
+        <v>9.47639794750996e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.476397947509988e-10</v>
+        <v>9.47639794750996e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.487187408774076e-10</v>
+        <v>9.487187408774039e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.489173536884129e-10</v>
+        <v>9.489173536884156e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.488688539930073e-10</v>
+        <v>9.48868853993005e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.489173536884129e-10</v>
+        <v>9.489173536884156e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.489173536884129e-10</v>
+        <v>9.489173536884156e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.489173536884129e-10</v>
+        <v>9.489173536884156e-10</v>
       </c>
     </row>
     <row r="4">
@@ -2974,34 +2974,34 @@
         <v>1.426215645395613e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.418858590413594e-09</v>
+        <v>1.418858590413602e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>3.280729115981331e-09</v>
+        <v>1.427811060859224e-09</v>
       </c>
       <c r="E4" t="n">
         <v>1.406455524242461e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.427309415743639e-09</v>
+        <v>1.427309415743635e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.426017032584607e-09</v>
+        <v>3.245447776403317e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.295631677693818e-09</v>
+        <v>3.295631677693816e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.426167145700211e-09</v>
+        <v>3.245597889518918e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.48001371703117e-09</v>
+        <v>1.480013717031172e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.426082537912784e-09</v>
+        <v>1.426082537912788e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.426979967006441e-09</v>
+        <v>1.42697996700643e-09</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.416190625375395e-09</v>
+        <v>5.416190625375396e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.413704358611732e-09</v>
+        <v>5.413704358611747e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.416024025234966e-09</v>
+        <v>5.416024025234978e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.417207915961785e-09</v>
+        <v>5.417207915961808e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.417207915961785e-09</v>
+        <v>5.417207915961808e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.415992012564388e-09</v>
+        <v>5.415992012564396e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.416190625375395e-09</v>
+        <v>5.416190625375396e-09</v>
       </c>
       <c r="I5" t="n">
         <v>5.416142125679984e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.416190625375395e-09</v>
+        <v>5.416190625375396e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.416190625375395e-09</v>
+        <v>5.416190625375396e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.416190625375395e-09</v>
+        <v>5.416190625375396e-09</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.245252129402884e-09</v>
+        <v>5.245252129402889e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.35601643946537e-09</v>
+        <v>8.356016439465368e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.001835040013468e-09</v>
+        <v>9.001835040013456e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.507272849616055e-09</v>
+        <v>7.50727284961604e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.34456574950664e-09</v>
+        <v>5.344565749506637e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.356464989335461e-09</v>
+        <v>8.35646498933545e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.356663602150473e-09</v>
+        <v>8.356663602150456e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.356615102451058e-09</v>
+        <v>8.356615102451072e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.35727508407637e-09</v>
+        <v>8.357275084076365e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.187456063858698e-09</v>
+        <v>5.187456063858697e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.160679305782924e-08</v>
+        <v>1.160679305782923e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.841930511248196e-09</v>
+        <v>3.8419305112482e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.805600192443466e-09</v>
+        <v>4.805600192443479e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.808087705175704e-09</v>
+        <v>4.808087705175709e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.922961712365942e-09</v>
+        <v>5.922961712365922e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.808037278227846e-09</v>
+        <v>4.80803727822783e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.807887846396124e-09</v>
+        <v>4.807887846396117e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.808086459207137e-09</v>
+        <v>4.808086459207145e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.80803795951173e-09</v>
+        <v>4.808037959511712e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.808086459207137e-09</v>
+        <v>4.808086459207145e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.248292432622174e-09</v>
+        <v>3.59152333957185e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.808086459207137e-09</v>
+        <v>4.808086459207145e-09</v>
       </c>
     </row>
     <row r="8">
@@ -3131,34 +3131,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.037666558803766e-09</v>
+        <v>2.037666558803768e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.575178302587829e-10</v>
+        <v>9.575178302587806e-10</v>
       </c>
       <c r="D8" t="n">
-        <v>1.327421215936e-09</v>
+        <v>1.327421215935998e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.271969627588066e-09</v>
+        <v>1.271969627588065e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.271969627588066e-09</v>
+        <v>1.271969627588065e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.269535486495105e-09</v>
+        <v>1.269535486495106e-09</v>
       </c>
       <c r="H8" t="n">
         <v>1.335116253111501e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.271969627588066e-09</v>
+        <v>1.271969627588065e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.575092958931602e-09</v>
+        <v>1.575092958931598e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.466425759305602e-09</v>
+        <v>2.466425759305628e-09</v>
       </c>
       <c r="L8" t="n">
         <v>1.302308739710452e-09</v>
@@ -3174,31 +3174,31 @@
         <v>2.043172700491922e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>9.822823670214556e-10</v>
+        <v>9.82282367021455e-10</v>
       </c>
       <c r="D9" t="n">
-        <v>1.365926499017861e-09</v>
+        <v>1.365926499017864e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.312019186757333e-09</v>
+        <v>1.312019186757332e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.312019186757333e-09</v>
+        <v>1.312019186757331e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.299458272568906e-09</v>
+        <v>1.299458272568907e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.369138797454258e-09</v>
+        <v>1.369138797454257e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.312019186757333e-09</v>
+        <v>1.312019186757332e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.615485540246417e-09</v>
+        <v>1.615485540246415e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>2.472338927980693e-09</v>
+        <v>2.472338927980729e-09</v>
       </c>
       <c r="L9" t="n">
         <v>1.345678922106492e-09</v>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.530837668268702e-09</v>
+        <v>3.530837668268703e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.375530966039333e-09</v>
+        <v>5.375530966039336e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>6.800189612476405e-09</v>
+        <v>6.8001896124764e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.981445024268098e-09</v>
+        <v>6.981445024268076e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.981445024268098e-09</v>
+        <v>6.981445024268076e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.225579647932847e-09</v>
+        <v>6.225579647932894e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>6.851338259433619e-09</v>
+        <v>6.851338259433625e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.981445024268098e-09</v>
+        <v>6.981445024268076e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>7.485966526320089e-09</v>
+        <v>7.48596652632011e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>5.674266997326628e-09</v>
+        <v>5.674266997326611e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>7.829769527524531e-09</v>
+        <v>7.829769527524522e-09</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.508140596846864e-10</v>
+        <v>9.508140596846846e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.232762526101037e-10</v>
+        <v>9.232762526101014e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.508140596846864e-10</v>
+        <v>9.508140596846846e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.513634909405587e-10</v>
+        <v>9.51363490940557e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.513634909405595e-10</v>
+        <v>9.513634909405564e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.506028826587674e-10</v>
+        <v>9.506028826593882e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.508140596846864e-10</v>
+        <v>9.508140596846846e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.506875071412494e-10</v>
+        <v>9.50687507142499e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.508140596846864e-10</v>
+        <v>9.508140596846846e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.508140596846864e-10</v>
+        <v>9.508140596846846e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.508140596846864e-10</v>
+        <v>9.508140596846846e-10</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.263862748596406e-09</v>
+        <v>3.263862748596407e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.434739302923281e-09</v>
+        <v>1.434739302923279e-09</v>
       </c>
       <c r="D4" t="n">
         <v>1.443157441803998e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.421397913710418e-09</v>
+        <v>1.421397913710423e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.443213072758579e-09</v>
+        <v>1.443213072758578e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.26365157157048e-09</v>
+        <v>3.263651571570483e-09</v>
       </c>
       <c r="H4" t="n">
         <v>3.323151683108102e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.441957295806848e-09</v>
+        <v>1.441957295806845e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.294783288115805e-09</v>
+        <v>3.294783288115806e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.441873960693858e-09</v>
+        <v>1.441873960693861e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.442772652900653e-09</v>
+        <v>1.442772652900654e-09</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.379395349992622e-09</v>
+        <v>5.379395349992629e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.376900828958485e-09</v>
+        <v>5.37690082895849e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.379229530503614e-09</v>
+        <v>5.379229530503615e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.380964417702928e-09</v>
+        <v>5.380964417702932e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.380964417702928e-09</v>
+        <v>5.380964417702932e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.379184172966696e-09</v>
+        <v>5.379184172966694e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.379395349992622e-09</v>
+        <v>5.379395349992629e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.379268797449175e-09</v>
+        <v>5.379268797449178e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.379395349992622e-09</v>
+        <v>5.379395349992629e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.379395349992622e-09</v>
+        <v>5.379395349992629e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.379395349992622e-09</v>
+        <v>5.379395349992629e-09</v>
       </c>
     </row>
     <row r="6">
@@ -3447,34 +3447,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.177791003873824e-09</v>
+        <v>5.17779100387382e-09</v>
       </c>
       <c r="C6" t="n">
         <v>8.242093076547966e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.877572394709506e-09</v>
+        <v>8.877572394709505e-09</v>
       </c>
       <c r="E6" t="n">
         <v>7.406083612575028e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.275910538195045e-09</v>
+        <v>5.275910538195047e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.241945113079594e-09</v>
+        <v>8.241945113079603e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.242156290111261e-09</v>
+        <v>8.242156290111265e-09</v>
       </c>
       <c r="I6" t="n">
         <v>8.242029737562084e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.242758525971394e-09</v>
+        <v>8.242758525971391e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.120868845408715e-09</v>
+        <v>5.120868845408712e-09</v>
       </c>
       <c r="L6" t="n">
         <v>1.144314206991462e-08</v>
@@ -3487,34 +3487,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.710070675730412e-09</v>
+        <v>3.710070675730417e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.63544528425455e-09</v>
+        <v>4.635445284254575e-09</v>
       </c>
       <c r="D7" t="n">
         <v>4.637941059427503e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.708554849041635e-09</v>
+        <v>5.708554849041655e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.637812581604653e-09</v>
+        <v>4.637812581604667e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.637728628262764e-09</v>
+        <v>4.63772862826277e-09</v>
       </c>
       <c r="H7" t="n">
         <v>4.637939805288682e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.637813252745248e-09</v>
+        <v>4.637813252745243e-09</v>
       </c>
       <c r="J7" t="n">
         <v>4.637939805288682e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.10032931508539e-09</v>
+        <v>4.078517727512077e-09</v>
       </c>
       <c r="L7" t="n">
         <v>4.637939805288682e-09</v>
@@ -3527,13 +3527,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.051245681342976e-09</v>
+        <v>2.051245681342974e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.341707970231308e-10</v>
+        <v>9.341707970231297e-10</v>
       </c>
       <c r="D8" t="n">
-        <v>1.296921629486861e-09</v>
+        <v>1.29692162948686e-09</v>
       </c>
       <c r="E8" t="n">
         <v>1.24109803177094e-09</v>
@@ -3542,7 +3542,7 @@
         <v>1.24109803177094e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.249743106774237e-09</v>
+        <v>1.249743106774236e-09</v>
       </c>
       <c r="H8" t="n">
         <v>1.310780162084655e-09</v>
@@ -3551,13 +3551,13 @@
         <v>1.24109803177094e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.538588215236559e-09</v>
+        <v>1.538588215236555e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.439612699354466e-09</v>
+        <v>2.439612699354463e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.277181713164794e-09</v>
+        <v>1.277181713164793e-09</v>
       </c>
     </row>
     <row r="9">
@@ -3573,31 +3573,31 @@
         <v>9.636469287614301e-10</v>
       </c>
       <c r="D9" t="n">
-        <v>1.336991260969485e-09</v>
+        <v>1.336991260969482e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.283667024254411e-09</v>
+        <v>1.28366702425441e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.283667024254411e-09</v>
+        <v>1.28366702425441e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.281041379460538e-09</v>
+        <v>1.281041379460537e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.342709904093285e-09</v>
+        <v>1.342709904093283e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.283667024254411e-09</v>
+        <v>1.28366702425441e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.580386444632469e-09</v>
+        <v>1.580386444632466e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>2.445702569717415e-09</v>
+        <v>2.445702569717411e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.320135447229014e-09</v>
+        <v>1.320135447229013e-09</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.474762955359475e-09</v>
+        <v>3.47476295535946e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.113561044069015e-09</v>
+        <v>5.113561044069021e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>7.084321299486314e-09</v>
+        <v>7.08432129948629e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>7.011703714517091e-09</v>
+        <v>7.011703714517088e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>7.011703714517091e-09</v>
+        <v>7.011703714517088e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.739838905054353e-09</v>
+        <v>6.739838905053989e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.202175287946242e-08</v>
+        <v>1.202175287946241e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.011703714517091e-09</v>
+        <v>7.011703714517088e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>6.791922004049806e-09</v>
+        <v>6.791922004049786e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>6.323934679513939e-09</v>
+        <v>6.323934679513909e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.038832292851579e-08</v>
+        <v>1.038832292851576e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.852488872446656e-10</v>
+        <v>9.852488872446553e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.573889684218512e-10</v>
+        <v>9.573889684218505e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.852488872446656e-10</v>
+        <v>9.852488872446553e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.831365296458123e-10</v>
+        <v>9.831365296458156e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.83136529645812e-10</v>
+        <v>9.831365296458158e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.850430577823314e-10</v>
+        <v>9.850430577823242e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.852488872446656e-10</v>
+        <v>9.852488872446553e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.851547619650963e-10</v>
+        <v>9.851547619651059e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.852488872446656e-10</v>
+        <v>9.852488872446553e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.852488872446656e-10</v>
+        <v>9.852488872446553e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.852488872446656e-10</v>
+        <v>9.852488872446553e-10</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.40981298343671e-09</v>
+        <v>1.486892543655678e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.47859193674589e-09</v>
+        <v>1.478591936745921e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.488498309776176e-09</v>
+        <v>1.488498309776145e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.465409428919706e-09</v>
+        <v>1.465409428919709e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.487830437251152e-09</v>
+        <v>1.487830437251157e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.409607153974368e-09</v>
+        <v>3.409607153974346e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.454250490269767e-09</v>
+        <v>3.454250490269739e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.486798418376141e-09</v>
+        <v>3.409718858157155e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.438858385722445e-09</v>
+        <v>3.438858385722418e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.487269040526478e-09</v>
+        <v>1.487269040526462e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.488357333284038e-09</v>
+        <v>1.488357333284024e-09</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.72035244852588e-09</v>
+        <v>5.720352448525872e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.717851451673737e-09</v>
+        <v>5.717851451673731e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.720175976916795e-09</v>
+        <v>5.720175976916776e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.721197081798042e-09</v>
+        <v>5.721197081798043e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.721197081798042e-09</v>
+        <v>5.721197081798043e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.720146619063546e-09</v>
+        <v>5.720146619063528e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.72035244852588e-09</v>
+        <v>5.720352448525872e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.720258323246327e-09</v>
+        <v>5.720258323246323e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.72035244852588e-09</v>
+        <v>5.720352448525872e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.72035244852588e-09</v>
+        <v>5.720352448525872e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.72035244852588e-09</v>
+        <v>5.720352448525872e-09</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.561841167840714e-09</v>
+        <v>5.561841167840684e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.874253356382654e-09</v>
+        <v>8.874253356382649e-09</v>
       </c>
       <c r="D6" t="n">
         <v>9.561986856797767e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.970311920473827e-09</v>
+        <v>7.970311920473837e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.667433872222231e-09</v>
+        <v>5.667433872222242e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.874779087741664e-09</v>
+        <v>8.874779087741666e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.874984917205263e-09</v>
+        <v>8.874984917205283e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.874890791924452e-09</v>
+        <v>8.874890791924464e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.875636045357849e-09</v>
+        <v>8.875636045357843e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.50029782168535e-09</v>
+        <v>5.500297821685356e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.233584060443564e-08</v>
+        <v>1.233584060443568e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.204157171962926e-09</v>
+        <v>4.204157171962919e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.268238116263265e-09</v>
+        <v>5.268238116263277e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.270740373041174e-09</v>
+        <v>5.270740373041173e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.50145809342467e-09</v>
+        <v>6.501458093424694e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.27064420522978e-09</v>
+        <v>5.27064420522979e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.270533283653079e-09</v>
+        <v>5.270533283653111e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.270739113115419e-09</v>
+        <v>5.270739113115423e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.270644987835866e-09</v>
+        <v>5.270644987835883e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.270739113115419e-09</v>
+        <v>5.270739113115423e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.627685547069905e-09</v>
+        <v>4.652757877541141e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.270739113115419e-09</v>
+        <v>5.270739113115423e-09</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.048419087079581e-09</v>
+        <v>2.048419087079569e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.814594081110397e-10</v>
+        <v>9.814594081110391e-10</v>
       </c>
       <c r="D8" t="n">
-        <v>1.353022577395634e-09</v>
+        <v>1.353022577395629e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.301005491085901e-09</v>
+        <v>1.301005491085902e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.301005491085901e-09</v>
+        <v>1.301005491085902e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.283669974378744e-09</v>
+        <v>1.283669974378737e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.267143568626217e-09</v>
+        <v>1.267143568626212e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.301005491085901e-09</v>
+        <v>1.301005491085902e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.632415048925244e-09</v>
+        <v>1.632415048925248e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.485485365572788e-09</v>
+        <v>2.485485365572767e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.284106282528466e-09</v>
+        <v>1.284106282528458e-09</v>
       </c>
     </row>
     <row r="9">
@@ -3963,13 +3963,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.05394405017155e-09</v>
+        <v>2.053944050171539e-09</v>
       </c>
       <c r="C9" t="n">
         <v>1.003096225631157e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.391159306366074e-09</v>
+        <v>1.391159306366058e-09</v>
       </c>
       <c r="E9" t="n">
         <v>1.338102991428761e-09</v>
@@ -3978,22 +3978,22 @@
         <v>1.338102991428761e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.316806727072901e-09</v>
+        <v>1.316806727072897e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.356346582947388e-09</v>
+        <v>1.356346582947373e-09</v>
       </c>
       <c r="I9" t="n">
         <v>1.338102991428761e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.658863223998898e-09</v>
+        <v>1.658863223998885e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>2.495495326746701e-09</v>
+        <v>2.495495326746719e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.351625964188514e-09</v>
+        <v>1.35162596418851e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.350906603337728e-09</v>
+        <v>3.350906603337683e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.072345611951436e-09</v>
+        <v>5.072345611951444e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>6.713179139907138e-09</v>
+        <v>6.713179139907136e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.829987713126108e-09</v>
+        <v>6.829987713126074e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.829987713126108e-09</v>
+        <v>6.829987713126074e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.108039834252851e-09</v>
+        <v>6.108039834252572e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>6.83899184934071e-09</v>
+        <v>6.838991849340651e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.829987713126108e-09</v>
+        <v>6.829987713126074e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>7.363773334051134e-09</v>
+        <v>7.363773334051126e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>5.827499443031317e-09</v>
+        <v>5.827499443031021e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>7.625342154016989e-09</v>
+        <v>7.625342154016914e-09</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.351268240188324e-10</v>
+        <v>9.351268240188123e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.08329280276049e-10</v>
+        <v>9.083292802760504e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.351268240188324e-10</v>
+        <v>9.351268240188123e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.347342451471715e-10</v>
+        <v>9.347342451471702e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.347342451471711e-10</v>
+        <v>9.347342451471707e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.349049921086305e-10</v>
+        <v>9.349049921086127e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.351268240188324e-10</v>
+        <v>9.351268240188123e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.349230646485295e-10</v>
+        <v>9.349230646485266e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.351268240188324e-10</v>
+        <v>9.351268240188123e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.351268240188324e-10</v>
+        <v>9.351268240188123e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.351268240188324e-10</v>
+        <v>9.351268240188123e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.231849326555272e-09</v>
+        <v>1.417798418620069e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.410334659590036e-09</v>
+        <v>1.41033465959005e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.419493891897145e-09</v>
+        <v>1.419494681849809e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.397937378153981e-09</v>
+        <v>1.397937378153982e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.418786958617621e-09</v>
+        <v>1.418786958617623e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.417576586709874e-09</v>
+        <v>1.417576586709873e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.280447568901338e-09</v>
+        <v>3.280447568901333e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.417594659249779e-09</v>
+        <v>3.231645567184953e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.471303993792439e-09</v>
+        <v>3.260110032512373e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.418382277352288e-09</v>
+        <v>1.418382277352265e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.418445392300802e-09</v>
+        <v>1.418445392300775e-09</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.351226792275014e-09</v>
+        <v>5.351226792274958e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.348742099092327e-09</v>
+        <v>5.348742099092325e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.351061408273932e-09</v>
+        <v>5.351061408273915e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.352391361888771e-09</v>
+        <v>5.352391361888779e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.352391361888771e-09</v>
+        <v>5.352391361888779e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.351004960364765e-09</v>
+        <v>5.351004960364772e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.351226792275014e-09</v>
+        <v>5.351226792274958e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.351023032904677e-09</v>
+        <v>5.3510230329047e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.351226792275014e-09</v>
+        <v>5.351226792274958e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.351226792275014e-09</v>
+        <v>5.351226792274958e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.351226792275014e-09</v>
+        <v>5.351226792274958e-09</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.117087738622508e-09</v>
+        <v>5.117087738622482e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.148635851756124e-09</v>
+        <v>8.148635851756135e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.777698280868102e-09</v>
+        <v>8.777698280868066e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.321446819108679e-09</v>
+        <v>7.321446819108683e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.213906152871073e-09</v>
+        <v>5.213906152871061e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.148787711558305e-09</v>
+        <v>8.148787711558267e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.149009543472358e-09</v>
+        <v>8.149009543472309e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.148805784098204e-09</v>
+        <v>8.148805784098182e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.149605403372252e-09</v>
+        <v>8.149605403372247e-09</v>
       </c>
       <c r="K6" t="n">
         <v>5.060768234472316e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.131610539418717e-08</v>
+        <v>1.131610539418714e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.769370372649363e-09</v>
+        <v>3.769370372649319e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.713821116367948e-09</v>
+        <v>4.713821116367924e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.716307044083002e-09</v>
+        <v>4.716307044082946e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.808845774181519e-09</v>
+        <v>5.808845774181506e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.716101403860399e-09</v>
+        <v>4.716101403860388e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.716083977640393e-09</v>
+        <v>4.71608397764037e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.71630580955062e-09</v>
+        <v>4.71630580955055e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.716102050180295e-09</v>
+        <v>4.71610205018026e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.71630580955062e-09</v>
+        <v>4.71630580955055e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.523944747150049e-09</v>
+        <v>4.167648217747187e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.71630580955062e-09</v>
+        <v>4.71630580955055e-09</v>
       </c>
     </row>
     <row r="8">
@@ -4319,13 +4319,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.1814704365592e-09</v>
+        <v>2.181470436559196e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.392255241093985e-10</v>
+        <v>9.392255241094004e-10</v>
       </c>
       <c r="D8" t="n">
-        <v>1.277913540657834e-09</v>
+        <v>1.277913540657842e-09</v>
       </c>
       <c r="E8" t="n">
         <v>1.22693997160444e-09</v>
@@ -4334,22 +4334,22 @@
         <v>1.22693997160444e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.253572058282467e-09</v>
+        <v>1.253572058282459e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.289945830037517e-09</v>
+        <v>1.289945830037511e-09</v>
       </c>
       <c r="I8" t="n">
         <v>1.22693997160444e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.509532778306467e-09</v>
+        <v>1.509532778306433e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.429502900515228e-09</v>
+        <v>2.429502900515277e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.265168072802822e-09</v>
+        <v>1.265168072802811e-09</v>
       </c>
     </row>
     <row r="9">
@@ -4359,34 +4359,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.185560100316316e-09</v>
+        <v>2.185560100316303e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>9.645150901928095e-10</v>
+        <v>9.645150901928102e-10</v>
       </c>
       <c r="D9" t="n">
-        <v>1.317195348931352e-09</v>
+        <v>1.31719534893137e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.267758912135931e-09</v>
+        <v>1.267758912135928e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.267758912135931e-09</v>
+        <v>1.267758912135928e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.28333683021601e-09</v>
+        <v>1.283336830215993e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.322170213057585e-09</v>
+        <v>1.32217021305758e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.267758912135931e-09</v>
+        <v>1.267758912135928e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.550283552549221e-09</v>
+        <v>1.55028355254921e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>2.438038745520403e-09</v>
+        <v>2.4380387455204e-09</v>
       </c>
       <c r="L9" t="n">
         <v>1.305937806456274e-09</v>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.495144453265473e-09</v>
+        <v>3.495144453265475e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.281277789411404e-09</v>
+        <v>5.281277789411396e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>6.645782238016201e-09</v>
+        <v>6.645782238016192e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.951332916584638e-09</v>
+        <v>6.951332916584697e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.951332916584638e-09</v>
+        <v>6.951332916584697e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.170464679596309e-09</v>
+        <v>6.170464679596012e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>6.841004302082351e-09</v>
+        <v>6.841004302082344e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.951332916584638e-09</v>
+        <v>6.951332916584697e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>7.803424262218742e-09</v>
+        <v>7.803424262218736e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>5.789481337305367e-09</v>
+        <v>5.789481337305359e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>7.728001760523218e-09</v>
+        <v>7.728001760523211e-09</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.353949350272423e-10</v>
+        <v>9.353949350272452e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.064064278539324e-10</v>
+        <v>9.064064278539278e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.353949350272423e-10</v>
+        <v>9.353949350272452e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.363508354878112e-10</v>
+        <v>9.363508354878133e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.363508354878069e-10</v>
+        <v>9.363508354878139e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.351336677108367e-10</v>
+        <v>9.351336677108416e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.353949350272423e-10</v>
+        <v>9.353949350272452e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.349337838304349e-10</v>
+        <v>9.349337838304369e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.353949350272423e-10</v>
+        <v>9.353949350272454e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.353949350272423e-10</v>
+        <v>9.353949350272452e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.353949350272423e-10</v>
+        <v>9.353949350272452e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.246427232398644e-09</v>
+        <v>1.43046428768795e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.422735494613977e-09</v>
+        <v>1.42273549461399e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.431716188173608e-09</v>
+        <v>1.431716188173602e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.409642801899614e-09</v>
+        <v>1.409642801899616e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.431311600043481e-09</v>
+        <v>1.431311600043478e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.246165965082228e-09</v>
+        <v>3.246165965082235e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.302898728896655e-09</v>
+        <v>3.30289872889666e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.430003136491151e-09</v>
+        <v>3.245966081201831e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.276889464119025e-09</v>
+        <v>1.484385096810358e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.430848471047858e-09</v>
+        <v>1.430848471047846e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.431295675939367e-09</v>
+        <v>1.431295675939364e-09</v>
       </c>
     </row>
     <row r="5">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.309366828890559e-09</v>
+        <v>5.309366828890561e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.306869780135852e-09</v>
+        <v>5.306869780135838e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.309202384116095e-09</v>
+        <v>5.309202384116091e-09</v>
       </c>
       <c r="E5" t="n">
         <v>5.310820677839048e-09</v>
@@ -4610,22 +4610,22 @@
         <v>5.310820677839048e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.309105561574156e-09</v>
+        <v>5.309105561574144e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.309366828890559e-09</v>
+        <v>5.309366828890561e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.308905677693756e-09</v>
+        <v>5.308905677693746e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.309366828890559e-09</v>
+        <v>5.309366828890561e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.309366828890559e-09</v>
+        <v>5.309366828890561e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.309366828890559e-09</v>
+        <v>5.309366828890561e-09</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.037312294426531e-09</v>
+        <v>5.037312294426537e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.015246047477813e-09</v>
+        <v>8.015246047477808e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.632589054432015e-09</v>
+        <v>8.632589054432016e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.202557300296453e-09</v>
+        <v>7.202557300296462e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.132483571364466e-09</v>
+        <v>5.132483571364464e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.014859749821774e-09</v>
+        <v>8.014859749821772e-09</v>
       </c>
       <c r="H6" t="n">
         <v>8.015121017143598e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.014659865941386e-09</v>
+        <v>8.014659865941378e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.015706242140431e-09</v>
+        <v>8.015706242140434e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.981997968569136e-09</v>
+        <v>4.981997968569132e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.112569122859033e-08</v>
+        <v>1.112569122859032e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.632901435527662e-09</v>
+        <v>3.632901435527647e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.538108037128017e-09</v>
+        <v>4.538108037127996e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.540606322169068e-09</v>
+        <v>4.540606322169065e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.58761503431811e-09</v>
+        <v>5.587615034318076e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.540143307463205e-09</v>
+        <v>4.540143307463168e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.540343818566327e-09</v>
+        <v>4.540343818566292e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.540605085882728e-09</v>
+        <v>4.540605085882691e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.540143934685931e-09</v>
+        <v>4.540143934685898e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.540605085882728e-09</v>
+        <v>4.540605085882691e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.993340991792252e-09</v>
+        <v>3.993340991792224e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.540605085882728e-09</v>
+        <v>4.540605085882691e-09</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.629259255118638e-09</v>
+        <v>2.629259255118627e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.201164891368348e-10</v>
+        <v>9.201164891368335e-10</v>
       </c>
       <c r="D8" t="n">
-        <v>1.247221209428617e-09</v>
+        <v>1.247221209428615e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.191261144268361e-09</v>
+        <v>1.191261144268362e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.191261144268361e-09</v>
+        <v>1.191261144268362e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.270951952282692e-09</v>
+        <v>1.270951952282686e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.257565705381464e-09</v>
+        <v>1.257565705381463e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.191261144268361e-09</v>
+        <v>1.191261144268362e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.458958246507116e-09</v>
+        <v>1.458958246507119e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.39604509628246e-09</v>
+        <v>2.396045096282397e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.233556463819081e-09</v>
+        <v>1.233556463819078e-09</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.628308112251936e-09</v>
+        <v>2.62830811225193e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>9.485670219659181e-10</v>
+        <v>9.485670219659152e-10</v>
       </c>
       <c r="D9" t="n">
-        <v>1.286083932851988e-09</v>
+        <v>1.286083932851987e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.234382991692254e-09</v>
+        <v>1.23438299169226e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.234382991692254e-09</v>
+        <v>1.234382991692259e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.301346109992286e-09</v>
+        <v>1.30134610999228e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.290371554585036e-09</v>
+        <v>1.290371554585038e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.234382991692254e-09</v>
+        <v>1.23438299169226e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.506430906449923e-09</v>
+        <v>1.50643090644992e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>2.404621036321193e-09</v>
+        <v>2.404621036321132e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.276122285234707e-09</v>
+        <v>1.276122285234704e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.101473451462513e-08</v>
+        <v>1.101473451462511e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>6.853647298683079e-09</v>
+        <v>6.853647298683094e-09</v>
       </c>
       <c r="D2" t="n">
         <v>1.381277346204406e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>6.853647298683079e-09</v>
+        <v>6.853647298683094e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.853647298683079e-09</v>
+        <v>6.853647298683094e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.129137082274693e-08</v>
+        <v>1.129137082274696e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.23215076466935e-08</v>
+        <v>2.232150764669355e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>6.853647298683079e-09</v>
+        <v>6.853647298683094e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.332866220391e-08</v>
+        <v>1.332866220390996e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>9.030268345176249e-09</v>
+        <v>9.030268345176376e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>9.329610129824352e-09</v>
+        <v>9.329610129824334e-09</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.930823170238284e-10</v>
+        <v>9.93082317023822e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.78666693977158e-10</v>
+        <v>9.786666939771496e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.930823170238284e-10</v>
+        <v>9.93082317023822e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.846504655696599e-10</v>
+        <v>9.84650465569653e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.846504655696597e-10</v>
+        <v>9.846504655696526e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.927575385396585e-10</v>
+        <v>9.927575385396529e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.930823170238284e-10</v>
+        <v>9.93082317023822e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.92222497000931e-10</v>
+        <v>9.922224970009281e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.930823170238284e-10</v>
+        <v>9.93082317023822e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.930823170238284e-10</v>
+        <v>9.93082317023822e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.930823170238284e-10</v>
+        <v>9.93082317023822e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.535421871413169e-09</v>
+        <v>3.535421871413165e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.53112999276367e-09</v>
+        <v>1.531129992763656e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.549548243154518e-09</v>
+        <v>1.549548243154511e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.509909517564117e-09</v>
+        <v>1.50990951756411e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.540598406190709e-09</v>
+        <v>1.540598406190696e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.541551822895732e-09</v>
+        <v>3.535097092928995e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.546464194285029e-09</v>
+        <v>3.520257057153982e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.534562051390279e-09</v>
+        <v>3.534562051390268e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.521883053075564e-09</v>
+        <v>3.521883053075561e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.539375661636954e-09</v>
+        <v>1.539375661636947e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.547856382972281e-09</v>
+        <v>1.547856382972275e-09</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.757294627112993e-09</v>
+        <v>5.757294627112985e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.756434807090106e-09</v>
+        <v>5.756434807090093e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.757110974900156e-09</v>
+        <v>5.757110974900148e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.756068266478774e-09</v>
+        <v>5.756068266478756e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.756068266478774e-09</v>
+        <v>5.756068266478756e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.756969848628818e-09</v>
+        <v>5.756969848628813e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.757294627112993e-09</v>
+        <v>5.757294627112985e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.756434807090106e-09</v>
+        <v>5.756434807090093e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.757294627112993e-09</v>
+        <v>5.757294627112985e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.757294627112993e-09</v>
+        <v>5.757294627112985e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.757294627112993e-09</v>
+        <v>5.757294627112985e-09</v>
       </c>
     </row>
     <row r="6">
@@ -5031,34 +5031,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.584007990192909e-09</v>
+        <v>5.584007990192902e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.895975921147032e-09</v>
+        <v>8.895975921147037e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.583131368149193e-09</v>
+        <v>9.583131368149201e-09</v>
       </c>
       <c r="E6" t="n">
         <v>7.98998813892372e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.688033768923438e-09</v>
+        <v>5.688033768923443e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.895980226090977e-09</v>
+        <v>8.89598022609097e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.896305004574973e-09</v>
+        <v>8.896305004574987e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.895445184552242e-09</v>
+        <v>8.895445184552231e-09</v>
       </c>
       <c r="J6" t="n">
         <v>8.896955966307307e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.5224803725781e-09</v>
+        <v>5.522480372578098e-09</v>
       </c>
       <c r="L6" t="n">
         <v>1.235627620629304e-08</v>
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.346336886626932e-09</v>
+        <v>4.346336886626913e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.444880649506697e-09</v>
+        <v>5.444880649506672e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.445741717930452e-09</v>
+        <v>5.445741717930445e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.713569005735531e-09</v>
+        <v>6.713569005735525e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.444879692828446e-09</v>
+        <v>5.444879692828423e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.445415691045424e-09</v>
+        <v>5.445415691045414e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.445740469529596e-09</v>
+        <v>5.445740469529578e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.444880649506697e-09</v>
+        <v>5.444880649506672e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.445740469529596e-09</v>
+        <v>5.445740469529578e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.808742240977427e-09</v>
+        <v>4.808742240977406e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.445740469529596e-09</v>
+        <v>5.445740469529578e-09</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.423185471034088e-09</v>
+        <v>1.423185471034087e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.418928486246938e-09</v>
+        <v>1.41892848624694e-09</v>
       </c>
       <c r="D8" t="n">
         <v>1.362628795209188e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.418928486246938e-09</v>
+        <v>1.41892848624694e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.418928486246938e-09</v>
+        <v>1.41892848624694e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.421838615044275e-09</v>
+        <v>1.421838615044276e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.221597100373153e-09</v>
+        <v>1.221597100373151e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.418928486246938e-09</v>
+        <v>1.41892848624694e-09</v>
       </c>
       <c r="J8" t="n">
         <v>1.389220931494068e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.473438069563376e-09</v>
+        <v>1.473438069563374e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.127354115636501e-09</v>
+        <v>1.484166449703356e-09</v>
       </c>
     </row>
     <row r="9">
@@ -5151,13 +5151,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.51355169143454e-09</v>
+        <v>1.513551691434541e-09</v>
       </c>
       <c r="C9" t="n">
         <v>1.45687986324337e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.488893914611514e-09</v>
+        <v>1.488893914611513e-09</v>
       </c>
       <c r="E9" t="n">
         <v>1.45687986324337e-09</v>
@@ -5169,7 +5169,7 @@
         <v>1.510772399689412e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.431807319583573e-09</v>
+        <v>1.431807319583571e-09</v>
       </c>
       <c r="I9" t="n">
         <v>1.45687986324337e-09</v>
@@ -5178,10 +5178,10 @@
         <v>1.499802239081158e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.534026475749546e-09</v>
+        <v>1.534026475749544e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.393426679981732e-09</v>
+        <v>1.538482529891008e-09</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.380211211204386e-09</v>
+        <v>9.380211211204419e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.900897499743551e-09</v>
+        <v>6.900897499743606e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.22300343824183e-08</v>
+        <v>1.223003438241825e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>6.900897499743551e-09</v>
+        <v>6.900897499743606e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.900897499743551e-09</v>
+        <v>6.900897499743606e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.027352818276184e-08</v>
+        <v>1.027352818276185e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.913675930521503e-08</v>
+        <v>1.913675930521508e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>6.900897499743551e-09</v>
+        <v>6.900897499743606e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.173060969205507e-08</v>
+        <v>1.17306096920551e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.273136371102347e-09</v>
+        <v>8.273136371102364e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>2.472467164908376e-08</v>
+        <v>9.912377694927943e-09</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.425468417385647e-10</v>
+        <v>9.425468417385676e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.310851116645513e-10</v>
+        <v>9.310851116645517e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.425468417385647e-10</v>
+        <v>9.42546841738568e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.365258185351341e-10</v>
+        <v>9.36525818535136e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.365258185351358e-10</v>
+        <v>9.36525818535136e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.422371764020314e-10</v>
+        <v>9.422371764020345e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.425468417385647e-10</v>
+        <v>9.42546841738568e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.41778587246313e-10</v>
+        <v>9.417785872463147e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.425468417385647e-10</v>
+        <v>9.42546841738568e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.425468417385647e-10</v>
+        <v>9.42546841738568e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.425468417385647e-10</v>
+        <v>9.42546841738568e-10</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.459664688196417e-09</v>
+        <v>3.30974991531642e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.451149041505952e-09</v>
+        <v>1.451149041505955e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.465672102711732e-09</v>
+        <v>1.465672102711748e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.431278736860141e-09</v>
+        <v>1.431278736860143e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.458760386650034e-09</v>
+        <v>1.458760386650036e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4593550228599e-09</v>
+        <v>3.309440249979892e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.295431769621103e-09</v>
+        <v>3.295431769621091e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.45889643370418e-09</v>
+        <v>3.308981660824171e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.514550050577646e-09</v>
+        <v>3.297880183245452e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.457408761090281e-09</v>
+        <v>1.457408761090282e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.464634569503709e-09</v>
+        <v>1.464634569503708e-09</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.338485865992404e-09</v>
+        <v>5.33848586599241e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.337717611500151e-09</v>
+        <v>5.337717611500157e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.338315065030533e-09</v>
+        <v>5.338315065030527e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.337751527476465e-09</v>
+        <v>5.337751527476476e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.337751527476465e-09</v>
+        <v>5.337751527476476e-09</v>
       </c>
       <c r="G5" t="n">
         <v>5.338176200655881e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.338485865992404e-09</v>
+        <v>5.33848586599241e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.337717611500151e-09</v>
+        <v>5.337717611500157e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.338485865992404e-09</v>
+        <v>5.33848586599241e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.338485865992404e-09</v>
+        <v>5.33848586599241e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.338485865992404e-09</v>
+        <v>5.33848586599241e-09</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.123834782635137e-09</v>
+        <v>5.123834782635132e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.142892389533996e-09</v>
+        <v>8.142892389538739e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.768827115064863e-09</v>
+        <v>8.768827115064865e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.317093071656049e-09</v>
+        <v>7.317093071656063e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.218885843936943e-09</v>
+        <v>5.218885843936941e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.142511049742988e-09</v>
+        <v>8.142511049742998e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.142820715079357e-09</v>
+        <v>8.142820715079343e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.142052460587292e-09</v>
+        <v>8.142052460587282e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.143414032715342e-09</v>
+        <v>8.143414032715347e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.067755568959107e-09</v>
+        <v>5.067755568959105e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.129640396537941e-08</v>
+        <v>1.129640396537939e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.896314631386435e-09</v>
+        <v>3.896314631386438e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.870092649809765e-09</v>
+        <v>4.870092649809766e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.870862068278725e-09</v>
+        <v>4.870862068278737e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.994698390621185e-09</v>
+        <v>5.994698390621172e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.870091812509683e-09</v>
+        <v>4.870091812509689e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.870551238965481e-09</v>
+        <v>4.870551238965486e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.870860904302043e-09</v>
+        <v>4.870860904302022e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.870092649809765e-09</v>
+        <v>4.870092649809766e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.870860904302043e-09</v>
+        <v>4.870860904302022e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.643732889129125e-09</v>
+        <v>3.643732889129126e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.870860904302043e-09</v>
+        <v>4.870860904302022e-09</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.417682539942866e-09</v>
+        <v>1.417682539942872e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.368348239295665e-09</v>
+        <v>1.36834823929567e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.345563676002932e-09</v>
+        <v>1.345563676002936e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.368348239295665e-09</v>
+        <v>1.36834823929567e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.368348239295665e-09</v>
+        <v>1.36834823929567e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.396205184191692e-09</v>
+        <v>1.396205184191691e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.228446395324645e-09</v>
+        <v>1.228446395324647e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.368348239295665e-09</v>
+        <v>1.36834823929567e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.375223794506484e-09</v>
+        <v>1.375223794506486e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.44079492906686e-09</v>
+        <v>1.440794929066863e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.12670353376905e-09</v>
+        <v>1.42619214656806e-09</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.493757613925074e-09</v>
+        <v>1.493757613925079e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.414980644552346e-09</v>
+        <v>1.414980644552351e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.464390277169332e-09</v>
+        <v>1.464390277169335e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.414980644552346e-09</v>
+        <v>1.414980644552351e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.414980644552346e-09</v>
+        <v>1.414980644552351e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.482862893110445e-09</v>
+        <v>1.482862893110446e-09</v>
       </c>
       <c r="H9" t="n">
         <v>1.417009536035571e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.414980644552346e-09</v>
+        <v>1.414980644552351e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.476542263263714e-09</v>
+        <v>1.476542263263717e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.503178481493664e-09</v>
+        <v>1.503178481493667e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.497337770184148e-09</v>
+        <v>1.497337770184147e-09</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.598844497403912e-09</v>
+        <v>8.598844497403865e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>8.145302718929337e-09</v>
+        <v>8.145302718929224e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.121235375938757e-08</v>
+        <v>1.121235375938746e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>8.145302718929337e-09</v>
+        <v>8.145302718929224e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>8.145302718929337e-09</v>
+        <v>8.145302718929224e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>9.79699728036868e-09</v>
+        <v>9.796997280368378e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.671491779419797e-08</v>
+        <v>1.671491779419799e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>8.145302718929337e-09</v>
+        <v>8.145302718929224e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.153208087326028e-08</v>
+        <v>1.153208087326022e-08</v>
       </c>
       <c r="K2" t="n">
         <v>7.994454124893979e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>2.311751243700481e-08</v>
+        <v>2.311751243700498e-08</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.407230793422956e-10</v>
+        <v>9.407230793422962e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.328142248181765e-10</v>
+        <v>9.328142248181691e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.407230793422956e-10</v>
+        <v>9.407230793422964e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.38043282979665e-10</v>
+        <v>9.380432829796608e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.380432829796662e-10</v>
+        <v>9.380432829796596e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.404723042726909e-10</v>
+        <v>9.404723042726923e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.407230793422956e-10</v>
+        <v>9.407230793422964e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.403284592562784e-10</v>
+        <v>9.403284592562722e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.407230793422956e-10</v>
+        <v>9.407230793422964e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.407230793422956e-10</v>
+        <v>9.407230793422964e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.407230793422956e-10</v>
+        <v>9.407230793422964e-10</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.463487955394789e-09</v>
+        <v>1.463487955394784e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.459001741029327e-09</v>
+        <v>1.459001741029317e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>3.30303722540792e-09</v>
+        <v>3.303037225407911e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.438916275775614e-09</v>
+        <v>1.438916275775603e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.464011635669833e-09</v>
+        <v>1.464011635669831e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.463237180325186e-09</v>
+        <v>1.463237180325177e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.293559597471218e-09</v>
+        <v>3.293559597471219e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.307360425365582e-09</v>
+        <v>3.307360425365574e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.296011067809981e-09</v>
+        <v>1.518435907015038e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.461313352282127e-09</v>
+        <v>1.461313352282115e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.46823569443202e-09</v>
+        <v>1.468235694432025e-09</v>
       </c>
     </row>
     <row r="5">
@@ -5786,34 +5786,34 @@
         <v>5.309595492065201e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.309200871979187e-09</v>
+        <v>5.309200871979172e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.309424814392327e-09</v>
+        <v>5.309424814392325e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.309783426183909e-09</v>
+        <v>5.309783426183899e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.309783426183909e-09</v>
+        <v>5.309783426183899e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.309344716995598e-09</v>
+        <v>5.309344716995591e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.309595492065201e-09</v>
+        <v>5.3095954920652e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.309200871979187e-09</v>
+        <v>5.309200871979172e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.309595492065201e-09</v>
+        <v>5.3095954920652e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.309595492065201e-09</v>
+        <v>5.3095954920652e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.309595492065201e-09</v>
+        <v>5.3095954920652e-09</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.060831220452809e-09</v>
+        <v>5.060831220452806e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.037696442601237e-09</v>
+        <v>8.037696442601222e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.653808104320989e-09</v>
+        <v>8.653808104320974e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.223624891715551e-09</v>
+        <v>7.223624891715533e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.155217496057265e-09</v>
+        <v>5.155217496057251e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.036484282406949e-09</v>
+        <v>8.036484282406926e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.036735057476429e-09</v>
+        <v>8.036735057476408e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.036340437390535e-09</v>
+        <v>8.036340437390513e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.037319908225602e-09</v>
+        <v>8.037319908225592e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.005552278819593e-09</v>
+        <v>5.005552278819584e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.114531545662373e-08</v>
+        <v>1.11453154566237e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5866,34 +5866,34 @@
         <v>3.768780050850842e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.70633369120548e-09</v>
+        <v>4.706333691205468e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.706729471722687e-09</v>
+        <v>4.706729471722695e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.788706160893239e-09</v>
+        <v>5.788706160893232e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.706332903884826e-09</v>
+        <v>4.70633290388479e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.706477536221899e-09</v>
+        <v>4.706477536221921e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.706728311291502e-09</v>
+        <v>4.706728311291498e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.70633369120548e-09</v>
+        <v>4.706333691205468e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.706728311291502e-09</v>
+        <v>4.706728311291498e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.163277893658082e-09</v>
+        <v>4.163277893658081e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.706728311291502e-09</v>
+        <v>4.706728311291498e-09</v>
       </c>
     </row>
     <row r="8">
@@ -5906,34 +5906,34 @@
         <v>1.415352266408604e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.31464999221038e-09</v>
+        <v>1.314649992210385e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.347245915813566e-09</v>
+        <v>1.347245915813567e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.31464999221038e-09</v>
+        <v>1.314649992210385e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.31464999221038e-09</v>
+        <v>1.314649992210385e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.386563972512627e-09</v>
+        <v>1.386563972512619e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.251517447324642e-09</v>
+        <v>1.251517447324646e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.31464999221038e-09</v>
+        <v>1.314649992210385e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.361443247782388e-09</v>
+        <v>1.361443247782389e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.424010718896222e-09</v>
+        <v>1.424010718896227e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.135776324504374e-09</v>
+        <v>1.135776324504385e-09</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.482090214844401e-09</v>
+        <v>1.482090214844402e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.38179001925694e-09</v>
+        <v>1.381790019256934e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.454356611796354e-09</v>
+        <v>1.454356611796357e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.38179001925694e-09</v>
+        <v>1.381790019256934e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.38179001925694e-09</v>
+        <v>1.381790019256934e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.468407054559341e-09</v>
+        <v>1.468407054559338e-09</v>
       </c>
       <c r="H9" t="n">
         <v>1.415649166044286e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.38179001925694e-09</v>
+        <v>1.381790019256934e-09</v>
       </c>
       <c r="J9" t="n">
         <v>1.460209412869921e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.485623991290846e-09</v>
+        <v>1.485623991290848e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.368542447036363e-09</v>
+        <v>1.368542447036366e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.570404830672463e-09</v>
+        <v>6.570404830672468e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.848210732924516e-09</v>
+        <v>5.848210732924517e-09</v>
       </c>
       <c r="D2" t="n">
         <v>7.584191329199376e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>5.848210732924516e-09</v>
+        <v>5.848210732924517e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>5.848210732924516e-09</v>
+        <v>5.848210732924517e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>7.393565098470078e-09</v>
+        <v>7.393565098470073e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.137243869540517e-08</v>
+        <v>1.137243869540512e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>5.848210732924516e-09</v>
+        <v>5.848210732924517e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.050430444598419e-08</v>
+        <v>1.050430444598417e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>7.072097318994639e-09</v>
+        <v>7.072097318994626e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>9.933853032675005e-09</v>
+        <v>1.179364329811337e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.106705180566696e-10</v>
+        <v>9.106705180566667e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.007370555923689e-10</v>
+        <v>9.007370555923696e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.106705180566696e-10</v>
+        <v>9.106705180566667e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.060849570192114e-10</v>
+        <v>9.060849570192093e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.060849570192114e-10</v>
+        <v>9.060849570192098e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.103857555599062e-10</v>
+        <v>9.103857555599055e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.106705180566696e-10</v>
+        <v>9.106705180566667e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.100461776541395e-10</v>
+        <v>9.100461776541378e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.106705180566696e-10</v>
+        <v>9.106705180566667e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.106705180566696e-10</v>
+        <v>9.106705180566667e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.106705180566696e-10</v>
+        <v>9.106705180566667e-10</v>
       </c>
     </row>
     <row r="4">
@@ -6142,34 +6142,34 @@
         <v>1.487857713889635e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.481866634426375e-09</v>
+        <v>1.481866634426377e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.48893907313058e-09</v>
+        <v>3.405910440140174e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.461534946544512e-09</v>
+        <v>1.461534946544503e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.48728871562499e-09</v>
+        <v>1.487288715624988e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.40792217277167e-09</v>
+        <v>1.487572951392869e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.394835467718053e-09</v>
+        <v>3.394835467718049e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.407582594865904e-09</v>
+        <v>1.487233373487106e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.398665507089393e-09</v>
+        <v>3.398665507089392e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.487521211613153e-09</v>
+        <v>1.487521211613154e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.489371005624557e-09</v>
+        <v>1.489371005624552e-09</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.455188182153095e-09</v>
+        <v>5.455188182153096e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.454563841750558e-09</v>
+        <v>5.454563841750564e-09</v>
       </c>
       <c r="D5" t="n">
         <v>5.455006898097646e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.454800976070645e-09</v>
+        <v>5.454800976070643e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.454800976070645e-09</v>
+        <v>5.454800976070643e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.454903419656327e-09</v>
+        <v>5.454903419656331e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.455188182153095e-09</v>
+        <v>5.455188182153096e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.454563841750558e-09</v>
+        <v>5.454563841750564e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.455188182153095e-09</v>
+        <v>5.455188182153096e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.455188182153095e-09</v>
+        <v>5.455188182153096e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.455188182153095e-09</v>
+        <v>5.455188182153096e-09</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.110903087599587e-09</v>
+        <v>5.110903087599596e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.132020707450616e-09</v>
+        <v>8.132020707445576e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.757957767805736e-09</v>
+        <v>8.757957767805758e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.305729245310633e-09</v>
+        <v>7.305729245310649e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.20627969203246e-09</v>
+        <v>5.206279692032468e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.131312408993378e-09</v>
+        <v>8.131312408993393e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.131597171489955e-09</v>
+        <v>8.131597171489976e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.130972831087616e-09</v>
+        <v>8.130972831087633e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.132190824830289e-09</v>
+        <v>8.132190824830299e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.054792144133318e-09</v>
+        <v>5.054792144133328e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.128696472881186e-08</v>
+        <v>1.128696472881188e-08</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.001859277686154e-09</v>
+        <v>4.001859277686147e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.009289846602157e-09</v>
+        <v>5.009289846602149e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.009915427239649e-09</v>
+        <v>5.009915427239651e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.17256402932517e-09</v>
+        <v>6.172564029325167e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.009289102953774e-09</v>
+        <v>5.009289102953772e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.009629424507919e-09</v>
+        <v>5.009629424507921e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.009914187004681e-09</v>
+        <v>5.009914187004682e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.009289846602157e-09</v>
+        <v>5.009289846602149e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.009914187004681e-09</v>
+        <v>5.009914187004682e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.740592797565556e-09</v>
+        <v>4.425843735246531e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.009914187004681e-09</v>
+        <v>5.009914187004682e-09</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.388788934226194e-09</v>
+        <v>1.388788934226193e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.276208437445065e-09</v>
+        <v>1.276208437445066e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.363158587700932e-09</v>
+        <v>1.363158587700931e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.276208437445065e-09</v>
+        <v>1.276208437445066e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.276208437445065e-09</v>
+        <v>1.276208437445066e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.368051224418417e-09</v>
+        <v>1.368051224418416e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.29312646891179e-09</v>
+        <v>1.293126468911789e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.276208437445065e-09</v>
+        <v>1.276208437445066e-09</v>
       </c>
       <c r="J8" t="n">
         <v>1.310728496082799e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.375512556690361e-09</v>
+        <v>1.37551255669036e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.299070701751221e-09</v>
+        <v>1.330719999445027e-09</v>
       </c>
     </row>
     <row r="9">
@@ -6339,13 +6339,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.419238245774821e-09</v>
+        <v>1.41923824577482e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.302704947661885e-09</v>
+        <v>1.302704947661884e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.408802047750967e-09</v>
+        <v>1.408802047750966e-09</v>
       </c>
       <c r="E9" t="n">
         <v>1.302704947661885e-09</v>
@@ -6354,22 +6354,22 @@
         <v>1.302704947661885e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.408819660954061e-09</v>
+        <v>1.40881966095406e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.380441151711126e-09</v>
+        <v>1.380441151711125e-09</v>
       </c>
       <c r="I9" t="n">
         <v>1.302704947661885e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.387505865569279e-09</v>
+        <v>1.387505865569277e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.413835927532801e-09</v>
+        <v>1.413835927532799e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.395691862211449e-09</v>
+        <v>1.382826704839093e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.347435497817492e-09</v>
+        <v>7.347435497817498e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.012131700272438e-09</v>
+        <v>6.012131700272437e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>6.015556132479081e-09</v>
+        <v>6.015556132479079e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.012131700272438e-09</v>
+        <v>6.012131700272437e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.012131700272438e-09</v>
+        <v>6.012131700272437e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.67641976553293e-09</v>
+        <v>6.676419765532833e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>7.121060643710497e-09</v>
+        <v>7.121060643710504e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.012131700272438e-09</v>
+        <v>6.012131700272437e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.015965757438823e-08</v>
+        <v>1.015965757438822e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>6.869527301634647e-09</v>
+        <v>6.869527301634659e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>8.030860130898663e-09</v>
+        <v>8.030860130898668e-09</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.601473025955875e-10</v>
+        <v>8.601473025955889e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>8.517652847245458e-10</v>
+        <v>8.517652847245444e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>8.601473025955875e-10</v>
+        <v>8.601473025955889e-10</v>
       </c>
       <c r="E3" t="n">
         <v>8.566161372054138e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>8.566161372054138e-10</v>
+        <v>8.566161372054169e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>8.598692079781944e-10</v>
+        <v>8.598692079781933e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>8.601473025955875e-10</v>
+        <v>8.601473025955889e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>8.595594228275318e-10</v>
+        <v>8.595594228275291e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>8.601473025955875e-10</v>
+        <v>8.601473025955889e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.601473025955875e-10</v>
+        <v>8.601473025955889e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>8.601473025955875e-10</v>
+        <v>8.601473025955889e-10</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.405208041229697e-09</v>
+        <v>3.185320325867273e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.400861165107999e-09</v>
+        <v>1.400861165107994e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.403551340945974e-09</v>
+        <v>1.40355256478915e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.381722254182329e-09</v>
+        <v>1.381722254182328e-09</v>
       </c>
       <c r="F4" t="n">
         <v>1.404794071737695e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4049299466123e-09</v>
+        <v>1.404929946612301e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.172447350679316e-09</v>
+        <v>1.40539232021581e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.404620161461642e-09</v>
+        <v>1.404620161461638e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.457932722418231e-09</v>
+        <v>3.176517474915609e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.405562978516037e-09</v>
+        <v>1.405562978516041e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.405321404439287e-09</v>
+        <v>1.405321404439292e-09</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.037489194300487e-09</v>
+        <v>5.037489194300491e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.036901314532421e-09</v>
+        <v>5.036901314532426e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.037321305201703e-09</v>
+        <v>5.037321305201708e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.037183481085586e-09</v>
+        <v>5.037183481085591e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.037183481085586e-09</v>
+        <v>5.037183481085591e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.037211099683086e-09</v>
+        <v>5.03721109968309e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.037489194300487e-09</v>
+        <v>5.037489194300491e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.036901314532421e-09</v>
+        <v>5.036901314532426e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.037489194300487e-09</v>
+        <v>5.037489194300491e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.037489194300487e-09</v>
+        <v>5.037489194300491e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.037489194300487e-09</v>
+        <v>5.037489194300491e-09</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.643190494798045e-09</v>
+        <v>4.643190494798038e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>7.367669370660268e-09</v>
+        <v>7.367669370660267e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>7.932091124219611e-09</v>
+        <v>7.932091124219602e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>6.62251404487045e-09</v>
+        <v>6.622514044870445e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>4.729219302974461e-09</v>
+        <v>4.729219302974456e-09</v>
       </c>
       <c r="G6" t="n">
         <v>7.366963324814134e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>7.36724141943148e-09</v>
+        <v>7.367241419431472e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>7.366653539663473e-09</v>
+        <v>7.366653539663472e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>7.367776773824945e-09</v>
+        <v>7.367776773824939e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.592589850317395e-09</v>
+        <v>4.592589850317399e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.021274039195009e-08</v>
+        <v>1.021274039195008e-08</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.560490435941794e-09</v>
+        <v>3.560490435941787e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.446128035980266e-09</v>
+        <v>4.446128035980267e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.446717093275627e-09</v>
+        <v>4.446717093275618e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.468813759886129e-09</v>
+        <v>5.468813759886125e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.44612743339185e-09</v>
+        <v>4.446127433391847e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.446437821130925e-09</v>
+        <v>4.446437821130924e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.446715915748325e-09</v>
+        <v>4.446715915748302e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.446128035980266e-09</v>
+        <v>4.446128035980267e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.446715915748325e-09</v>
+        <v>4.446715915748302e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.912401225252593e-09</v>
+        <v>3.912401225252592e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.446715915748325e-09</v>
+        <v>4.446715915748302e-09</v>
       </c>
     </row>
     <row r="8">
@@ -6698,25 +6698,25 @@
         <v>1.311667000227151e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.203387045452728e-09</v>
+        <v>1.203387045452729e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.345059913488605e-09</v>
+        <v>1.345059913488606e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.203387045452728e-09</v>
+        <v>1.203387045452729e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.203387045452728e-09</v>
+        <v>1.203387045452729e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.325857018975627e-09</v>
+        <v>1.325857018975628e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.328979862143124e-09</v>
+        <v>1.328979862143125e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.203387045452728e-09</v>
+        <v>1.203387045452729e-09</v>
       </c>
       <c r="J8" t="n">
         <v>1.248114434309938e-09</v>
@@ -6725,7 +6725,7 @@
         <v>1.320598924000407e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.324346814460174e-09</v>
+        <v>1.324346814460175e-09</v>
       </c>
     </row>
     <row r="9">
@@ -6741,7 +6741,7 @@
         <v>1.239894765619185e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.374475892327362e-09</v>
+        <v>1.374475892327363e-09</v>
       </c>
       <c r="E9" t="n">
         <v>1.239894765619185e-09</v>
@@ -6753,19 +6753,19 @@
         <v>1.364766345641332e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.368013279188238e-09</v>
+        <v>1.368013279188237e-09</v>
       </c>
       <c r="I9" t="n">
         <v>1.239894765619185e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.335055725170114e-09</v>
+        <v>1.335055725170115e-09</v>
       </c>
       <c r="K9" t="n">
         <v>1.364516468391879e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.359420037873463e-09</v>
+        <v>1.366113100484593e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.553317424277737e-09</v>
+        <v>8.553317424277744e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.426897077150888e-09</v>
+        <v>6.426897077150781e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>7.004890094333768e-09</v>
+        <v>7.004890094333788e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.426897077150888e-09</v>
+        <v>6.426897077150781e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.426897077150888e-09</v>
+        <v>6.426897077150781e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.954894526542535e-09</v>
+        <v>6.954894526542683e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>6.827707042570474e-09</v>
+        <v>6.827707042570495e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.426897077150888e-09</v>
+        <v>6.426897077150781e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.613205313803438e-08</v>
+        <v>1.61320531380344e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>6.912919018147353e-09</v>
+        <v>6.912919018147376e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>8.501013462827432e-09</v>
+        <v>8.505424767682648e-09</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.620602495948483e-10</v>
+        <v>8.620602495948456e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>8.536909855137632e-10</v>
+        <v>8.536909855137682e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>8.620602495948483e-10</v>
+        <v>8.62060249594846e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>8.585912532506714e-10</v>
+        <v>8.585912532506783e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>8.585912532506718e-10</v>
+        <v>8.585912532506765e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>8.617839990864741e-10</v>
+        <v>8.617839990864914e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>8.620602495948483e-10</v>
+        <v>8.620602495948456e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>8.614841087556066e-10</v>
+        <v>8.61484108755614e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>8.620602495948483e-10</v>
+        <v>8.620602495948456e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.620602495948483e-10</v>
+        <v>8.620602495948456e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>8.620602495948483e-10</v>
+        <v>8.620602495948456e-10</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.411368583125169e-09</v>
+        <v>1.411368583125157e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.40675818969704e-09</v>
+        <v>1.406758189697051e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>3.189331933406974e-09</v>
+        <v>1.410656528894222e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.387207094455313e-09</v>
+        <v>1.387207094455315e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.410742716425337e-09</v>
+        <v>1.410742716425347e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.411092332616781e-09</v>
+        <v>3.197718966845463e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.179033833538827e-09</v>
+        <v>3.179033833538839e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.410792442285921e-09</v>
+        <v>1.410792442285928e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.465911524520899e-09</v>
+        <v>3.182693108105705e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.410820629802014e-09</v>
+        <v>1.410820629802003e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.411323379571548e-09</v>
+        <v>1.411323379571556e-09</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.029058383225544e-09</v>
+        <v>5.029058383225577e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.028482242386338e-09</v>
+        <v>5.02848224238635e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.028890831340978e-09</v>
+        <v>5.028890831340988e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.028754520436616e-09</v>
+        <v>5.028754520436626e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.028754520436616e-09</v>
+        <v>5.028754520436626e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.028782132717224e-09</v>
+        <v>5.028782132717225e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.029058383225544e-09</v>
+        <v>5.029058383225577e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.028482242386338e-09</v>
+        <v>5.02848224238635e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.029058383225544e-09</v>
+        <v>5.029058383225577e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.029058383225544e-09</v>
+        <v>5.029058383225577e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.029058383225544e-09</v>
+        <v>5.029058383225577e-09</v>
       </c>
     </row>
     <row r="6">
@@ -7011,34 +7011,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.613445911800366e-09</v>
+        <v>4.613445911800363e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>7.318112502375045e-09</v>
+        <v>7.318112502379549e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>7.878428503424379e-09</v>
+        <v>7.878428503424381e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>6.578376648079265e-09</v>
+        <v>6.578376648079266e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>4.698852404352967e-09</v>
+        <v>4.698852404352971e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>7.317410333103646e-09</v>
+        <v>7.31741033310364e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>7.317686583612061e-09</v>
+        <v>7.31768658361207e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>7.317110442772749e-09</v>
+        <v>7.317110442772772e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>7.3182180447074e-09</v>
+        <v>7.318218044707382e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.563213252937943e-09</v>
+        <v>4.563213252937934e-09</v>
       </c>
       <c r="L6" t="n">
         <v>1.014249209053686e-08</v>
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.467244637906384e-09</v>
+        <v>3.467244637906399e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.32670990917757e-09</v>
+        <v>4.32670990917759e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.327287228830743e-09</v>
+        <v>4.327287228830757e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.319179818302156e-09</v>
+        <v>5.319179818302171e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.326709340977179e-09</v>
+        <v>4.326709340977197e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.327009799508442e-09</v>
+        <v>4.327009799508461e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.327286050016805e-09</v>
+        <v>4.32728605001682e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.32670990917757e-09</v>
+        <v>4.32670990917759e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.327286050016805e-09</v>
+        <v>4.32728605001682e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.828975174001422e-09</v>
+        <v>3.808758024474616e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.327286050016805e-09</v>
+        <v>4.32728605001682e-09</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.274900263501115e-09</v>
+        <v>1.274900263501113e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.18688075641579e-09</v>
+        <v>1.186880756415793e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.313917388480348e-09</v>
+        <v>1.313917388480347e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.18688075641579e-09</v>
+        <v>1.186880756415793e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.18688075641579e-09</v>
+        <v>1.186880756415793e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.314839008953781e-09</v>
+        <v>1.31483900895377e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.334425624792734e-09</v>
+        <v>1.334425624792733e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.18688075641579e-09</v>
+        <v>1.186880756415793e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.099834440508999e-09</v>
+        <v>1.099834440508997e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.312814175920206e-09</v>
+        <v>1.312814175920208e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.293125482811895e-09</v>
+        <v>1.293125482811893e-09</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.343066501276005e-09</v>
+        <v>1.343066501276012e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.229650028178487e-09</v>
+        <v>1.22965002817849e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.358960745372567e-09</v>
+        <v>1.358960745372562e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.229650028178487e-09</v>
+        <v>1.22965002817849e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.229650028178487e-09</v>
+        <v>1.22965002817849e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.357464792664209e-09</v>
+        <v>1.357464792664213e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.367389947168213e-09</v>
+        <v>1.367389947168221e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.229650028178487e-09</v>
+        <v>1.22965002817849e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.271885226269431e-09</v>
+        <v>1.271885226269437e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.358514250827943e-09</v>
+        <v>1.358514250827935e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.350583799316585e-09</v>
+        <v>1.354185219923354e-09</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.597917580912214e-09</v>
+        <v>8.597917580912217e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.356666149219431e-09</v>
+        <v>6.356666149219436e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.29485699755622e-08</v>
+        <v>1.294856997556221e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>6.356666149219431e-09</v>
+        <v>6.356666149219436e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.356666149219431e-09</v>
+        <v>6.356666149219436e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.023044399017444e-08</v>
+        <v>1.023044399017442e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.065504370980239e-08</v>
+        <v>2.065504370980245e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>6.356666149219431e-09</v>
+        <v>6.356666149219436e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.065258088624607e-08</v>
+        <v>1.065258088624609e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.360451809732599e-09</v>
+        <v>8.360451809732614e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>2.471262416274975e-08</v>
+        <v>2.471262416274977e-08</v>
       </c>
     </row>
     <row r="3">
@@ -7290,25 +7290,25 @@
         <v>9.406313779379868e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.27295290080932e-10</v>
+        <v>9.272952900809384e-10</v>
       </c>
       <c r="D3" t="n">
         <v>9.406313779379868e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.329724035928969e-10</v>
+        <v>9.329724035929008e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.329724035928965e-10</v>
+        <v>9.329724035929008e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.402801333375641e-10</v>
+        <v>9.402801333375674e-10</v>
       </c>
       <c r="H3" t="n">
         <v>9.406313779379868e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.395895611911537e-10</v>
+        <v>9.395895611911638e-10</v>
       </c>
       <c r="J3" t="n">
         <v>9.406313779379868e-10</v>
@@ -7330,31 +7330,31 @@
         <v>1.51128155081565e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.501280118649929e-09</v>
+        <v>1.501280118649932e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.519622197432525e-09</v>
+        <v>1.519622197432531e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.480665441564901e-09</v>
+        <v>1.480665441564897e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.509919980234179e-09</v>
+        <v>1.509919980234178e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.463886672827488e-09</v>
+        <v>3.463886672827494e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.453507079978693e-09</v>
+        <v>3.453507079978694e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.510239734068818e-09</v>
+        <v>3.463196100681085e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.455094126721476e-09</v>
+        <v>3.455094126721479e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.50935181385907e-09</v>
+        <v>1.509351813859069e-09</v>
       </c>
       <c r="L4" t="n">
         <v>1.516482586225136e-09</v>
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.56359078200253e-09</v>
+        <v>5.563590782002523e-09</v>
       </c>
       <c r="C5" t="n">
         <v>5.5625489652557e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.563408795221241e-09</v>
+        <v>5.563408795221247e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.562408691447824e-09</v>
+        <v>5.562408691447833e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.562408691447824e-09</v>
+        <v>5.562408691447833e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.563239537402106e-09</v>
+        <v>5.563239537402105e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.56359078200253e-09</v>
+        <v>5.563590782002523e-09</v>
       </c>
       <c r="I5" t="n">
         <v>5.5625489652557e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.56359078200253e-09</v>
+        <v>5.563590782002523e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.56359078200253e-09</v>
+        <v>5.563590782002523e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.56359078200253e-09</v>
+        <v>5.563590782002523e-09</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.283311943157419e-09</v>
+        <v>5.283311943157422e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.409341001262372e-09</v>
+        <v>8.409341001267289e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.057945870735308e-09</v>
+        <v>9.0579458707353e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.554186148493186e-09</v>
+        <v>7.554186148493208e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.381395868467268e-09</v>
+        <v>5.381395868467289e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.40932303026724e-09</v>
+        <v>8.40932303026725e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.409674274867566e-09</v>
+        <v>8.409674274867564e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.408632458120828e-09</v>
+        <v>8.408632458120854e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.410288695070841e-09</v>
+        <v>8.410288695070857e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.225238157735415e-09</v>
+        <v>5.225238157735419e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.167542115289559e-08</v>
+        <v>1.16754211528956e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.159734629251736e-09</v>
+        <v>4.159734629251731e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.208720925908715e-09</v>
+        <v>5.208720925908724e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.209763945250737e-09</v>
+        <v>5.209763945250743e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.42043106086644e-09</v>
+        <v>6.420431060866442e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.20872002123755e-09</v>
+        <v>5.208720021237565e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.209411498055117e-09</v>
+        <v>5.209411498055123e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.209762742655542e-09</v>
+        <v>5.209762742655547e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.208720925908715e-09</v>
+        <v>5.208720925908724e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.209762742655542e-09</v>
+        <v>5.209762742655547e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.576689639953352e-09</v>
+        <v>4.601372835777751e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.209762742655542e-09</v>
+        <v>5.209762742655547e-09</v>
       </c>
     </row>
     <row r="8">
@@ -7487,13 +7487,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.39279253365358e-09</v>
+        <v>1.392792533653582e-09</v>
       </c>
       <c r="C8" t="n">
         <v>1.324024674877777e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.287400498660908e-09</v>
+        <v>1.28740049866091e-09</v>
       </c>
       <c r="E8" t="n">
         <v>1.324024674877777e-09</v>
@@ -7505,7 +7505,7 @@
         <v>1.355301707001609e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.141061408923659e-09</v>
+        <v>1.141061408923658e-09</v>
       </c>
       <c r="I8" t="n">
         <v>1.324024674877777e-09</v>
@@ -7517,7 +7517,7 @@
         <v>1.399500869719535e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.405105246089272e-09</v>
+        <v>1.10206968320755e-09</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.45098171752348e-09</v>
+        <v>1.450981717523481e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.356671716266517e-09</v>
+        <v>1.356671716266518e-09</v>
       </c>
       <c r="D9" t="n">
         <v>1.408062479637661e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.356671716266517e-09</v>
+        <v>1.356671716266518e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.356671716266517e-09</v>
+        <v>1.356671716266518e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.433519592526356e-09</v>
+        <v>1.433519592526357e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.34880879302189e-09</v>
+        <v>1.348808793021888e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.356671716266517e-09</v>
+        <v>1.356671716266518e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.437641934362957e-09</v>
+        <v>1.437641934362958e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.453720525760198e-09</v>
+        <v>1.453720525760199e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.456084587831942e-09</v>
+        <v>1.332890855275442e-09</v>
       </c>
     </row>
   </sheetData>
@@ -7643,13 +7643,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.248213695147273e-09</v>
+        <v>6.248213695147272e-09</v>
       </c>
       <c r="C2" t="n">
         <v>5.819080754183032e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.033193532371116e-08</v>
+        <v>1.033193532371123e-08</v>
       </c>
       <c r="E2" t="n">
         <v>5.819080754183032e-09</v>
@@ -7658,10 +7658,10 @@
         <v>5.819080754183032e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>8.117709364201059e-09</v>
+        <v>8.117709364201066e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>8.721624143015249e-09</v>
+        <v>8.721624143015253e-09</v>
       </c>
       <c r="I2" t="n">
         <v>5.819080754183032e-09</v>
@@ -7670,10 +7670,10 @@
         <v>1.004544491927911e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>6.236037803633794e-09</v>
+        <v>6.236037803633789e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.710183516096661e-08</v>
+        <v>7.781803818142619e-09</v>
       </c>
     </row>
     <row r="3">
@@ -7686,25 +7686,25 @@
         <v>8.920599877769784e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>8.815651158420045e-10</v>
+        <v>8.81565115841999e-10</v>
       </c>
       <c r="D3" t="n">
         <v>8.920599877769784e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>8.867013217318467e-10</v>
+        <v>8.867013217318458e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>8.867013217318467e-10</v>
+        <v>8.867013217318449e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>8.917484838256822e-10</v>
+        <v>8.917484838256802e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>8.920599877769776e-10</v>
+        <v>8.920599877769784e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>8.912684870594401e-10</v>
+        <v>8.912684870594381e-10</v>
       </c>
       <c r="J3" t="n">
         <v>8.920599877769784e-10</v>
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.423938052722706e-09</v>
+        <v>3.232269680318497e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.416946451560687e-09</v>
+        <v>1.416946451560688e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.430386041186657e-09</v>
+        <v>1.430386041186545e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.397690665126007e-09</v>
+        <v>1.397690665126002e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.423102363964708e-09</v>
+        <v>1.4231023639647e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.231958176367204e-09</v>
+        <v>1.423626548771411e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.21914876960137e-09</v>
+        <v>3.219148769601369e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.231478179600956e-09</v>
+        <v>3.231478179600947e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.223492842687221e-09</v>
+        <v>1.47739933693144e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.421098641356744e-09</v>
+        <v>1.421098641356747e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.427099148197768e-09</v>
+        <v>1.427099148197763e-09</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.160309928643384e-09</v>
+        <v>5.160309928643388e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.159518427925847e-09</v>
+        <v>5.159518427925851e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.16014080223011e-09</v>
+        <v>5.160140802230102e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.159627816491219e-09</v>
+        <v>5.159627816491229e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.159627816491219e-09</v>
+        <v>5.159627816491229e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.159998424692095e-09</v>
+        <v>5.159998424692098e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.160309928643384e-09</v>
+        <v>5.160309928643388e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.159518427925847e-09</v>
+        <v>5.159518427925851e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.160309928643384e-09</v>
+        <v>5.160309928643388e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.160309928643384e-09</v>
+        <v>5.160309928643388e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.160309928643384e-09</v>
+        <v>5.160309928643388e-09</v>
       </c>
     </row>
     <row r="6">
@@ -7803,34 +7803,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.845530689472127e-09</v>
+        <v>4.845530689472128e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>7.695058352766724e-09</v>
+        <v>7.695058352771295e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.285823552549463e-09</v>
+        <v>8.28582355254944e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>6.915624095814385e-09</v>
+        <v>6.915624095814378e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>4.935228260994259e-09</v>
+        <v>4.935228260994251e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>7.694661601274363e-09</v>
+        <v>7.694661601274359e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>7.694973105225475e-09</v>
+        <v>7.694973105225479e-09</v>
       </c>
       <c r="I6" t="n">
         <v>7.694181604508114e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>7.695533102670374e-09</v>
+        <v>7.695533102670372e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.792600833665173e-09</v>
+        <v>4.792600833665174e-09</v>
       </c>
       <c r="L6" t="n">
         <v>1.067145397531364e-08</v>
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.702402247060124e-09</v>
+        <v>3.702402247060112e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.625701506239018e-09</v>
+        <v>4.625701506239002e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.626494220708574e-09</v>
+        <v>4.626494220708582e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.692082916181949e-09</v>
+        <v>5.69208291618194e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.625700842003042e-09</v>
+        <v>4.625700842003031e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.626181503005254e-09</v>
+        <v>4.626181503005251e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.626493006956554e-09</v>
+        <v>4.626493006956548e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.625701506239018e-09</v>
+        <v>4.625701506239002e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.626493006956554e-09</v>
+        <v>4.626493006956548e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.091071701987582e-09</v>
+        <v>3.462897476051301e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.626493006956554e-09</v>
+        <v>4.626493006956548e-09</v>
       </c>
     </row>
     <row r="8">
@@ -7883,28 +7883,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.407094104488714e-09</v>
+        <v>1.407094104488715e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.29054131136013e-09</v>
+        <v>1.290541311360127e-09</v>
       </c>
       <c r="D8" t="n">
         <v>1.295277051929484e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.29054131136013e-09</v>
+        <v>1.290541311360127e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.29054131136013e-09</v>
+        <v>1.290541311360127e-09</v>
       </c>
       <c r="G8" t="n">
         <v>1.357029948268145e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.360016327264189e-09</v>
+        <v>1.360016327264188e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.29054131136013e-09</v>
+        <v>1.290541311360127e-09</v>
       </c>
       <c r="J8" t="n">
         <v>1.325716277731283e-09</v>
@@ -7913,7 +7913,7 @@
         <v>1.405459764023224e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.383731227085436e-09</v>
+        <v>1.18925167827763e-09</v>
       </c>
     </row>
     <row r="9">
@@ -7926,34 +7926,34 @@
         <v>1.438507555870309e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.32212388524419e-09</v>
+        <v>1.322123885244188e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.392970399765487e-09</v>
+        <v>1.392970399765484e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.32212388524419e-09</v>
+        <v>1.322123885244188e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.32212388524419e-09</v>
+        <v>1.322123885244188e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.416053622678656e-09</v>
+        <v>1.416053622678657e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.419455308071967e-09</v>
+        <v>1.419455308071966e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.32212388524419e-09</v>
+        <v>1.322123885244188e-09</v>
       </c>
       <c r="J9" t="n">
         <v>1.405426045875273e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.437846454203286e-09</v>
+        <v>1.437846454203287e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.42907230224581e-09</v>
+        <v>1.350010399610464e-09</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen human toxicity carcinogenic results.xlsx
+++ b/Results/Hydrogen/hydrogen human toxicity carcinogenic results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.299546510563524e-08</v>
+        <v>1.29954651056357e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>8.580419078195497e-09</v>
+        <v>8.58041907819554e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.509441795517441e-08</v>
+        <v>1.50944179551744e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>8.580419078195497e-09</v>
+        <v>8.58041907819554e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>8.580419078195497e-09</v>
+        <v>8.58041907819554e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.246447976248571e-08</v>
+        <v>1.246447976248566e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.565290456453549e-08</v>
+        <v>2.565290456453527e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>8.580419078195497e-09</v>
+        <v>8.58041907819554e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.367320129959203e-08</v>
+        <v>1.367320129959212e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.055521772573474e-08</v>
+        <v>1.055521772573471e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.090040074072369e-08</v>
+        <v>3.056744720014586e-08</v>
       </c>
     </row>
     <row r="3">
@@ -564,19 +564,19 @@
         <v>1.066905063684551e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>1.059234533997173e-09</v>
+        <v>1.05923453399717e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.059234533997169e-09</v>
+        <v>1.05923453399717e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.066635895851769e-09</v>
+        <v>1.066635895851772e-09</v>
       </c>
       <c r="H3" t="n">
         <v>1.066905063684551e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>1.066408517584701e-09</v>
+        <v>1.0664085175847e-09</v>
       </c>
       <c r="J3" t="n">
         <v>1.066905063684551e-09</v>
@@ -598,34 +598,34 @@
         <v>1.642253693357425e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.632858079981069e-09</v>
+        <v>1.632858079981056e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.649378816961288e-09</v>
+        <v>1.649377298367111e-09</v>
       </c>
       <c r="E4" t="n">
         <v>1.609866355836165e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.641813903005798e-09</v>
+        <v>1.641813903005797e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.789572712620436e-09</v>
+        <v>3.789572712620438e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.773948477211241e-09</v>
+        <v>3.773948477211244e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.641757147257575e-09</v>
+        <v>3.789345334353367e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.706311851253122e-09</v>
+        <v>3.77499515234612e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.640430573383067e-09</v>
+        <v>1.640430573383064e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.648814904429585e-09</v>
+        <v>1.648814904429587e-09</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.234532964107388e-09</v>
+        <v>6.234532964107402e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>6.234036418007548e-09</v>
+        <v>6.234036418007556e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>6.234335687057964e-09</v>
+        <v>6.234335687057969e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>6.233754290479969e-09</v>
+        <v>6.233754290479973e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>6.233754290479969e-09</v>
+        <v>6.233754290479973e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>6.234263796274608e-09</v>
+        <v>6.234263796274615e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>6.234532964107388e-09</v>
+        <v>6.234532964107402e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>6.234036418007548e-09</v>
+        <v>6.234036418007556e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>6.234532964107388e-09</v>
+        <v>6.234532964107402e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>6.234532964107388e-09</v>
+        <v>6.234532964107402e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>6.234532964107388e-09</v>
+        <v>6.234532964107402e-09</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.111760113646136e-09</v>
+        <v>6.111760113646131e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>9.754950721179241e-09</v>
+        <v>9.754950721184343e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.051015225595225e-08</v>
+        <v>1.051015225595222e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>8.758499611803911e-09</v>
+        <v>8.758499611803896e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>6.226690224070032e-09</v>
+        <v>6.226690224070021e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>9.754484618213572e-09</v>
+        <v>9.754484618213559e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>9.754753786046348e-09</v>
+        <v>9.754753786046328e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>9.754257239946504e-09</v>
+        <v>9.754257239946479e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>9.755469739210855e-09</v>
+        <v>9.75546973921084e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>6.044089635823462e-09</v>
+        <v>6.04408963582346e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.356016529952759e-08</v>
+        <v>1.356016529952757e-08</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.933311445719947e-09</v>
+        <v>4.933311445719954e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>6.192533572008003e-09</v>
+        <v>6.19253357200799e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>6.19303143904304e-09</v>
+        <v>6.193031439043045e-09</v>
       </c>
       <c r="E7" t="n">
         <v>7.646222081669607e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>6.192532514390753e-09</v>
+        <v>6.192532514390761e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>6.192760950275076e-09</v>
+        <v>6.192760950275061e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>6.193030118107848e-09</v>
+        <v>6.193030118107843e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>6.192533572008003e-09</v>
+        <v>6.19253357200799e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>6.193030118107848e-09</v>
+        <v>6.193030118107843e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>5.463144727609648e-09</v>
+        <v>4.606819108225801e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>6.193030118107848e-09</v>
+        <v>6.193030118107843e-09</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.449147922548444e-09</v>
+        <v>1.449147922548417e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.458616191296106e-09</v>
+        <v>1.458616191296102e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.409388575243884e-09</v>
+        <v>1.40938857524388e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.458616191296106e-09</v>
+        <v>1.458616191296102e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.458616191296106e-09</v>
+        <v>1.458616191296102e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.466925974400105e-09</v>
+        <v>1.466925974400101e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.241408949265437e-09</v>
+        <v>1.241408949265444e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.458616191296106e-09</v>
+        <v>1.458616191296102e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.45286952423194e-09</v>
+        <v>1.452869524231939e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.506841466777256e-09</v>
+        <v>1.506841466777264e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.518345503244036e-09</v>
+        <v>1.518345503244035e-09</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.554380129104455e-09</v>
+        <v>1.554380129104461e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.511356355991734e-09</v>
+        <v>1.511356355991733e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.538193117392924e-09</v>
+        <v>1.538193117392921e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.511356355991734e-09</v>
+        <v>1.511356355991733e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.511356355991734e-09</v>
+        <v>1.511356355991733e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.559475828875569e-09</v>
+        <v>1.559475828875566e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.470160843131607e-09</v>
+        <v>1.470160843131608e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.511356355991734e-09</v>
+        <v>1.511356355991733e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.555975648302643e-09</v>
+        <v>1.555975648302641e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.577886559753926e-09</v>
+        <v>1.577886559753922e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.582671015503594e-09</v>
+        <v>1.439569211839654e-09</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.152655218333415e-09</v>
+        <v>6.152655218333446e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.446420499375381e-09</v>
+        <v>6.446420499375454e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>6.845144606231498e-09</v>
+        <v>6.845144606231492e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.446420499375381e-09</v>
+        <v>6.446420499375454e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.446420499375381e-09</v>
+        <v>6.446420499375454e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.934582966240333e-09</v>
+        <v>6.934582966240326e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>7.507415735920814e-09</v>
+        <v>7.507415735920832e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.446420499375381e-09</v>
+        <v>6.446420499375454e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.394480882034655e-08</v>
+        <v>1.394480882034654e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>6.40577397472666e-09</v>
+        <v>6.405773974726663e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>8.851639360415435e-09</v>
+        <v>8.85163936041545e-09</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.889668644823997e-10</v>
+        <v>8.88966864482405e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>8.811532021808685e-10</v>
+        <v>8.81153202180871e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>8.889668644823997e-10</v>
+        <v>8.88966864482405e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>8.861357667445717e-10</v>
+        <v>8.861357667445785e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>8.86135766744573e-10</v>
+        <v>8.861357667445763e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>8.887242380017149e-10</v>
+        <v>8.88724238001718e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>8.889668644823997e-10</v>
+        <v>8.88966864482405e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>8.886135370014414e-10</v>
+        <v>8.886135370014463e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>8.889668644823997e-10</v>
+        <v>8.88966864482405e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.889668644823997e-10</v>
+        <v>8.88966864482405e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>8.889668644823997e-10</v>
+        <v>8.88966864482405e-10</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.217215332623246e-09</v>
+        <v>1.423219208120912e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.420098381792436e-09</v>
+        <v>1.420098381792451e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>3.217628277491022e-09</v>
+        <v>3.217628277491014e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.400534192846538e-09</v>
+        <v>1.400534192846535e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.423525783400475e-09</v>
+        <v>1.423525783400481e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.422976581640222e-09</v>
+        <v>3.216972706142561e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.206835997012277e-09</v>
+        <v>3.206835997012276e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.422865880639948e-09</v>
+        <v>1.422865880639953e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.211019968679948e-09</v>
+        <v>1.477989672740518e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.422595012091081e-09</v>
+        <v>1.422595012091088e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.42394374197044e-09</v>
+        <v>1.423943741970443e-09</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.136544478668683e-09</v>
+        <v>5.136544478668704e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.136191151187722e-09</v>
+        <v>5.136191151187736e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.13637563144636e-09</v>
+        <v>5.136375631446379e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.136568389627579e-09</v>
+        <v>5.136568389627597e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.136568389627579e-09</v>
+        <v>5.136568389627599e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.136301852188007e-09</v>
+        <v>5.136301852188017e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.136544478668683e-09</v>
+        <v>5.136544478668704e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.136191151187722e-09</v>
+        <v>5.136191151187736e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.136544478668683e-09</v>
+        <v>5.136544478668704e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.136544478668683e-09</v>
+        <v>5.136544478668704e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.136544478668683e-09</v>
+        <v>5.136544478668704e-09</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.790340094905887e-09</v>
+        <v>4.790340094905912e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>7.604772162160947e-09</v>
+        <v>7.604772162165584e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.187430656144934e-09</v>
+        <v>8.187430656144971e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>6.835097743513777e-09</v>
+        <v>6.835097743513809e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>4.879501206806925e-09</v>
+        <v>4.87950120680694e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>7.60375732838685e-09</v>
+        <v>7.603757328386898e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>7.603999954867413e-09</v>
+        <v>7.603999954867446e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>7.603646627386593e-09</v>
+        <v>7.603646627386621e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>7.604552920000272e-09</v>
+        <v>7.604552920000282e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.738074918444988e-09</v>
+        <v>4.738074918444994e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.054310295332831e-08</v>
+        <v>1.054310295332836e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.564266935396425e-09</v>
+        <v>3.564266935396436e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.449491128659568e-09</v>
+        <v>4.449491128659587e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.449845641746074e-09</v>
+        <v>4.449845641746096e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.471429105076496e-09</v>
+        <v>5.471429105076533e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.449490507053227e-09</v>
+        <v>4.44949050705323e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.449601829659831e-09</v>
+        <v>4.44960182965986e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.449844456140535e-09</v>
+        <v>4.449844456140552e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.449491128659568e-09</v>
+        <v>4.449491128659587e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.449844456140535e-09</v>
+        <v>4.449844456140552e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.936737861351295e-09</v>
+        <v>3.936737861351302e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.449844456140535e-09</v>
+        <v>4.449844456140552e-09</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.392774089582685e-09</v>
+        <v>1.392774089582688e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.257617455384255e-09</v>
+        <v>1.257617455384261e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.374841642141155e-09</v>
+        <v>1.374841642141159e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.257617455384255e-09</v>
+        <v>1.257617455384261e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.257617455384255e-09</v>
+        <v>1.257617455384261e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.372312248365966e-09</v>
+        <v>1.372312248365962e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.375739125118934e-09</v>
+        <v>1.375739125118933e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.257617455384255e-09</v>
+        <v>1.257617455384261e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.21735628465951e-09</v>
+        <v>1.217356284659512e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.383253901965218e-09</v>
+        <v>1.383253901965217e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.352287649721632e-09</v>
+        <v>1.35228764972163e-09</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.423523815810604e-09</v>
+        <v>1.423523815810607e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.299395075227922e-09</v>
+        <v>1.299395075227926e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.416222731516217e-09</v>
+        <v>1.41622273151622e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.299395075227922e-09</v>
+        <v>1.299395075227926e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.299395075227922e-09</v>
+        <v>1.299395075227926e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.413329972647159e-09</v>
+        <v>1.413329972647164e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.416678444071879e-09</v>
+        <v>1.416678444071878e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.299395075227922e-09</v>
+        <v>1.299395075227926e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.35217572581594e-09</v>
+        <v>1.352175725815943e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.419651196318879e-09</v>
+        <v>1.419651196318877e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.413797498142886e-09</v>
+        <v>1.407127139396286e-09</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.705149371202262e-09</v>
+        <v>4.705149371202224e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>8.147422426420962e-09</v>
+        <v>8.147422426420949e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.074514259321788e-08</v>
+        <v>1.074514259321809e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>7.60850330561166e-09</v>
+        <v>7.608503305611621e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>7.60850330561166e-09</v>
+        <v>7.608503305611621e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>8.661931898979365e-09</v>
+        <v>8.661931898979385e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.493546653471012e-08</v>
+        <v>1.493546653471008e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.60850330561166e-09</v>
+        <v>7.608503305611621e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>9.776903941730595e-09</v>
+        <v>9.776903941730558e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>7.861496014293394e-09</v>
+        <v>7.86149601429333e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.059028494736098e-08</v>
+        <v>1.059028494736099e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.991114687471688e-10</v>
+        <v>9.991114687471709e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.71856411322261e-10</v>
+        <v>9.718564113222651e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.991114687471688e-10</v>
+        <v>9.991114687471698e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.925040086332841e-10</v>
+        <v>9.925040086332901e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.925040086332845e-10</v>
+        <v>9.925040086332895e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.988703473128448e-10</v>
+        <v>9.988703473128529e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.991114687471688e-10</v>
+        <v>9.991114687471709e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.988007546303605e-10</v>
+        <v>9.988007546303612e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.991114687471688e-10</v>
+        <v>9.991114687471709e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.991114687471688e-10</v>
+        <v>9.991114687471698e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.991114687471688e-10</v>
+        <v>9.991114687471698e-10</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.513551906175092e-09</v>
+        <v>3.445097611726895e-09</v>
       </c>
       <c r="C4" t="n">
         <v>1.507797421790874e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.519382176297955e-09</v>
+        <v>1.519381318877185e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.48855798543944e-09</v>
+        <v>1.488557985439438e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.513665206806101e-09</v>
+        <v>1.513665206806093e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.444856490292572e-09</v>
+        <v>1.513310784740766e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.492187545975846e-09</v>
+        <v>3.492187545975845e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.444786897610086e-09</v>
+        <v>1.513241192058279e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.474888784139446e-09</v>
+        <v>3.474888784139449e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.513974938790862e-09</v>
+        <v>1.513974938790864e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.514684300234091e-09</v>
+        <v>1.514684300234086e-09</v>
       </c>
     </row>
     <row r="5">
@@ -1430,25 +1430,25 @@
         <v>5.759421579209073e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.756915729426632e-09</v>
+        <v>5.756915729426642e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.759244312346005e-09</v>
+        <v>5.759244312345997e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.759076999020352e-09</v>
+        <v>5.759076999020353e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.759076999020352e-09</v>
+        <v>5.759076999020353e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.759180457774747e-09</v>
+        <v>5.759180457774748e-09</v>
       </c>
       <c r="H5" t="n">
         <v>5.759421579209073e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.759110865092265e-09</v>
+        <v>5.759110865092268e-09</v>
       </c>
       <c r="J5" t="n">
         <v>5.759421579209073e-09</v>
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.641320112042488e-09</v>
+        <v>5.641320112042503e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.997025964599104e-09</v>
+        <v>8.997025964599098e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.694852936586845e-09</v>
+        <v>9.69485293658687e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>8.08087628162768e-09</v>
+        <v>8.0808762816277e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.747518132956369e-09</v>
+        <v>5.747518132956383e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.998440943087498e-09</v>
+        <v>8.998440943087499e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.998682064523325e-09</v>
+        <v>8.998682064523345e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.998371350405011e-09</v>
+        <v>8.99837135040502e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.99934188282037e-09</v>
+        <v>8.999341882820392e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.578955390062195e-09</v>
+        <v>5.578955390062201e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.250572736237573e-08</v>
+        <v>1.250572736237575e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.308813937324305e-09</v>
+        <v>4.308813937324299e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.399099199333492e-09</v>
+        <v>5.399099199333494e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.401606322867907e-09</v>
+        <v>5.401606322867917e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.66235221249081e-09</v>
+        <v>6.662352212490805e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.401293498161743e-09</v>
+        <v>5.401293498161734e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.401363927681608e-09</v>
+        <v>5.401363927681604e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.401605049115929e-09</v>
+        <v>5.401605049115933e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.401294334999126e-09</v>
+        <v>5.401294334999122e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.401605049115929e-09</v>
+        <v>5.401605049115933e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.768438122957247e-09</v>
+        <v>4.768438122957256e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.401605049115929e-09</v>
+        <v>5.401605049115934e-09</v>
       </c>
     </row>
     <row r="8">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.977658719212757e-09</v>
+        <v>1.977658719212758e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.385962189496375e-10</v>
+        <v>9.385962189496377e-10</v>
       </c>
       <c r="D8" t="n">
-        <v>1.31092183049482e-09</v>
+        <v>1.310921830494816e-09</v>
       </c>
       <c r="E8" t="n">
         <v>1.327091377002484e-09</v>
@@ -1562,7 +1562,7 @@
         <v>1.327091377002484e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.264924162552472e-09</v>
+        <v>1.264924162552473e-09</v>
       </c>
       <c r="H8" t="n">
         <v>1.250220062239468e-09</v>
@@ -1574,7 +1574,7 @@
         <v>1.623013354628265e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.488245033429887e-09</v>
+        <v>2.488245033429892e-09</v>
       </c>
       <c r="L8" t="n">
         <v>1.314025059128039e-09</v>
@@ -1587,13 +1587,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.000093063168893e-09</v>
+        <v>2.000093063168894e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.000132503472135e-09</v>
+        <v>1.000132503472136e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.398358473803638e-09</v>
+        <v>1.398358473803637e-09</v>
       </c>
       <c r="E9" t="n">
         <v>1.371471782740227e-09</v>
@@ -1602,19 +1602,19 @@
         <v>1.371471782740227e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.323067266626242e-09</v>
+        <v>1.323067266626244e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.37385317404573e-09</v>
+        <v>1.373853174045729e-09</v>
       </c>
       <c r="I9" t="n">
         <v>1.371471782740227e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.687255038479305e-09</v>
+        <v>1.687255038479304e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>2.518451495935849e-09</v>
+        <v>2.518451495935851e-09</v>
       </c>
       <c r="L9" t="n">
         <v>1.38325286584612e-09</v>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.649903507523066e-09</v>
+        <v>3.649903507523077e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.93698028322169e-09</v>
+        <v>6.936980283221793e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>8.976720864376812e-09</v>
+        <v>8.976720864376835e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.977181543024369e-09</v>
+        <v>6.977181543024407e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.977181543024369e-09</v>
+        <v>6.977181543024407e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>7.233579185440783e-09</v>
+        <v>7.233579185441143e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.069220189058074e-08</v>
+        <v>1.069220189058076e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>6.977181543024369e-09</v>
+        <v>6.977181543024407e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>7.666036525938873e-09</v>
+        <v>7.666036525938868e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>6.339543512911574e-09</v>
+        <v>6.339543512911576e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>7.614449101890323e-09</v>
+        <v>7.614449101890361e-09</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.765260641460083e-10</v>
+        <v>9.765260641460046e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.494980151763179e-10</v>
+        <v>9.494980151763187e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.765260641460083e-10</v>
+        <v>9.765260641460046e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.725795616776001e-10</v>
+        <v>9.725795616776076e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.725795616776053e-10</v>
+        <v>9.725795616776076e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.763138236583471e-10</v>
+        <v>9.763138236583622e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.765260641460083e-10</v>
+        <v>9.765260641460046e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.764010220260764e-10</v>
+        <v>9.764010220260783e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.765260641460079e-10</v>
+        <v>9.765260641460046e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.765260641460083e-10</v>
+        <v>9.765260641460046e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.765260641460083e-10</v>
+        <v>9.765260641460046e-10</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.289663938983805e-09</v>
+        <v>3.289663938983824e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.447845580769019e-09</v>
+        <v>1.447845580769012e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>3.325963151022565e-09</v>
+        <v>3.325963151022572e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.431253825608549e-09</v>
+        <v>1.431253825608551e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.454199004332865e-09</v>
+        <v>1.454199004332869e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.453300183569573e-09</v>
+        <v>3.289451698496178e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.342014412302737e-09</v>
+        <v>3.34201441230271e-09</v>
       </c>
       <c r="I4" t="n">
         <v>1.4533873819373e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.50834115534782e-09</v>
+        <v>1.508341155347814e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.45335104002534e-09</v>
+        <v>1.453351040025353e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.454048535458812e-09</v>
+        <v>1.454048535458815e-09</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.506031446339973e-09</v>
+        <v>5.506031446339984e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.503541525510985e-09</v>
+        <v>5.50354152551099e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.505863787879716e-09</v>
+        <v>5.505863787879712e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.506410929939195e-09</v>
+        <v>5.506410929939204e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.506410929939195e-09</v>
+        <v>5.506410929939204e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.505819205852344e-09</v>
+        <v>5.505819205852334e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.506031446339973e-09</v>
+        <v>5.506031446339984e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.505906404220051e-09</v>
+        <v>5.505906404220057e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.506031446339973e-09</v>
+        <v>5.506031446339984e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.506031446339973e-09</v>
+        <v>5.506031446339984e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.506031446339973e-09</v>
+        <v>5.506031446339984e-09</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.399325144219035e-09</v>
+        <v>5.399325144219067e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.601911595933428e-09</v>
+        <v>8.601911595925996e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.267398692935114e-09</v>
+        <v>9.267398692935112e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.727894566077776e-09</v>
+        <v>7.727894566077791e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.501155154726291e-09</v>
+        <v>5.501155154726298e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.602867140832919e-09</v>
+        <v>8.602867140832931e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.603079381324469e-09</v>
+        <v>8.603079381324502e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.60295433920063e-09</v>
+        <v>8.602954339200632e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.603709011247954e-09</v>
+        <v>8.603709011247968e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.339813764417741e-09</v>
+        <v>5.339813764417768e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.19496685759498e-08</v>
+        <v>1.194966857594983e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.968987594808143e-09</v>
+        <v>3.968987594808188e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.965374762127111e-09</v>
+        <v>4.965374762127121e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.967865912470071e-09</v>
+        <v>4.967865912470102e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.120422804768667e-09</v>
+        <v>6.120422804768688e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.967738898732302e-09</v>
+        <v>4.967738898732332e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.967652442468465e-09</v>
+        <v>4.96765244246848e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.967864682956086e-09</v>
+        <v>4.967864682956142e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.967739640836181e-09</v>
+        <v>4.967739640836201e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.967864682956086e-09</v>
+        <v>4.967864682956142e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.389111892319054e-09</v>
+        <v>4.389111892319093e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.967864682956086e-09</v>
+        <v>4.967864682956142e-09</v>
       </c>
     </row>
     <row r="8">
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.997243147498467e-09</v>
+        <v>1.997243147498465e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.5821197197374e-10</v>
+        <v>9.58211971973739e-10</v>
       </c>
       <c r="D8" t="n">
-        <v>1.34385561916903e-09</v>
+        <v>1.343855619169024e-09</v>
       </c>
       <c r="E8" t="n">
         <v>1.337648808767791e-09</v>
@@ -1958,22 +1958,22 @@
         <v>1.337648808767791e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.288588812052954e-09</v>
+        <v>1.288588812052948e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.328131748020758e-09</v>
+        <v>1.32813174802077e-09</v>
       </c>
       <c r="I8" t="n">
         <v>1.337648808767791e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.665612086077054e-09</v>
+        <v>1.665612086077075e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.515111603012066e-09</v>
+        <v>2.515111603012084e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.369779316071469e-09</v>
+        <v>1.36977931607148e-09</v>
       </c>
     </row>
     <row r="9">
@@ -1986,34 +1986,34 @@
         <v>2.008126107495971e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.008504897226529e-09</v>
+        <v>1.008504897226528e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.413622250570657e-09</v>
+        <v>1.413622250570649e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.378425942748561e-09</v>
+        <v>1.378425942748562e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.378425942748561e-09</v>
+        <v>1.378425942748562e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.332851670397735e-09</v>
+        <v>1.33285167039773e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.407367321446775e-09</v>
+        <v>1.407367321446783e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.378425942748561e-09</v>
+        <v>1.378425942748562e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.707626244891428e-09</v>
+        <v>1.707626244891425e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>2.529134395768891e-09</v>
+        <v>2.529134395768902e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.408470866420014e-09</v>
+        <v>1.408470866420013e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.278724687007102e-09</v>
+        <v>3.278724687007106e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.255136845954077e-09</v>
+        <v>6.255136845954071e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>8.015934967764511e-09</v>
+        <v>8.015934967764487e-09</v>
       </c>
       <c r="E2" t="n">
         <v>6.816720254253664e-09</v>
@@ -2114,10 +2114,10 @@
         <v>6.816720254253664e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.619960314773386e-09</v>
+        <v>6.619960314773467e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>8.747127956377234e-09</v>
+        <v>8.747127956377257e-09</v>
       </c>
       <c r="I2" t="n">
         <v>6.816720254253664e-09</v>
@@ -2126,10 +2126,10 @@
         <v>6.114269869759888e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>5.84336779736422e-09</v>
+        <v>5.843367797364207e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>7.298337715844217e-09</v>
+        <v>7.298337715844215e-09</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.743286397400256e-10</v>
+        <v>9.743286397400236e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.45503481950717e-10</v>
+        <v>9.455034819507149e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.743286397400254e-10</v>
+        <v>9.743286397400242e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.716589691762428e-10</v>
+        <v>9.716589691762424e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.716589691762428e-10</v>
+        <v>9.716589691762432e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.741277792721136e-10</v>
+        <v>9.741277792721152e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.743286397400254e-10</v>
+        <v>9.743286397400242e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.742772915730463e-10</v>
+        <v>9.74277291573049e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.743286397400256e-10</v>
+        <v>9.743286397400242e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.743286397400254e-10</v>
+        <v>9.743286397400242e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.743286397400254e-10</v>
+        <v>9.743286397400242e-10</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.453518488667855e-09</v>
+        <v>1.453518488667854e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.447144808306883e-09</v>
+        <v>1.447144808306886e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.457338705010312e-09</v>
+        <v>1.457339436948652e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.432015446432316e-09</v>
+        <v>1.43201544643231e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.454481491560357e-09</v>
+        <v>1.454481491560354e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.287029879098328e-09</v>
+        <v>3.287029879098322e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.345905935290291e-09</v>
+        <v>3.345905935290281e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.287179391399254e-09</v>
+        <v>3.287179391399257e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.318020900627606e-09</v>
+        <v>3.318020900627597e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.453303232084335e-09</v>
+        <v>1.453303232084249e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.454003292498777e-09</v>
+        <v>1.454003292498771e-09</v>
       </c>
     </row>
     <row r="5">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.488348667206621e-09</v>
+        <v>5.488348667206626e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.485858510910742e-09</v>
+        <v>5.485858510910746e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.488181372592599e-09</v>
+        <v>5.4881813725926e-09</v>
       </c>
       <c r="E5" t="n">
         <v>5.489130968878827e-09</v>
@@ -2234,22 +2234,22 @@
         <v>5.489130968878827e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.488147806738708e-09</v>
+        <v>5.488147806738715e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.488348667206621e-09</v>
+        <v>5.488348667206626e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.488297319039641e-09</v>
+        <v>5.488297319039643e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.488348667206621e-09</v>
+        <v>5.488348667206626e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.488348667206621e-09</v>
+        <v>5.488348667206626e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.488348667206621e-09</v>
+        <v>5.488348667206626e-09</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.375966186106686e-09</v>
+        <v>5.375966186106685e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.563317250339026e-09</v>
+        <v>8.563317250348349e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.225269645414141e-09</v>
+        <v>9.225269645414139e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.69359295823644e-09</v>
+        <v>7.693592958236439e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.477573214069215e-09</v>
+        <v>5.477573214069208e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.563973127880044e-09</v>
+        <v>8.563973127880041e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.564173988353617e-09</v>
+        <v>8.56417398835362e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.564122640180972e-09</v>
+        <v>8.564122640180971e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.564800562914552e-09</v>
+        <v>8.564800562914555e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.31674358931597e-09</v>
+        <v>5.316743589315965e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.189452363176304e-08</v>
+        <v>1.189452363176302e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.843859187745596e-09</v>
+        <v>3.843859187745626e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.805334608812381e-09</v>
+        <v>4.805334608812402e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.807826006566553e-09</v>
+        <v>4.807826006566575e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.920169485072866e-09</v>
+        <v>5.920169485072878e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.807772704120849e-09</v>
+        <v>4.807772704120856e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.807623904640344e-09</v>
+        <v>4.807623904640356e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.807824765108251e-09</v>
+        <v>4.807824765108272e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.807773416941278e-09</v>
+        <v>4.807773416941301e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.807824765108251e-09</v>
+        <v>4.807824765108272e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.594019714202433e-09</v>
+        <v>4.226639734091704e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.807824765108251e-09</v>
+        <v>4.807824765108272e-09</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.998494164711013e-09</v>
+        <v>1.998494164711012e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.646433196105503e-10</v>
+        <v>9.646433196105499e-10</v>
       </c>
       <c r="D8" t="n">
-        <v>1.354867847548696e-09</v>
+        <v>1.354867847548695e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.329083206937385e-09</v>
+        <v>1.329083206937384e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.329083206937385e-09</v>
+        <v>1.329083206937384e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.291634241660457e-09</v>
+        <v>1.291634241660456e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.357554590878293e-09</v>
+        <v>1.357554590878291e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.329083206937385e-09</v>
+        <v>1.329083206937384e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.686097740776567e-09</v>
+        <v>1.686097740776559e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.511972117959646e-09</v>
+        <v>2.51197211795962e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.365256959596997e-09</v>
+        <v>1.365256959596995e-09</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.004258658094451e-09</v>
+        <v>2.004258658094452e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.005445227813259e-09</v>
+        <v>1.005445227813258e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.410907972819261e-09</v>
+        <v>1.41090797281926e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.36773424768728e-09</v>
+        <v>1.367734247687279e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.36773424768728e-09</v>
+        <v>1.367734247687279e-09</v>
       </c>
       <c r="G9" t="n">
         <v>1.327434793417425e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.412113178416871e-09</v>
+        <v>1.41211317841687e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.36773424768728e-09</v>
+        <v>1.367734247687279e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.707008969497892e-09</v>
+        <v>1.70700896949789e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>2.519060791053317e-09</v>
+        <v>2.51906079105332e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.400140922227839e-09</v>
+        <v>1.400140922227838e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2495,34 +2495,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.48855830509844e-09</v>
+        <v>3.488558305098443e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.010511810274743e-09</v>
+        <v>5.010511810274741e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>8.821852987044107e-09</v>
+        <v>8.821852987044117e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.919490253056248e-09</v>
+        <v>6.919490253056208e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.919490253056248e-09</v>
+        <v>6.919490253056208e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>7.686288958873125e-09</v>
+        <v>7.686288958873723e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.310345096219854e-08</v>
+        <v>1.31034509621987e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>6.919490253056248e-09</v>
+        <v>6.919490253056208e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>9.683785272213604e-09</v>
+        <v>9.683785272213635e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>7.089871711000007e-09</v>
+        <v>7.089871711000011e-09</v>
       </c>
       <c r="L2" t="n">
         <v>1.097471332451792e-08</v>
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.884448483082751e-10</v>
+        <v>9.884448483082794e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.598757480649155e-10</v>
+        <v>9.598757480649132e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.884448483082751e-10</v>
+        <v>9.884448483082794e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.849655590049324e-10</v>
+        <v>9.849655590049402e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.849655590049346e-10</v>
+        <v>9.849655590049402e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.882099466609153e-10</v>
+        <v>9.88209946660918e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.884448483082751e-10</v>
+        <v>9.884448483082794e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.88168379296019e-10</v>
+        <v>9.88168379296021e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.884448483082751e-10</v>
+        <v>9.884448483082794e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.884448483082751e-10</v>
+        <v>9.884448483082794e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.884448483082751e-10</v>
+        <v>9.884448483082794e-10</v>
       </c>
     </row>
     <row r="4">
@@ -2578,34 +2578,34 @@
         <v>1.494435148086263e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.484526607282435e-09</v>
+        <v>1.484526607282423e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.498275212159185e-09</v>
+        <v>1.498276071782072e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.470971172262227e-09</v>
+        <v>1.470971172262234e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.494969129336287e-09</v>
+        <v>1.494969129336284e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.494200246438897e-09</v>
+        <v>1.494200246438903e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.465271155177409e-09</v>
+        <v>3.465271155177414e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.494158679074003e-09</v>
+        <v>3.419834868831e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.449470756321255e-09</v>
+        <v>1.552241712264753e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.495082363933207e-09</v>
+        <v>1.495082363933211e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.49607852885597e-09</v>
+        <v>1.496078528855973e-09</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.738006266485289e-09</v>
+        <v>5.738006266485299e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.735457482590568e-09</v>
+        <v>5.735457482590583e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.737829368691298e-09</v>
+        <v>5.737829368691308e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.738507840847689e-09</v>
+        <v>5.738507840847699e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.738507840847689e-09</v>
+        <v>5.738507840847699e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.737771364837928e-09</v>
+        <v>5.737771364837942e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.738006266485289e-09</v>
+        <v>5.738006266485299e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.737729797473037e-09</v>
+        <v>5.737729797473042e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.738006266485289e-09</v>
+        <v>5.738006266485299e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.738006266485289e-09</v>
+        <v>5.738006266485299e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.738006266485289e-09</v>
+        <v>5.738006266485299e-09</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.60670835218926e-09</v>
+        <v>5.60670835218927e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.946471700678989e-09</v>
+        <v>8.946471700685646e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.640112563632025e-09</v>
+        <v>9.640112563632043e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>8.034877422130596e-09</v>
+        <v>8.034877422130618e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.712896276187662e-09</v>
+        <v>5.71289627618767e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.947163763069173e-09</v>
+        <v>8.947163763069203e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.947398664717842e-09</v>
+        <v>8.947398664717877e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.947122195704281e-09</v>
+        <v>8.947122195704315e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.948055206565799e-09</v>
+        <v>8.948055206565805e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.544653314480071e-09</v>
+        <v>5.544653314480083e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.243702904058533e-08</v>
+        <v>1.243702904058537e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.251868851098278e-09</v>
+        <v>4.251868851098269e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.328678384510623e-09</v>
+        <v>5.32867838451063e-09</v>
       </c>
       <c r="D7" t="n">
         <v>5.331228451259019e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.576507469379149e-09</v>
+        <v>6.576507469379127e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.330949897980135e-09</v>
+        <v>5.330949897980149e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.330992266757988e-09</v>
+        <v>5.330992266757996e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.33122716840535e-09</v>
+        <v>5.33122716840536e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.330950699393092e-09</v>
+        <v>5.3309506993931e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.33122716840535e-09</v>
+        <v>5.331227168405356e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.972122049649472e-09</v>
+        <v>4.705843259953801e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.33122716840535e-09</v>
+        <v>5.331227168405356e-09</v>
       </c>
     </row>
     <row r="8">
@@ -2735,34 +2735,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.04127728115625e-09</v>
+        <v>2.041277281156253e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.896256896939139e-10</v>
+        <v>9.896256896939151e-10</v>
       </c>
       <c r="D8" t="n">
         <v>1.332574282523663e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.322134369892249e-09</v>
+        <v>1.322134369892253e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.322134369892249e-09</v>
+        <v>1.322134369892253e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.27540299221455e-09</v>
+        <v>1.275402992214552e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.264791681253988e-09</v>
+        <v>1.264791681253995e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.322134369892249e-09</v>
+        <v>1.322134369892253e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.599447319052738e-09</v>
+        <v>1.59944731905274e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.48746515496206e-09</v>
+        <v>2.487465154962063e-09</v>
       </c>
       <c r="L8" t="n">
         <v>1.289464848172471e-09</v>
@@ -2775,19 +2775,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.047079185945222e-09</v>
+        <v>2.047079185945224e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.009792155418816e-09</v>
+        <v>1.009792155418817e-09</v>
       </c>
       <c r="D9" t="n">
         <v>1.394132141105584e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.35760688487765e-09</v>
+        <v>1.357606884877644e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.35760688487765e-09</v>
+        <v>1.357606884877644e-09</v>
       </c>
       <c r="G9" t="n">
         <v>1.320855296597361e-09</v>
@@ -2796,16 +2796,16 @@
         <v>1.366709395054845e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.35760688487765e-09</v>
+        <v>1.357606884877644e-09</v>
       </c>
       <c r="J9" t="n">
         <v>1.662981201715723e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>2.507545320031853e-09</v>
+        <v>2.507545320031858e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.363606382273125e-09</v>
+        <v>1.363606382273129e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.295826026468649e-09</v>
+        <v>3.295826026468636e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.054963698712071e-09</v>
+        <v>5.054963698712062e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>6.724885518417455e-09</v>
+        <v>6.724885518417452e-09</v>
       </c>
       <c r="E2" t="n">
         <v>6.837377314594718e-09</v>
@@ -2906,22 +2906,22 @@
         <v>6.837377314594718e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.149421928549153e-09</v>
+        <v>6.149421928549149e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>7.052599614001296e-09</v>
+        <v>7.052599614001293e-09</v>
       </c>
       <c r="I2" t="n">
         <v>6.837377314594718e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>7.425673824494428e-09</v>
+        <v>7.425673824494431e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>5.693503731545534e-09</v>
+        <v>5.69350373154553e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>7.898683848843452e-09</v>
+        <v>7.898683848843459e-09</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.489173536884156e-10</v>
+        <v>9.489173536884162e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.226823990634976e-10</v>
+        <v>9.226823990635013e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.489173536884156e-10</v>
+        <v>9.489173536884162e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.47639794750996e-10</v>
+        <v>9.476397947509957e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.47639794750996e-10</v>
+        <v>9.476397947509957e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.487187408774039e-10</v>
+        <v>9.487187408774091e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.489173536884156e-10</v>
+        <v>9.489173536884162e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.48868853993005e-10</v>
+        <v>9.488688539930071e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.489173536884156e-10</v>
+        <v>9.489173536884162e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.489173536884156e-10</v>
+        <v>9.489173536884162e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.489173536884156e-10</v>
+        <v>9.489173536884162e-10</v>
       </c>
     </row>
     <row r="4">
@@ -2974,34 +2974,34 @@
         <v>1.426215645395613e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.418858590413602e-09</v>
+        <v>1.418858590413593e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.427811060859224e-09</v>
+        <v>3.280729115981344e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.406455524242461e-09</v>
+        <v>1.406455524242455e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.427309415743635e-09</v>
+        <v>1.427309415743639e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.245447776403317e-09</v>
+        <v>1.426017032584605e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.295631677693816e-09</v>
+        <v>3.295631677693815e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.245597889518918e-09</v>
+        <v>3.245597889518915e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.480013717031172e-09</v>
+        <v>3.274291625484602e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.426082537912788e-09</v>
+        <v>1.426082537912782e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.42697996700643e-09</v>
+        <v>1.426979967006436e-09</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.416190625375396e-09</v>
+        <v>5.416190625375393e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.413704358611747e-09</v>
+        <v>5.413704358611736e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.416024025234978e-09</v>
+        <v>5.41602402523496e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.417207915961808e-09</v>
+        <v>5.417207915961782e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.417207915961808e-09</v>
+        <v>5.417207915961782e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.415992012564396e-09</v>
+        <v>5.415992012564382e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.416190625375396e-09</v>
+        <v>5.416190625375393e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.416142125679984e-09</v>
+        <v>5.416142125679989e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.416190625375396e-09</v>
+        <v>5.416190625375393e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.416190625375396e-09</v>
+        <v>5.416190625375393e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.416190625375396e-09</v>
+        <v>5.416190625375393e-09</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.245252129402889e-09</v>
+        <v>5.24525212940288e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.356016439465368e-09</v>
+        <v>8.356016439458127e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.001835040013456e-09</v>
+        <v>9.00183504001346e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.50727284961604e-09</v>
+        <v>7.507272849616033e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.344565749506637e-09</v>
+        <v>5.34456574950663e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.35646498933545e-09</v>
+        <v>8.356464989335455e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.356663602150456e-09</v>
+        <v>8.356663602150453e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.356615102451072e-09</v>
+        <v>8.356615102451045e-09</v>
       </c>
       <c r="J6" t="n">
         <v>8.357275084076365e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.187456063858697e-09</v>
+        <v>5.187456063858695e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.160679305782923e-08</v>
+        <v>1.160679305782924e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8419305112482e-09</v>
+        <v>3.841930511248202e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.805600192443479e-09</v>
+        <v>4.805600192443487e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.808087705175709e-09</v>
+        <v>4.808087705175701e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.922961712365922e-09</v>
+        <v>5.92296171236596e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.80803727822783e-09</v>
+        <v>4.808037278227865e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.807887846396117e-09</v>
+        <v>4.80788784639613e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.808086459207145e-09</v>
+        <v>4.808086459207137e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.808037959511712e-09</v>
+        <v>4.808037959511737e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.808086459207145e-09</v>
+        <v>4.808086459207137e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.59152333957185e-09</v>
+        <v>4.248292432622178e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.808086459207145e-09</v>
+        <v>4.808086459207137e-09</v>
       </c>
     </row>
     <row r="8">
@@ -3131,34 +3131,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.037666558803768e-09</v>
+        <v>2.037666558803766e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.575178302587806e-10</v>
+        <v>9.575178302587825e-10</v>
       </c>
       <c r="D8" t="n">
-        <v>1.327421215935998e-09</v>
+        <v>1.327421215936e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.271969627588065e-09</v>
+        <v>1.271969627588067e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.271969627588065e-09</v>
+        <v>1.271969627588068e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.269535486495106e-09</v>
+        <v>1.269535486495101e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.335116253111501e-09</v>
+        <v>1.335116253111503e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.271969627588065e-09</v>
+        <v>1.271969627588067e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.575092958931598e-09</v>
+        <v>1.575092958931605e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.466425759305628e-09</v>
+        <v>2.466425759305564e-09</v>
       </c>
       <c r="L8" t="n">
         <v>1.302308739710452e-09</v>
@@ -3174,31 +3174,31 @@
         <v>2.043172700491922e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>9.82282367021455e-10</v>
+        <v>9.822823670214567e-10</v>
       </c>
       <c r="D9" t="n">
-        <v>1.365926499017864e-09</v>
+        <v>1.36592649901786e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.312019186757332e-09</v>
+        <v>1.312019186757336e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.312019186757331e-09</v>
+        <v>1.312019186757336e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.299458272568907e-09</v>
+        <v>1.299458272568902e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.369138797454257e-09</v>
+        <v>1.369138797454261e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.312019186757332e-09</v>
+        <v>1.312019186757336e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.615485540246415e-09</v>
+        <v>1.615485540246414e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>2.472338927980729e-09</v>
+        <v>2.472338927980658e-09</v>
       </c>
       <c r="L9" t="n">
         <v>1.345678922106492e-09</v>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.530837668268703e-09</v>
+        <v>3.530837668268711e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.375530966039336e-09</v>
+        <v>5.375530966039335e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8001896124764e-09</v>
+        <v>6.80018961247641e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.981445024268076e-09</v>
+        <v>6.981445024268084e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.981445024268076e-09</v>
+        <v>6.981445024268084e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.225579647932894e-09</v>
+        <v>6.225579647932842e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>6.851338259433625e-09</v>
+        <v>6.851338259433648e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.981445024268076e-09</v>
+        <v>6.981445024268084e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>7.48596652632011e-09</v>
+        <v>7.485966526320102e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>5.674266997326611e-09</v>
+        <v>5.674266997326616e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>7.829769527524522e-09</v>
+        <v>7.829769527524517e-09</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.508140596846846e-10</v>
+        <v>9.508140596846759e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.232762526101014e-10</v>
+        <v>9.232762526101049e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.508140596846846e-10</v>
+        <v>9.508140596846759e-10</v>
       </c>
       <c r="E3" t="n">
         <v>9.51363490940557e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.513634909405564e-10</v>
+        <v>9.513634909405568e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.506028826593882e-10</v>
+        <v>9.506028826584522e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.508140596846846e-10</v>
+        <v>9.508140596846761e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.50687507142499e-10</v>
+        <v>9.506875071412473e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.508140596846846e-10</v>
+        <v>9.508140596846761e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.508140596846846e-10</v>
+        <v>9.508140596846759e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.508140596846846e-10</v>
+        <v>9.508140596846759e-10</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.263862748596407e-09</v>
+        <v>3.263862748596403e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.434739302923279e-09</v>
+        <v>1.434739302923285e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.443157441803998e-09</v>
+        <v>1.443157441804012e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.421397913710423e-09</v>
+        <v>1.421397913710422e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.443213072758578e-09</v>
+        <v>1.443213072758616e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.263651571570483e-09</v>
+        <v>3.263651571570479e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.323151683108102e-09</v>
+        <v>1.44251422689404e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.441957295806845e-09</v>
+        <v>3.26373619605296e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.294783288115806e-09</v>
+        <v>1.496485462086125e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.441873960693861e-09</v>
+        <v>1.441873960693876e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.442772652900654e-09</v>
+        <v>1.442772652900659e-09</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.379395349992629e-09</v>
+        <v>5.379395349992626e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.37690082895849e-09</v>
+        <v>5.376900828958488e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.379229530503615e-09</v>
+        <v>5.379229530503621e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.380964417702932e-09</v>
+        <v>5.380964417702937e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.380964417702932e-09</v>
+        <v>5.380964417702937e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.379184172966694e-09</v>
+        <v>5.379184172966688e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.379395349992629e-09</v>
+        <v>5.379395349992626e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.379268797449178e-09</v>
+        <v>5.379268797449185e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.379395349992629e-09</v>
+        <v>5.379395349992626e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.379395349992629e-09</v>
+        <v>5.379395349992626e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.379395349992629e-09</v>
+        <v>5.379395349992626e-09</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.17779100387382e-09</v>
+        <v>5.177791003873822e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.242093076547966e-09</v>
+        <v>8.242093076557907e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.877572394709505e-09</v>
+        <v>8.877572394709506e-09</v>
       </c>
       <c r="E6" t="n">
         <v>7.406083612575028e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.275910538195047e-09</v>
+        <v>5.275910538195043e-09</v>
       </c>
       <c r="G6" t="n">
         <v>8.241945113079603e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.242156290111265e-09</v>
+        <v>8.242156290111266e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.242029737562084e-09</v>
+        <v>8.242029737562083e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.242758525971391e-09</v>
+        <v>8.242758525971387e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.120868845408712e-09</v>
+        <v>5.120868845408711e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.144314206991462e-08</v>
+        <v>1.144314206991464e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.710070675730417e-09</v>
+        <v>3.710070675730428e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.635445284254575e-09</v>
+        <v>4.635445284254577e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.637941059427503e-09</v>
+        <v>4.63794105942754e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.708554849041655e-09</v>
+        <v>5.708554849041652e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.637812581604667e-09</v>
+        <v>4.637812581604684e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.63772862826277e-09</v>
+        <v>4.637728628262771e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.637939805288682e-09</v>
+        <v>4.637939805288676e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.637813252745243e-09</v>
+        <v>4.637813252745263e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.637939805288682e-09</v>
+        <v>4.637939805288676e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.078517727512077e-09</v>
+        <v>4.100329315085406e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.637939805288682e-09</v>
+        <v>4.637939805288676e-09</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.051245681342974e-09</v>
+        <v>2.051245681342975e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.341707970231297e-10</v>
+        <v>9.341707970231316e-10</v>
       </c>
       <c r="D8" t="n">
-        <v>1.29692162948686e-09</v>
+        <v>1.296921629486861e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.24109803177094e-09</v>
+        <v>1.241098031770943e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.24109803177094e-09</v>
+        <v>1.241098031770943e-09</v>
       </c>
       <c r="G8" t="n">
         <v>1.249743106774236e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.310780162084655e-09</v>
+        <v>1.310780162084653e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.24109803177094e-09</v>
+        <v>1.241098031770943e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.538588215236555e-09</v>
+        <v>1.538588215236556e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.439612699354463e-09</v>
+        <v>2.439612699354465e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.277181713164793e-09</v>
+        <v>1.277181713164796e-09</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.059699840997528e-09</v>
+        <v>2.05969984099753e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>9.636469287614301e-10</v>
+        <v>9.636469287614315e-10</v>
       </c>
       <c r="D9" t="n">
-        <v>1.336991260969482e-09</v>
+        <v>1.336991260969486e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.28366702425441e-09</v>
+        <v>1.283667024254412e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.28366702425441e-09</v>
+        <v>1.283667024254412e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.281041379460537e-09</v>
+        <v>1.281041379460535e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.342709904093283e-09</v>
+        <v>1.342709904093281e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.28366702425441e-09</v>
+        <v>1.283667024254412e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.580386444632466e-09</v>
+        <v>1.58038644463247e-09</v>
       </c>
       <c r="K9" t="n">
         <v>2.445702569717411e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.320135447229013e-09</v>
+        <v>1.32013544722901e-09</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.47476295535946e-09</v>
+        <v>3.474762955359477e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.113561044069021e-09</v>
+        <v>5.113561044069018e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>7.08432129948629e-09</v>
+        <v>7.084321299486322e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>7.011703714517088e-09</v>
+        <v>7.011703714517111e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>7.011703714517088e-09</v>
+        <v>7.011703714517111e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.739838905053989e-09</v>
+        <v>6.739838905054027e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.202175287946241e-08</v>
+        <v>1.202175287946247e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.011703714517088e-09</v>
+        <v>7.011703714517111e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>6.791922004049786e-09</v>
+        <v>6.791922004049813e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>6.323934679513909e-09</v>
+        <v>6.323934679513944e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.038832292851576e-08</v>
+        <v>1.038832292851579e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.852488872446553e-10</v>
+        <v>9.852488872446704e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.573889684218505e-10</v>
+        <v>9.573889684218536e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.852488872446553e-10</v>
+        <v>9.852488872446704e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.831365296458156e-10</v>
+        <v>9.831365296458137e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.831365296458158e-10</v>
+        <v>9.831365296458137e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.850430577823242e-10</v>
+        <v>9.850430577823202e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.852488872446553e-10</v>
+        <v>9.852488872446704e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.851547619651059e-10</v>
+        <v>9.851547619651123e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.852488872446553e-10</v>
+        <v>9.852488872446704e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.852488872446553e-10</v>
+        <v>9.852488872446704e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.852488872446553e-10</v>
+        <v>9.852488872446704e-10</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.486892543655678e-09</v>
+        <v>1.486892543655702e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.478591936745921e-09</v>
+        <v>1.478591936745892e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.488498309776145e-09</v>
+        <v>1.488498309776168e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.465409428919709e-09</v>
+        <v>1.465409428919708e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.487830437251157e-09</v>
+        <v>1.487830437251153e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.409607153974346e-09</v>
+        <v>1.486686714193353e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.454250490269739e-09</v>
+        <v>3.454250490269766e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.409718858157155e-09</v>
+        <v>1.48679841837614e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.438858385722418e-09</v>
+        <v>1.543454412240272e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.487269040526462e-09</v>
+        <v>1.48726904052649e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.488357333284024e-09</v>
+        <v>1.48835733328404e-09</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.720352448525872e-09</v>
+        <v>5.72035244852589e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.717851451673731e-09</v>
+        <v>5.717851451673736e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.720175976916776e-09</v>
+        <v>5.720175976916804e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.721197081798043e-09</v>
+        <v>5.721197081798042e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.721197081798043e-09</v>
+        <v>5.721197081798042e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.720146619063528e-09</v>
+        <v>5.720146619063561e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.720352448525872e-09</v>
+        <v>5.72035244852589e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.720258323246323e-09</v>
+        <v>5.720258323246328e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.720352448525872e-09</v>
+        <v>5.72035244852589e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.720352448525872e-09</v>
+        <v>5.72035244852589e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.720352448525872e-09</v>
+        <v>5.72035244852589e-09</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.561841167840684e-09</v>
+        <v>5.561841167840713e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.874253356382649e-09</v>
+        <v>8.874253356376118e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.561986856797767e-09</v>
+        <v>9.561986856797773e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.970311920473837e-09</v>
+        <v>7.970311920473842e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.667433872222242e-09</v>
+        <v>5.667433872222243e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.874779087741666e-09</v>
+        <v>8.874779087741709e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.874984917205283e-09</v>
+        <v>8.874984917205287e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.874890791924464e-09</v>
+        <v>8.874890791924474e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.875636045357843e-09</v>
+        <v>8.875636045357866e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.500297821685356e-09</v>
+        <v>5.500297821685366e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.233584060443568e-08</v>
+        <v>1.233584060443571e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3886,34 +3886,34 @@
         <v>4.204157171962919e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.268238116263277e-09</v>
+        <v>5.268238116263246e-09</v>
       </c>
       <c r="D7" t="n">
         <v>5.270740373041173e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.501458093424694e-09</v>
+        <v>6.501458093424652e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.27064420522979e-09</v>
+        <v>5.270644205229767e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.270533283653111e-09</v>
+        <v>5.270533283653065e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.270739113115423e-09</v>
+        <v>5.270739113115399e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.270644987835883e-09</v>
+        <v>5.270644987835842e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.270739113115423e-09</v>
+        <v>5.270739113115399e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.652757877541141e-09</v>
+        <v>4.652757877541144e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.270739113115423e-09</v>
+        <v>5.270739113115399e-09</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.048419087079569e-09</v>
+        <v>2.048419087079583e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.814594081110391e-10</v>
+        <v>9.814594081110376e-10</v>
       </c>
       <c r="D8" t="n">
-        <v>1.353022577395629e-09</v>
+        <v>1.353022577395634e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.301005491085902e-09</v>
+        <v>1.301005491085901e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.301005491085902e-09</v>
+        <v>1.301005491085901e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.283669974378737e-09</v>
+        <v>1.283669974378745e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.267143568626212e-09</v>
+        <v>1.267143568626221e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.301005491085902e-09</v>
+        <v>1.301005491085901e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.632415048925248e-09</v>
+        <v>1.63241504892524e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.485485365572767e-09</v>
+        <v>2.485485365572778e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.284106282528458e-09</v>
+        <v>1.284106282528469e-09</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.053944050171539e-09</v>
+        <v>2.053944050171556e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.003096225631157e-09</v>
+        <v>1.003096225631158e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.391159306366058e-09</v>
+        <v>1.391159306366073e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.338102991428761e-09</v>
+        <v>1.338102991428762e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.338102991428761e-09</v>
+        <v>1.338102991428762e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.316806727072897e-09</v>
+        <v>1.316806727072899e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.356346582947373e-09</v>
+        <v>1.356346582947393e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.338102991428761e-09</v>
+        <v>1.338102991428762e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.658863223998885e-09</v>
+        <v>1.658863223998897e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>2.495495326746719e-09</v>
+        <v>2.495495326746695e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.35162596418851e-09</v>
+        <v>1.351625964188516e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.350906603337683e-09</v>
+        <v>3.350906603337671e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.072345611951444e-09</v>
+        <v>5.072345611951428e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>6.713179139907136e-09</v>
+        <v>6.713179139907115e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.829987713126074e-09</v>
+        <v>6.829987713126075e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.829987713126074e-09</v>
+        <v>6.829987713126075e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.108039834252572e-09</v>
+        <v>6.108039834250803e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>6.838991849340651e-09</v>
+        <v>6.83899184934061e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.829987713126074e-09</v>
+        <v>6.829987713126075e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>7.363773334051126e-09</v>
+        <v>7.3637733340511e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>5.827499443031021e-09</v>
+        <v>5.827499443030998e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>7.625342154016914e-09</v>
+        <v>7.625342154016909e-09</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.351268240188123e-10</v>
+        <v>9.351268240188106e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.083292802760504e-10</v>
+        <v>9.083292802760468e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.351268240188123e-10</v>
+        <v>9.351268240188106e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.347342451471702e-10</v>
+        <v>9.347342451471707e-10</v>
       </c>
       <c r="F3" t="n">
         <v>9.347342451471707e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.349049921086127e-10</v>
+        <v>9.349049921086092e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.351268240188123e-10</v>
+        <v>9.351268240188106e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.349230646485266e-10</v>
+        <v>9.34923064648527e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.351268240188123e-10</v>
+        <v>9.351268240188106e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.351268240188123e-10</v>
+        <v>9.351268240188106e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.351268240188123e-10</v>
+        <v>9.351268240188106e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.417798418620069e-09</v>
+        <v>3.231849326555208e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.41033465959005e-09</v>
+        <v>1.410334659590014e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.419494681849809e-09</v>
+        <v>1.419493891897124e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.397937378153982e-09</v>
+        <v>1.397937378153981e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.418786958617623e-09</v>
+        <v>1.41878695861759e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.417576586709873e-09</v>
+        <v>1.417576586709849e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.280447568901333e-09</v>
+        <v>3.2804475689013e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.231645567184953e-09</v>
+        <v>3.231645567184899e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.260110032512373e-09</v>
+        <v>1.471303993792406e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.418382277352265e-09</v>
+        <v>1.418382277352244e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.418445392300775e-09</v>
+        <v>1.418445392300757e-09</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.351226792274958e-09</v>
+        <v>5.351226792274944e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.348742099092325e-09</v>
+        <v>5.348742099092316e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.351061408273915e-09</v>
+        <v>5.351061408273903e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.352391361888779e-09</v>
+        <v>5.35239136188876e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.352391361888779e-09</v>
+        <v>5.35239136188876e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.351004960364772e-09</v>
+        <v>5.351004960364757e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.351226792274958e-09</v>
+        <v>5.351226792274944e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.3510230329047e-09</v>
+        <v>5.351023032904677e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.351226792274958e-09</v>
+        <v>5.351226792274944e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.351226792274958e-09</v>
+        <v>5.351226792274944e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.351226792274958e-09</v>
+        <v>5.351226792274944e-09</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.117087738622482e-09</v>
+        <v>5.117087738622464e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.148635851756135e-09</v>
+        <v>8.148635851756094e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.777698280868066e-09</v>
+        <v>8.77769828086797e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.321446819108683e-09</v>
+        <v>7.32144681910867e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.213906152871061e-09</v>
+        <v>5.21390615287105e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.148787711558267e-09</v>
+        <v>8.148787711558244e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.149009543472309e-09</v>
+        <v>8.149009543472253e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.148805784098182e-09</v>
+        <v>8.148805784098149e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.149605403372247e-09</v>
+        <v>8.149605403372177e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.060768234472316e-09</v>
+        <v>5.060768234472297e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.131610539418714e-08</v>
+        <v>1.131610539418709e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.769370372649319e-09</v>
+        <v>3.769370372649274e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.713821116367924e-09</v>
+        <v>4.713821116367849e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.716307044082946e-09</v>
+        <v>4.71630704408283e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.808845774181506e-09</v>
+        <v>5.808845774181458e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.716101403860388e-09</v>
+        <v>4.716101403860349e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.71608397764037e-09</v>
+        <v>4.716083977640303e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.71630580955055e-09</v>
+        <v>4.716305809550482e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.71610205018026e-09</v>
+        <v>4.716102050180224e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.71630580955055e-09</v>
+        <v>4.716305809550482e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.167648217747187e-09</v>
+        <v>3.523944747149989e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.71630580955055e-09</v>
+        <v>4.716305809550482e-09</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.181470436559196e-09</v>
+        <v>2.181470436559188e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.392255241094004e-10</v>
+        <v>9.392255241093975e-10</v>
       </c>
       <c r="D8" t="n">
-        <v>1.277913540657842e-09</v>
+        <v>1.277913540657831e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.22693997160444e-09</v>
+        <v>1.226939971604435e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.22693997160444e-09</v>
+        <v>1.226939971604435e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.253572058282459e-09</v>
+        <v>1.253572058282463e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.289945830037511e-09</v>
+        <v>1.289945830037504e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.22693997160444e-09</v>
+        <v>1.226939971604435e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.509532778306433e-09</v>
+        <v>1.509532778306432e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.429502900515277e-09</v>
+        <v>2.429502900515227e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.265168072802811e-09</v>
+        <v>1.26516807280281e-09</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.185560100316303e-09</v>
+        <v>2.185560100316292e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>9.645150901928102e-10</v>
+        <v>9.645150901928077e-10</v>
       </c>
       <c r="D9" t="n">
-        <v>1.31719534893137e-09</v>
+        <v>1.317195348931364e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.267758912135928e-09</v>
+        <v>1.267758912135922e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.267758912135928e-09</v>
+        <v>1.267758912135922e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.283336830215993e-09</v>
+        <v>1.283336830215983e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.32217021305758e-09</v>
+        <v>1.322170213057579e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.267758912135928e-09</v>
+        <v>1.267758912135922e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.55028355254921e-09</v>
+        <v>1.550283552549194e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>2.4380387455204e-09</v>
+        <v>2.438038745520371e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.305937806456274e-09</v>
+        <v>1.305937806456263e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.495144453265475e-09</v>
+        <v>3.495144453265471e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.281277789411396e-09</v>
+        <v>5.281277789411369e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>6.645782238016192e-09</v>
+        <v>6.645782238016185e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.951332916584697e-09</v>
+        <v>6.951332916584626e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.951332916584697e-09</v>
+        <v>6.951332916584626e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.170464679596012e-09</v>
+        <v>6.17046467959601e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>6.841004302082344e-09</v>
+        <v>6.841004302082328e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.951332916584697e-09</v>
+        <v>6.951332916584626e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>7.803424262218736e-09</v>
+        <v>7.803424262218726e-09</v>
       </c>
       <c r="K2" t="n">
         <v>5.789481337305359e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>7.728001760523211e-09</v>
+        <v>7.728001760523209e-09</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.353949350272452e-10</v>
+        <v>9.353949350272432e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.064064278539278e-10</v>
+        <v>9.064064278539279e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.353949350272452e-10</v>
+        <v>9.353949350272432e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.363508354878133e-10</v>
+        <v>9.363508354878108e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.363508354878139e-10</v>
+        <v>9.363508354878108e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.351336677108416e-10</v>
+        <v>9.351336677108373e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.353949350272452e-10</v>
+        <v>9.353949350272432e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.349337838304369e-10</v>
+        <v>9.34933783830433e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.353949350272454e-10</v>
+        <v>9.353949350272432e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.353949350272452e-10</v>
+        <v>9.353949350272432e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.353949350272452e-10</v>
+        <v>9.353949350272432e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.43046428768795e-09</v>
+        <v>3.246427232398649e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.42273549461399e-09</v>
+        <v>1.422735494613991e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.431716188173602e-09</v>
+        <v>1.43171691295431e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.409642801899616e-09</v>
+        <v>1.409642801899615e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.431311600043478e-09</v>
+        <v>1.431311600043477e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.246165965082235e-09</v>
+        <v>1.430203020371548e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.30289872889666e-09</v>
+        <v>3.302898728896654e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.245966081201831e-09</v>
+        <v>1.430003136491145e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.484385096810358e-09</v>
+        <v>3.276889464119026e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.430848471047846e-09</v>
+        <v>1.430848471047852e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.431295675939364e-09</v>
+        <v>1.431295675939363e-09</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.309366828890561e-09</v>
+        <v>5.309366828890556e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.306869780135838e-09</v>
+        <v>5.306869780135842e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.309202384116091e-09</v>
+        <v>5.3092023841161e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.310820677839048e-09</v>
+        <v>5.310820677839046e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.310820677839048e-09</v>
+        <v>5.310820677839046e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.309105561574144e-09</v>
+        <v>5.309105561574155e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.309366828890561e-09</v>
+        <v>5.309366828890556e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.308905677693746e-09</v>
+        <v>5.308905677693745e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.309366828890561e-09</v>
+        <v>5.309366828890556e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.309366828890561e-09</v>
+        <v>5.309366828890556e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.309366828890561e-09</v>
+        <v>5.309366828890556e-09</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.037312294426537e-09</v>
+        <v>5.037312294426529e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.015246047477808e-09</v>
+        <v>8.015246047468247e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.632589054432016e-09</v>
+        <v>8.632589054431998e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.202557300296462e-09</v>
+        <v>7.20255730029644e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.132483571364464e-09</v>
+        <v>5.132483571364456e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.014859749821772e-09</v>
+        <v>8.014859749821769e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.015121017143598e-09</v>
+        <v>8.015121017143588e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.014659865941378e-09</v>
+        <v>8.014659865941364e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.015706242140434e-09</v>
+        <v>8.015706242140418e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.981997968569132e-09</v>
+        <v>4.981997968569125e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.112569122859032e-08</v>
+        <v>1.11256912285903e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4675,34 +4675,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.632901435527647e-09</v>
+        <v>3.63290143552763e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.538108037127996e-09</v>
+        <v>4.538108037127977e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.540606322169065e-09</v>
+        <v>4.540606322169044e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.587615034318076e-09</v>
+        <v>5.587615034318054e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.540143307463168e-09</v>
+        <v>4.540143307463163e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.540343818566292e-09</v>
+        <v>4.540343818566285e-09</v>
       </c>
       <c r="H7" t="n">
         <v>4.540605085882691e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.540143934685898e-09</v>
+        <v>4.540143934685876e-09</v>
       </c>
       <c r="J7" t="n">
         <v>4.540605085882691e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.993340991792224e-09</v>
+        <v>3.993340991792227e-09</v>
       </c>
       <c r="L7" t="n">
         <v>4.540605085882691e-09</v>
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.629259255118627e-09</v>
+        <v>2.629259255118634e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.201164891368335e-10</v>
+        <v>9.201164891368338e-10</v>
       </c>
       <c r="D8" t="n">
-        <v>1.247221209428615e-09</v>
+        <v>1.247221209428617e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.191261144268362e-09</v>
+        <v>1.191261144268356e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.191261144268362e-09</v>
+        <v>1.191261144268356e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.270951952282686e-09</v>
+        <v>1.270951952282687e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.257565705381463e-09</v>
+        <v>1.257565705381464e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.191261144268362e-09</v>
+        <v>1.191261144268356e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.458958246507119e-09</v>
+        <v>1.458958246507121e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.396045096282397e-09</v>
+        <v>2.3960450962824e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.233556463819078e-09</v>
+        <v>1.233556463819079e-09</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.62830811225193e-09</v>
+        <v>2.628308112251932e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>9.485670219659152e-10</v>
+        <v>9.48567021965916e-10</v>
       </c>
       <c r="D9" t="n">
-        <v>1.286083932851987e-09</v>
+        <v>1.286083932851989e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.23438299169226e-09</v>
+        <v>1.234382991692251e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.234382991692259e-09</v>
+        <v>1.234382991692251e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.30134610999228e-09</v>
+        <v>1.301346109992281e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.290371554585038e-09</v>
+        <v>1.290371554585036e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.23438299169226e-09</v>
+        <v>1.234382991692251e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.50643090644992e-09</v>
+        <v>1.506430906449923e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>2.404621036321132e-09</v>
+        <v>2.404621036321147e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.276122285234704e-09</v>
+        <v>1.276122285234708e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.101473451462511e-08</v>
+        <v>1.101473451462518e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>6.853647298683094e-09</v>
+        <v>6.85364729868307e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.381277346204406e-08</v>
+        <v>1.381277346204408e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>6.853647298683094e-09</v>
+        <v>6.85364729868307e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.853647298683094e-09</v>
+        <v>6.85364729868307e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.129137082274696e-08</v>
+        <v>1.12913708227468e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.232150764669355e-08</v>
+        <v>2.232150764669352e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>6.853647298683094e-09</v>
+        <v>6.85364729868307e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.332866220390996e-08</v>
+        <v>1.332866220391e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>9.030268345176376e-09</v>
+        <v>9.030268345176274e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>9.329610129824334e-09</v>
+        <v>9.329610129824316e-09</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.93082317023822e-10</v>
+        <v>9.930823170238234e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.786666939771496e-10</v>
+        <v>9.786666939771516e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.93082317023822e-10</v>
+        <v>9.930823170238234e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.84650465569653e-10</v>
+        <v>9.846504655696588e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.846504655696526e-10</v>
+        <v>9.846504655696588e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.927575385396529e-10</v>
+        <v>9.927575385396513e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.93082317023822e-10</v>
+        <v>9.930823170238234e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.922224970009281e-10</v>
+        <v>9.922224970009319e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.93082317023822e-10</v>
+        <v>9.930823170238234e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.93082317023822e-10</v>
+        <v>9.930823170238234e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.93082317023822e-10</v>
+        <v>9.930823170238234e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.535421871413165e-09</v>
+        <v>1.541876601379897e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.531129992763656e-09</v>
+        <v>1.531129992763664e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.549548243154511e-09</v>
+        <v>1.549546875397775e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.50990951756411e-09</v>
+        <v>1.509909517564112e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.540598406190696e-09</v>
+        <v>1.540598406190699e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.535097092928995e-09</v>
+        <v>1.541551822895728e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.520257057153982e-09</v>
+        <v>3.520257057153996e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.534562051390268e-09</v>
+        <v>3.534562051390276e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.521883053075561e-09</v>
+        <v>1.601434864672627e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.539375661636947e-09</v>
+        <v>1.539375661636949e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.547856382972275e-09</v>
+        <v>1.547856382972277e-09</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.757294627112985e-09</v>
+        <v>5.757294627112995e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.756434807090093e-09</v>
+        <v>5.756434807090099e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.757110974900148e-09</v>
+        <v>5.757110974900153e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.756068266478756e-09</v>
+        <v>5.756068266478771e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.756068266478756e-09</v>
+        <v>5.756068266478771e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.756969848628813e-09</v>
+        <v>5.756969848628797e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.757294627112985e-09</v>
+        <v>5.757294627112995e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.756434807090093e-09</v>
+        <v>5.756434807090099e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.757294627112985e-09</v>
+        <v>5.757294627112995e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.757294627112985e-09</v>
+        <v>5.757294627112995e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.757294627112985e-09</v>
+        <v>5.757294627112995e-09</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.584007990192902e-09</v>
+        <v>5.584007990192903e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.895975921147037e-09</v>
+        <v>8.895975921152009e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.583131368149201e-09</v>
+        <v>9.583131368149198e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.98998813892372e-09</v>
+        <v>7.989988138923709e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.688033768923443e-09</v>
+        <v>5.688033768923427e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.89598022609097e-09</v>
+        <v>8.895980226090983e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.896305004574987e-09</v>
+        <v>8.896305004575027e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.895445184552231e-09</v>
+        <v>8.895445184552256e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.896955966307307e-09</v>
+        <v>8.896955966307297e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.522480372578098e-09</v>
+        <v>5.522480372578111e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.235627620629304e-08</v>
+        <v>1.235627620629303e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.346336886626913e-09</v>
+        <v>4.346336886626927e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.444880649506672e-09</v>
+        <v>5.444880649506679e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.445741717930445e-09</v>
+        <v>5.445741717930491e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.713569005735525e-09</v>
+        <v>6.713569005735536e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.444879692828423e-09</v>
+        <v>5.444879692828446e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.445415691045414e-09</v>
+        <v>5.445415691045408e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.445740469529578e-09</v>
+        <v>5.445740469529592e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.444880649506672e-09</v>
+        <v>5.444880649506679e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.445740469529578e-09</v>
+        <v>5.445740469529592e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.808742240977406e-09</v>
+        <v>4.808742240977461e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.445740469529578e-09</v>
+        <v>5.445740469529592e-09</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.423185471034087e-09</v>
+        <v>1.423185471034088e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.41892848624694e-09</v>
+        <v>1.418928486246934e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.362628795209188e-09</v>
+        <v>1.362628795209187e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.41892848624694e-09</v>
+        <v>1.418928486246934e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.41892848624694e-09</v>
+        <v>1.418928486246934e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.421838615044276e-09</v>
+        <v>1.421838615044271e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.221597100373151e-09</v>
+        <v>1.221597100373153e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.41892848624694e-09</v>
+        <v>1.418928486246934e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.389220931494068e-09</v>
+        <v>1.389220931494066e-09</v>
       </c>
       <c r="K8" t="n">
         <v>1.473438069563374e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.484166449703356e-09</v>
+        <v>1.484166449703357e-09</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.513551691434541e-09</v>
+        <v>1.51355169143454e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.45687986324337e-09</v>
+        <v>1.456879863243371e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.488893914611513e-09</v>
+        <v>1.488893914611514e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.45687986324337e-09</v>
+        <v>1.456879863243371e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.45687986324337e-09</v>
+        <v>1.456879863243371e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.510772399689412e-09</v>
+        <v>1.510772399689415e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.431807319583571e-09</v>
+        <v>1.431807319583569e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.45687986324337e-09</v>
+        <v>1.456879863243371e-09</v>
       </c>
       <c r="J9" t="n">
         <v>1.499802239081158e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.534026475749544e-09</v>
+        <v>1.534026475749546e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.538482529891008e-09</v>
+        <v>1.393426679981729e-09</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.380211211204419e-09</v>
+        <v>9.380211211204424e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.900897499743606e-09</v>
+        <v>6.900897499743572e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.223003438241825e-08</v>
+        <v>1.22300343824183e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>6.900897499743606e-09</v>
+        <v>6.900897499743572e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.900897499743606e-09</v>
+        <v>6.900897499743572e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.027352818276185e-08</v>
+        <v>1.027352818276203e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.913675930521508e-08</v>
+        <v>1.913675930521491e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>6.900897499743606e-09</v>
+        <v>6.900897499743572e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.17306096920551e-08</v>
+        <v>1.173060969205511e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.273136371102364e-09</v>
+        <v>8.273136371102357e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>9.912377694927943e-09</v>
+        <v>9.912377694927768e-09</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.425468417385676e-10</v>
+        <v>9.42546841738569e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.310851116645517e-10</v>
+        <v>9.310851116645521e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.42546841738568e-10</v>
+        <v>9.425468417385686e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.36525818535136e-10</v>
+        <v>9.365258185351337e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.36525818535136e-10</v>
+        <v>9.36525818535135e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.422371764020345e-10</v>
+        <v>9.422371764020349e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.42546841738568e-10</v>
+        <v>9.425468417385686e-10</v>
       </c>
       <c r="I3" t="n">
         <v>9.417785872463147e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.42546841738568e-10</v>
+        <v>9.425468417385686e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.42546841738568e-10</v>
+        <v>9.425468417385686e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.42546841738568e-10</v>
+        <v>9.425468417385686e-10</v>
       </c>
     </row>
     <row r="4">
@@ -5347,34 +5347,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.30974991531642e-09</v>
+        <v>1.459664688196435e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.451149041505955e-09</v>
+        <v>1.451149041505952e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.465672102711748e-09</v>
+        <v>1.465672102711736e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.431278736860143e-09</v>
+        <v>1.431278736860142e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.458760386650036e-09</v>
+        <v>1.458760386650038e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.309440249979892e-09</v>
+        <v>1.4593550228599e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.295431769621091e-09</v>
+        <v>3.295431769621094e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.308981660824171e-09</v>
+        <v>3.308981660824165e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.297880183245452e-09</v>
+        <v>1.514550050577642e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.457408761090282e-09</v>
+        <v>1.457408761090283e-09</v>
       </c>
       <c r="L4" t="n">
         <v>1.464634569503708e-09</v>
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.33848586599241e-09</v>
+        <v>5.338485865992414e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.337717611500157e-09</v>
+        <v>5.337717611500155e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.338315065030527e-09</v>
+        <v>5.33831506503053e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.337751527476476e-09</v>
+        <v>5.337751527476473e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.337751527476476e-09</v>
+        <v>5.337751527476473e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.338176200655881e-09</v>
+        <v>5.338176200655877e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.33848586599241e-09</v>
+        <v>5.338485865992412e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.337717611500157e-09</v>
+        <v>5.337717611500155e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.33848586599241e-09</v>
+        <v>5.338485865992412e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.33848586599241e-09</v>
+        <v>5.338485865992412e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.33848586599241e-09</v>
+        <v>5.338485865992412e-09</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.123834782635132e-09</v>
+        <v>5.123834782635142e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.142892389538739e-09</v>
+        <v>8.142892389538757e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.768827115064865e-09</v>
+        <v>8.768827115064875e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.317093071656063e-09</v>
+        <v>7.317093071656065e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.218885843936941e-09</v>
+        <v>5.218885843936953e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.142511049742998e-09</v>
+        <v>8.142511049743006e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.142820715079343e-09</v>
+        <v>8.142820715079357e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.142052460587282e-09</v>
+        <v>8.142052460587287e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.143414032715347e-09</v>
+        <v>8.143414032715367e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.067755568959105e-09</v>
+        <v>5.067755568959112e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.129640396537939e-08</v>
+        <v>1.129640396537941e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.896314631386438e-09</v>
+        <v>3.896314631386434e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.870092649809766e-09</v>
+        <v>4.87009264980977e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.870862068278737e-09</v>
+        <v>4.870862068278735e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.994698390621172e-09</v>
+        <v>5.994698390621181e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.870091812509689e-09</v>
+        <v>4.870091812509693e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.870551238965486e-09</v>
+        <v>4.870551238965491e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.870860904302022e-09</v>
+        <v>4.870860904302034e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.870092649809766e-09</v>
+        <v>4.87009264980977e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.870860904302022e-09</v>
+        <v>4.870860904302034e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.643732889129126e-09</v>
+        <v>4.306205456000375e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.870860904302022e-09</v>
+        <v>4.870860904302034e-09</v>
       </c>
     </row>
     <row r="8">
@@ -5510,34 +5510,34 @@
         <v>1.417682539942872e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.36834823929567e-09</v>
+        <v>1.368348239295671e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.345563676002936e-09</v>
+        <v>1.345563676002931e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.36834823929567e-09</v>
+        <v>1.368348239295671e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.36834823929567e-09</v>
+        <v>1.368348239295671e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.396205184191691e-09</v>
+        <v>1.396205184191689e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.228446395324647e-09</v>
+        <v>1.228446395324649e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.36834823929567e-09</v>
+        <v>1.368348239295671e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.375223794506486e-09</v>
+        <v>1.375223794506487e-09</v>
       </c>
       <c r="K8" t="n">
         <v>1.440794929066863e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.42619214656806e-09</v>
+        <v>1.426192146568061e-09</v>
       </c>
     </row>
     <row r="9">
@@ -5550,34 +5550,34 @@
         <v>1.493757613925079e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.414980644552351e-09</v>
+        <v>1.414980644552352e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.464390277169335e-09</v>
+        <v>1.464390277169334e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.414980644552351e-09</v>
+        <v>1.414980644552352e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.414980644552351e-09</v>
+        <v>1.414980644552352e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.482862893110446e-09</v>
+        <v>1.482862893110445e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.417009536035571e-09</v>
+        <v>1.417009536035574e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.414980644552351e-09</v>
+        <v>1.414980644552352e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.476542263263717e-09</v>
+        <v>1.476542263263719e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.503178481493667e-09</v>
+        <v>1.503178481493668e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.497337770184147e-09</v>
+        <v>1.375586390665336e-09</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.598844497403865e-09</v>
+        <v>8.598844497403889e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>8.145302718929224e-09</v>
+        <v>8.145302718929347e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.121235375938746e-08</v>
+        <v>1.121235375938749e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>8.145302718929224e-09</v>
+        <v>8.145302718929347e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>8.145302718929224e-09</v>
+        <v>8.145302718929347e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>9.796997280368378e-09</v>
+        <v>9.796997280369041e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.671491779419799e-08</v>
+        <v>1.671491779419805e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>8.145302718929224e-09</v>
+        <v>8.145302718929347e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.153208087326022e-08</v>
+        <v>1.153208087326023e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>7.994454124893979e-09</v>
+        <v>7.99445412489397e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>2.311751243700498e-08</v>
+        <v>8.829082634169093e-09</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.407230793422962e-10</v>
+        <v>9.407230793422945e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.328142248181691e-10</v>
+        <v>9.328142248181726e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.407230793422964e-10</v>
+        <v>9.407230793422947e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.380432829796608e-10</v>
+        <v>9.380432829796596e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.380432829796596e-10</v>
+        <v>9.380432829796581e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.404723042726923e-10</v>
+        <v>9.404723042726849e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.407230793422964e-10</v>
+        <v>9.407230793422947e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.403284592562722e-10</v>
+        <v>9.403284592562709e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.407230793422964e-10</v>
+        <v>9.407230793422952e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.407230793422964e-10</v>
+        <v>9.407230793422947e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.407230793422964e-10</v>
+        <v>9.407230793422947e-10</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.463487955394784e-09</v>
+        <v>1.463487955394791e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.459001741029317e-09</v>
+        <v>1.459001741029335e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>3.303037225407911e-09</v>
+        <v>1.468056354286565e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.438916275775603e-09</v>
+        <v>1.43891627577561e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.464011635669831e-09</v>
+        <v>1.464011635669815e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.463237180325177e-09</v>
+        <v>3.307504270381995e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.293559597471219e-09</v>
+        <v>3.293559597471254e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.307360425365574e-09</v>
+        <v>1.463093335308774e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.518435907015038e-09</v>
+        <v>3.296011067809982e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.461313352282115e-09</v>
+        <v>1.461313352282126e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.468235694432025e-09</v>
+        <v>1.468235694432022e-09</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.309595492065201e-09</v>
+        <v>5.309595492065206e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.309200871979172e-09</v>
+        <v>5.309200871979177e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.309424814392325e-09</v>
+        <v>5.309424814392329e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.309783426183899e-09</v>
+        <v>5.309783426183902e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.309783426183899e-09</v>
+        <v>5.309783426183902e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.309344716995591e-09</v>
+        <v>5.309344716995594e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.3095954920652e-09</v>
+        <v>5.309595492065203e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.309200871979172e-09</v>
+        <v>5.309200871979177e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.3095954920652e-09</v>
+        <v>5.309595492065203e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.3095954920652e-09</v>
+        <v>5.309595492065203e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.3095954920652e-09</v>
+        <v>5.309595492065203e-09</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.060831220452806e-09</v>
+        <v>5.060831220452796e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.037696442601222e-09</v>
+        <v>8.037696442601217e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.653808104320974e-09</v>
+        <v>8.653808104320982e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.223624891715533e-09</v>
+        <v>7.22362489171553e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.155217496057251e-09</v>
+        <v>5.155217496057249e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.036484282406926e-09</v>
+        <v>8.036484282406924e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.036735057476408e-09</v>
+        <v>8.036735057476419e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.036340437390513e-09</v>
+        <v>8.036340437390522e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.037319908225592e-09</v>
+        <v>8.037319908225599e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.005552278819584e-09</v>
+        <v>5.0055522788196e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.11453154566237e-08</v>
+        <v>1.114531545662369e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.768780050850842e-09</v>
+        <v>3.768780050850809e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.706333691205468e-09</v>
+        <v>4.706333691205455e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.706729471722695e-09</v>
+        <v>4.706729471722646e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.788706160893232e-09</v>
+        <v>5.788706160893189e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.70633290388479e-09</v>
+        <v>4.706332903884796e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.706477536221921e-09</v>
+        <v>4.706477536221859e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.706728311291498e-09</v>
+        <v>4.706728311291455e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.706333691205468e-09</v>
+        <v>4.706333691205455e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.706728311291498e-09</v>
+        <v>4.706728311291455e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.163277893658081e-09</v>
+        <v>4.163277893658041e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.706728311291498e-09</v>
+        <v>4.706728311291455e-09</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.415352266408604e-09</v>
+        <v>1.415352266408601e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.314649992210385e-09</v>
+        <v>1.31464999221038e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.347245915813567e-09</v>
+        <v>1.347245915813562e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.314649992210385e-09</v>
+        <v>1.31464999221038e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.314649992210385e-09</v>
+        <v>1.31464999221038e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.386563972512619e-09</v>
+        <v>1.386563972512646e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.251517447324646e-09</v>
+        <v>1.251517447324644e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.314649992210385e-09</v>
+        <v>1.31464999221038e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.361443247782389e-09</v>
+        <v>1.361443247782386e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.424010718896227e-09</v>
+        <v>1.424010718896224e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.135776324504385e-09</v>
+        <v>1.135776324504379e-09</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.482090214844402e-09</v>
+        <v>1.482090214844399e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.381790019256934e-09</v>
+        <v>1.381790019256942e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.454356611796357e-09</v>
+        <v>1.454356611796353e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.381790019256934e-09</v>
+        <v>1.381790019256942e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.381790019256934e-09</v>
+        <v>1.381790019256942e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.468407054559338e-09</v>
+        <v>1.468407054559355e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.415649166044286e-09</v>
+        <v>1.415649166044285e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.381790019256934e-09</v>
+        <v>1.381790019256942e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.460209412869921e-09</v>
+        <v>1.46020941286992e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.485623991290848e-09</v>
+        <v>1.485623991290844e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.368542447036366e-09</v>
+        <v>1.368542447036363e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6059,34 +6059,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.570404830672468e-09</v>
+        <v>6.570404830672531e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.848210732924517e-09</v>
+        <v>5.848210732924518e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>7.584191329199376e-09</v>
+        <v>7.58419132919937e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>5.848210732924517e-09</v>
+        <v>5.848210732924518e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>5.848210732924517e-09</v>
+        <v>5.848210732924518e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>7.393565098470073e-09</v>
+        <v>7.393565098470043e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.137243869540512e-08</v>
+        <v>1.137243869540513e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>5.848210732924517e-09</v>
+        <v>5.848210732924518e-09</v>
       </c>
       <c r="J2" t="n">
         <v>1.050430444598417e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>7.072097318994626e-09</v>
+        <v>7.072097318994648e-09</v>
       </c>
       <c r="L2" t="n">
         <v>1.179364329811337e-08</v>
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.106705180566667e-10</v>
+        <v>9.106705180566696e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.007370555923696e-10</v>
+        <v>9.007370555923649e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.106705180566667e-10</v>
+        <v>9.106705180566696e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.060849570192093e-10</v>
+        <v>9.060849570192045e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.060849570192098e-10</v>
+        <v>9.060849570192048e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.103857555599055e-10</v>
+        <v>9.103857555599054e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.106705180566667e-10</v>
+        <v>9.106705180566696e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.100461776541378e-10</v>
+        <v>9.100461776541379e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.106705180566667e-10</v>
+        <v>9.106705180566696e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.106705180566667e-10</v>
+        <v>9.106705180566696e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.106705180566667e-10</v>
+        <v>9.106705180566696e-10</v>
       </c>
     </row>
     <row r="4">
@@ -6139,34 +6139,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.487857713889635e-09</v>
+        <v>3.408206935268432e-09</v>
       </c>
       <c r="C4" t="n">
         <v>1.481866634426377e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>3.405910440140174e-09</v>
+        <v>3.405910440140168e-09</v>
       </c>
       <c r="E4" t="n">
         <v>1.461534946544503e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.487288715624988e-09</v>
+        <v>1.487288715624982e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.487572951392869e-09</v>
+        <v>3.407922172771664e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.394835467718049e-09</v>
+        <v>1.489523398629824e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.487233373487106e-09</v>
+        <v>3.407582594865895e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.398665507089392e-09</v>
+        <v>3.39866550708938e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.487521211613154e-09</v>
+        <v>1.487521211613152e-09</v>
       </c>
       <c r="L4" t="n">
         <v>1.489371005624552e-09</v>
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.455188182153096e-09</v>
+        <v>5.455188182153088e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.454563841750564e-09</v>
+        <v>5.454563841750547e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.455006898097646e-09</v>
+        <v>5.455006898097638e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.454800976070643e-09</v>
+        <v>5.454800976070635e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.454800976070643e-09</v>
+        <v>5.454800976070635e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.454903419656331e-09</v>
+        <v>5.454903419656323e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.455188182153096e-09</v>
+        <v>5.455188182153088e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.454563841750564e-09</v>
+        <v>5.454563841750547e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.455188182153096e-09</v>
+        <v>5.455188182153088e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.455188182153096e-09</v>
+        <v>5.455188182153088e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.455188182153096e-09</v>
+        <v>5.455188182153088e-09</v>
       </c>
     </row>
     <row r="6">
@@ -6219,34 +6219,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.110903087599596e-09</v>
+        <v>5.110903087599597e-09</v>
       </c>
       <c r="C6" t="n">
         <v>8.132020707445576e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.757957767805758e-09</v>
+        <v>8.757957767805761e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.305729245310649e-09</v>
+        <v>7.305729245310653e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.206279692032468e-09</v>
+        <v>5.206279692032458e-09</v>
       </c>
       <c r="G6" t="n">
         <v>8.131312408993393e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.131597171489976e-09</v>
+        <v>8.13159717148997e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.130972831087633e-09</v>
+        <v>8.130972831087628e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.132190824830299e-09</v>
+        <v>8.132190824830294e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.054792144133328e-09</v>
+        <v>5.054792144133319e-09</v>
       </c>
       <c r="L6" t="n">
         <v>1.128696472881188e-08</v>
@@ -6259,34 +6259,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.001859277686147e-09</v>
+        <v>4.001859277686149e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.009289846602149e-09</v>
+        <v>5.00928984660215e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.009915427239651e-09</v>
+        <v>5.009915427239648e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.172564029325167e-09</v>
+        <v>6.172564029325164e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.009289102953772e-09</v>
+        <v>5.009289102953773e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.009629424507921e-09</v>
+        <v>5.009629424507923e-09</v>
       </c>
       <c r="H7" t="n">
         <v>5.009914187004682e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.009289846602149e-09</v>
+        <v>5.00928984660215e-09</v>
       </c>
       <c r="J7" t="n">
         <v>5.009914187004682e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.425843735246531e-09</v>
+        <v>4.425843735246526e-09</v>
       </c>
       <c r="L7" t="n">
         <v>5.009914187004682e-09</v>
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.388788934226193e-09</v>
+        <v>1.388788934226192e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.276208437445066e-09</v>
+        <v>1.276208437445065e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.363158587700931e-09</v>
+        <v>1.36315858770093e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.276208437445066e-09</v>
+        <v>1.276208437445065e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.276208437445066e-09</v>
+        <v>1.276208437445065e-09</v>
       </c>
       <c r="G8" t="n">
         <v>1.368051224418416e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.293126468911789e-09</v>
+        <v>1.293126468911788e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.276208437445066e-09</v>
+        <v>1.276208437445065e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.310728496082799e-09</v>
+        <v>1.310728496082798e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.37551255669036e-09</v>
+        <v>1.375512556690358e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.330719999445027e-09</v>
+        <v>1.299070701751219e-09</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.41923824577482e-09</v>
+        <v>1.419238245774819e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.302704947661884e-09</v>
+        <v>1.302704947661883e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.408802047750966e-09</v>
+        <v>1.408802047750965e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.302704947661885e-09</v>
+        <v>1.302704947661883e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.302704947661885e-09</v>
+        <v>1.302704947661883e-09</v>
       </c>
       <c r="G9" t="n">
         <v>1.40881966095406e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.380441151711125e-09</v>
+        <v>1.380441151711123e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.302704947661885e-09</v>
+        <v>1.302704947661883e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.387505865569277e-09</v>
+        <v>1.387505865569275e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.413835927532799e-09</v>
+        <v>1.413835927532797e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.382826704839093e-09</v>
+        <v>1.382826704839092e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.347435497817498e-09</v>
+        <v>7.347435497817502e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.012131700272437e-09</v>
+        <v>6.012131700272444e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>6.015556132479079e-09</v>
+        <v>6.015556132479083e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.012131700272437e-09</v>
+        <v>6.012131700272444e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.012131700272437e-09</v>
+        <v>6.012131700272444e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.676419765532833e-09</v>
+        <v>6.676419765533059e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>7.121060643710504e-09</v>
+        <v>7.121060643710506e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.012131700272437e-09</v>
+        <v>6.012131700272444e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.015965757438822e-08</v>
+        <v>1.015965757438824e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>6.869527301634659e-09</v>
+        <v>6.869527301634658e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>8.030860130898668e-09</v>
+        <v>8.030860130898671e-09</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.601473025955889e-10</v>
+        <v>8.601473025955875e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>8.517652847245444e-10</v>
+        <v>8.51765284724545e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>8.601473025955889e-10</v>
+        <v>8.601473025955875e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>8.566161372054138e-10</v>
+        <v>8.56616137205413e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>8.566161372054169e-10</v>
+        <v>8.56616137205414e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>8.598692079781933e-10</v>
+        <v>8.598692079781946e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>8.601473025955889e-10</v>
+        <v>8.601473025955875e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>8.595594228275291e-10</v>
+        <v>8.595594228275295e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>8.601473025955889e-10</v>
+        <v>8.601473025955875e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.601473025955889e-10</v>
+        <v>8.601473025955875e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>8.601473025955889e-10</v>
+        <v>8.601473025955875e-10</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.185320325867273e-09</v>
+        <v>3.185320325867274e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.400861165107994e-09</v>
+        <v>1.400861165107999e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.40355256478915e-09</v>
+        <v>1.403551340945979e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.381722254182328e-09</v>
+        <v>1.381722254182329e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.404794071737695e-09</v>
+        <v>1.404794071737694e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.404929946612301e-09</v>
+        <v>3.185042231249879e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.40539232021581e-09</v>
+        <v>3.172447350679323e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.404620161461638e-09</v>
+        <v>3.184732446099213e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.176517474915609e-09</v>
+        <v>1.457932722418236e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.405562978516041e-09</v>
+        <v>1.405562978516039e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.405321404439292e-09</v>
+        <v>1.40532140443929e-09</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.037489194300491e-09</v>
+        <v>5.037489194300482e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.036901314532426e-09</v>
+        <v>5.036901314532418e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.037321305201708e-09</v>
+        <v>5.037321305201701e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.037183481085591e-09</v>
+        <v>5.037183481085583e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.037183481085591e-09</v>
+        <v>5.037183481085583e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.03721109968309e-09</v>
+        <v>5.037211099683079e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.037489194300491e-09</v>
+        <v>5.037489194300482e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.036901314532426e-09</v>
+        <v>5.036901314532418e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.037489194300491e-09</v>
+        <v>5.037489194300482e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.037489194300491e-09</v>
+        <v>5.037489194300482e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.037489194300491e-09</v>
+        <v>5.037489194300482e-09</v>
       </c>
     </row>
     <row r="6">
@@ -6615,34 +6615,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.643190494798038e-09</v>
+        <v>4.643190494798033e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>7.367669370660267e-09</v>
+        <v>7.367669370660263e-09</v>
       </c>
       <c r="D6" t="n">
         <v>7.932091124219602e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>6.622514044870445e-09</v>
+        <v>6.622514044870448e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>4.729219302974456e-09</v>
+        <v>4.729219302974463e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>7.366963324814134e-09</v>
+        <v>7.366963324814138e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>7.367241419431472e-09</v>
+        <v>7.367241419431486e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>7.366653539663472e-09</v>
+        <v>7.36665353966347e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>7.367776773824939e-09</v>
+        <v>7.367776773824948e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.592589850317399e-09</v>
+        <v>4.592589850317398e-09</v>
       </c>
       <c r="L6" t="n">
         <v>1.021274039195008e-08</v>
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.560490435941787e-09</v>
+        <v>3.560490435941786e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.446128035980267e-09</v>
+        <v>4.446128035980275e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.446717093275618e-09</v>
+        <v>4.446717093275637e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.468813759886125e-09</v>
+        <v>5.468813759886133e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.446127433391847e-09</v>
+        <v>4.446127433391852e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.446437821130924e-09</v>
+        <v>4.446437821130935e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.446715915748302e-09</v>
+        <v>4.446715915748317e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.446128035980267e-09</v>
+        <v>4.446128035980275e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.446715915748302e-09</v>
+        <v>4.446715915748317e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.912401225252592e-09</v>
+        <v>3.933233887535907e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.446715915748302e-09</v>
+        <v>4.446715915748317e-09</v>
       </c>
     </row>
     <row r="8">
@@ -6710,7 +6710,7 @@
         <v>1.203387045452729e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.325857018975628e-09</v>
+        <v>1.325857018975625e-09</v>
       </c>
       <c r="H8" t="n">
         <v>1.328979862143125e-09</v>
@@ -6722,10 +6722,10 @@
         <v>1.248114434309938e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.320598924000407e-09</v>
+        <v>1.320598924000406e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.324346814460175e-09</v>
+        <v>1.307886039731296e-09</v>
       </c>
     </row>
     <row r="9">
@@ -6735,19 +6735,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.360873049305022e-09</v>
+        <v>1.360873049305024e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.239894765619185e-09</v>
+        <v>1.239894765619186e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.374475892327363e-09</v>
+        <v>1.374475892327364e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.239894765619185e-09</v>
+        <v>1.239894765619186e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.239894765619185e-09</v>
+        <v>1.239894765619186e-09</v>
       </c>
       <c r="G9" t="n">
         <v>1.364766345641332e-09</v>
@@ -6756,16 +6756,16 @@
         <v>1.368013279188237e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.239894765619185e-09</v>
+        <v>1.239894765619186e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.335055725170115e-09</v>
+        <v>1.335055725170114e-09</v>
       </c>
       <c r="K9" t="n">
         <v>1.364516468391879e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.366113100484593e-09</v>
+        <v>1.359420037873465e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.553317424277744e-09</v>
+        <v>8.553317424277722e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.426897077150781e-09</v>
+        <v>6.426897077150905e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>7.004890094333788e-09</v>
+        <v>7.004890094333762e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.426897077150781e-09</v>
+        <v>6.426897077150905e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.426897077150781e-09</v>
+        <v>6.426897077150905e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.954894526542683e-09</v>
+        <v>6.954894526542564e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>6.827707042570495e-09</v>
+        <v>6.827707042570464e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.426897077150781e-09</v>
+        <v>6.426897077150905e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.61320531380344e-08</v>
+        <v>1.613205313803434e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>6.912919018147376e-09</v>
+        <v>6.912919018147344e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>8.505424767682648e-09</v>
+        <v>8.50101346282741e-09</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.620602495948456e-10</v>
+        <v>8.620602495948404e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>8.536909855137682e-10</v>
+        <v>8.536909855137633e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>8.62060249594846e-10</v>
+        <v>8.620602495948403e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>8.585912532506783e-10</v>
+        <v>8.585912532506747e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>8.585912532506765e-10</v>
+        <v>8.585912532506747e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>8.617839990864914e-10</v>
+        <v>8.617839990864856e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>8.620602495948456e-10</v>
+        <v>8.620602495948403e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>8.61484108755614e-10</v>
+        <v>8.614841087556076e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>8.620602495948456e-10</v>
+        <v>8.620602495948404e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.620602495948456e-10</v>
+        <v>8.620602495948403e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>8.620602495948456e-10</v>
+        <v>8.620602495948403e-10</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.411368583125157e-09</v>
+        <v>1.41136858312515e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.406758189697051e-09</v>
+        <v>1.406758189697033e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.410656528894222e-09</v>
+        <v>1.410656528894213e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.387207094455315e-09</v>
+        <v>1.387207094455308e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.410742716425347e-09</v>
+        <v>1.410742716425334e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.197718966845463e-09</v>
+        <v>1.411092332616796e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.179033833538839e-09</v>
+        <v>3.17903383353883e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.410792442285928e-09</v>
+        <v>1.410792442285918e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.182693108105705e-09</v>
+        <v>1.465911524520897e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.410820629802003e-09</v>
+        <v>1.410820629801999e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.411323379571556e-09</v>
+        <v>1.411323379571549e-09</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.029058383225577e-09</v>
+        <v>5.029058383225562e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.02848224238635e-09</v>
+        <v>5.028482242386333e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.028890831340988e-09</v>
+        <v>5.028890831340977e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.028754520436626e-09</v>
+        <v>5.028754520436607e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.028754520436626e-09</v>
+        <v>5.028754520436607e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.028782132717225e-09</v>
+        <v>5.028782132717208e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.029058383225577e-09</v>
+        <v>5.029058383225562e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.02848224238635e-09</v>
+        <v>5.028482242386333e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.029058383225577e-09</v>
+        <v>5.029058383225562e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.029058383225577e-09</v>
+        <v>5.029058383225562e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.029058383225577e-09</v>
+        <v>5.029058383225562e-09</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.613445911800363e-09</v>
+        <v>4.613445911800351e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>7.318112502379549e-09</v>
+        <v>7.318112502379531e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>7.878428503424381e-09</v>
+        <v>7.878428503424363e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>6.578376648079266e-09</v>
+        <v>6.57837664807926e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>4.698852404352971e-09</v>
+        <v>4.698852404352964e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>7.31741033310364e-09</v>
+        <v>7.317410333103625e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>7.31768658361207e-09</v>
+        <v>7.317686583612066e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>7.317110442772772e-09</v>
+        <v>7.317110442772748e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>7.318218044707382e-09</v>
+        <v>7.318218044707356e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.563213252937934e-09</v>
+        <v>4.563213252937923e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.014249209053686e-08</v>
+        <v>1.014249209053685e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.467244637906399e-09</v>
+        <v>3.467244637906375e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.32670990917759e-09</v>
+        <v>4.32670990917756e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.327287228830757e-09</v>
+        <v>4.32728722883073e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.319179818302171e-09</v>
+        <v>5.319179818302145e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.326709340977197e-09</v>
+        <v>4.326709340977163e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.327009799508461e-09</v>
+        <v>4.327009799508432e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.32728605001682e-09</v>
+        <v>4.327286050016784e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.32670990917759e-09</v>
+        <v>4.32670990917756e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.32728605001682e-09</v>
+        <v>4.327286050016784e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.808758024474616e-09</v>
+        <v>3.808758024474582e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.32728605001682e-09</v>
+        <v>4.327286050016784e-09</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.274900263501113e-09</v>
+        <v>1.274900263501109e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.186880756415793e-09</v>
+        <v>1.186880756415788e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.313917388480347e-09</v>
+        <v>1.313917388480342e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.186880756415793e-09</v>
+        <v>1.186880756415788e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.186880756415793e-09</v>
+        <v>1.186880756415788e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.31483900895377e-09</v>
+        <v>1.314839008953767e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.334425624792733e-09</v>
+        <v>1.33442562479273e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.186880756415793e-09</v>
+        <v>1.186880756415788e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.099834440508997e-09</v>
+        <v>1.099834440508994e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.312814175920208e-09</v>
+        <v>1.312814175920202e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.293125482811893e-09</v>
+        <v>1.301981150485822e-09</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.343066501276012e-09</v>
+        <v>1.343066501276007e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.22965002817849e-09</v>
+        <v>1.229650028178483e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.358960745372562e-09</v>
+        <v>1.358960745372556e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.22965002817849e-09</v>
+        <v>1.229650028178483e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.22965002817849e-09</v>
+        <v>1.229650028178483e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.357464792664213e-09</v>
+        <v>1.357464792664209e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.367389947168221e-09</v>
+        <v>1.367389947168215e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.22965002817849e-09</v>
+        <v>1.229650028178483e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.271885226269437e-09</v>
+        <v>1.271885226269433e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.358514250827935e-09</v>
+        <v>1.358514250827932e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.354185219923354e-09</v>
+        <v>1.35418521992335e-09</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.597917580912217e-09</v>
+        <v>8.597917580912214e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.356666149219436e-09</v>
+        <v>6.356666149219432e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.294856997556221e-08</v>
+        <v>1.294856997556222e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>6.356666149219436e-09</v>
+        <v>6.356666149219432e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.356666149219436e-09</v>
+        <v>6.356666149219432e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.023044399017442e-08</v>
+        <v>1.023044399017391e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.065504370980245e-08</v>
+        <v>2.065504370980223e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>6.356666149219436e-09</v>
+        <v>6.356666149219432e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.065258088624609e-08</v>
+        <v>1.065258088624607e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.360451809732614e-09</v>
+        <v>8.360451809732596e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>2.471262416274977e-08</v>
+        <v>8.92915276340468e-09</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.406313779379868e-10</v>
+        <v>9.406313779379877e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>9.272952900809384e-10</v>
+        <v>9.272952900809365e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.406313779379868e-10</v>
+        <v>9.406313779379877e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>9.329724035929008e-10</v>
+        <v>9.32972403592901e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.329724035929008e-10</v>
+        <v>9.329724035928911e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.402801333375674e-10</v>
+        <v>9.402801333375602e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>9.406313779379868e-10</v>
+        <v>9.406313779379877e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>9.395895611911638e-10</v>
+        <v>9.395895611911601e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.406313779379868e-10</v>
+        <v>9.406313779379877e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>9.406313779379868e-10</v>
+        <v>9.406313779379877e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>9.406313779379868e-10</v>
+        <v>9.406313779379877e-10</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.51128155081565e-09</v>
+        <v>1.511281550815652e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.501280118649932e-09</v>
+        <v>1.501280118649916e-09</v>
       </c>
       <c r="D4" t="n">
         <v>1.519622197432531e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.480665441564897e-09</v>
+        <v>1.480665441564906e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.509919980234178e-09</v>
+        <v>1.509919980234179e-09</v>
       </c>
       <c r="G4" t="n">
         <v>3.463886672827494e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.453507079978694e-09</v>
+        <v>3.453507079978682e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.463196100681085e-09</v>
+        <v>3.463196100681086e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.455094126721479e-09</v>
+        <v>3.45509412672147e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.509351813859069e-09</v>
+        <v>1.509351813859073e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.516482586225136e-09</v>
+        <v>1.516482586225134e-09</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.563590782002523e-09</v>
+        <v>5.563590782002518e-09</v>
       </c>
       <c r="C5" t="n">
         <v>5.5625489652557e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.563408795221247e-09</v>
+        <v>5.563408795221241e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.562408691447833e-09</v>
+        <v>5.562408691447814e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.562408691447833e-09</v>
+        <v>5.562408691447814e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.563239537402105e-09</v>
+        <v>5.563239537402095e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.563590782002523e-09</v>
+        <v>5.563590782002518e-09</v>
       </c>
       <c r="I5" t="n">
         <v>5.5625489652557e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.563590782002523e-09</v>
+        <v>5.563590782002518e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.563590782002523e-09</v>
+        <v>5.563590782002518e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.563590782002523e-09</v>
+        <v>5.563590782002518e-09</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.283311943157422e-09</v>
+        <v>5.283311943157408e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.409341001267289e-09</v>
+        <v>8.409341001262381e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.0579458707353e-09</v>
+        <v>9.057945870735271e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.554186148493208e-09</v>
+        <v>7.554186148493198e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.381395868467289e-09</v>
+        <v>5.381395868467272e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.40932303026725e-09</v>
+        <v>8.409323030267243e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.409674274867564e-09</v>
+        <v>8.409674274867561e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.408632458120854e-09</v>
+        <v>8.408632458120821e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.410288695070857e-09</v>
+        <v>8.410288695070855e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.225238157735419e-09</v>
+        <v>5.225238157735415e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.16754211528956e-08</v>
+        <v>1.167542115289555e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.159734629251731e-09</v>
+        <v>4.159734629251727e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.208720925908724e-09</v>
+        <v>5.208720925908734e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.209763945250743e-09</v>
+        <v>5.209763945250739e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.420431060866442e-09</v>
+        <v>6.42043106086642e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.208720021237565e-09</v>
+        <v>5.208720021237575e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.209411498055123e-09</v>
+        <v>5.209411498055118e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.209762742655547e-09</v>
+        <v>5.20976274265559e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.208720925908724e-09</v>
+        <v>5.208720925908734e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.209762742655547e-09</v>
+        <v>5.20976274265559e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.601372835777751e-09</v>
+        <v>4.601372835777745e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.209762742655547e-09</v>
+        <v>5.20976274265559e-09</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.392792533653582e-09</v>
+        <v>1.39279253365358e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.324024674877777e-09</v>
+        <v>1.324024674877774e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.28740049866091e-09</v>
+        <v>1.287400498660906e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.324024674877777e-09</v>
+        <v>1.324024674877774e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.324024674877777e-09</v>
+        <v>1.324024674877774e-09</v>
       </c>
       <c r="G8" t="n">
         <v>1.355301707001609e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.141061408923658e-09</v>
+        <v>1.141061408923661e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.324024674877777e-09</v>
+        <v>1.324024674877774e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.359887553369016e-09</v>
+        <v>1.359887553369013e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.399500869719535e-09</v>
+        <v>1.399500869719534e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.10206968320755e-09</v>
+        <v>1.102069683207549e-09</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.450981717523481e-09</v>
+        <v>1.45098171752348e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.356671716266518e-09</v>
+        <v>1.356671716266515e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.408062479637661e-09</v>
+        <v>1.40806247963766e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.356671716266518e-09</v>
+        <v>1.356671716266515e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.356671716266518e-09</v>
+        <v>1.356671716266515e-09</v>
       </c>
       <c r="G9" t="n">
         <v>1.433519592526357e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.348808793021888e-09</v>
+        <v>1.348808793021887e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.356671716266518e-09</v>
+        <v>1.356671716266515e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.437641934362958e-09</v>
+        <v>1.437641934362955e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.453720525760199e-09</v>
+        <v>1.453720525760197e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.332890855275442e-09</v>
+        <v>1.456084587831941e-09</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.248213695147272e-09</v>
+        <v>6.248213695147262e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.819080754183032e-09</v>
+        <v>5.819080754183025e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.033193532371123e-08</v>
+        <v>1.033193532371118e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>5.819080754183032e-09</v>
+        <v>5.819080754183025e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>5.819080754183032e-09</v>
+        <v>5.819080754183025e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>8.117709364201066e-09</v>
+        <v>8.117709364201026e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>8.721624143015253e-09</v>
+        <v>8.721624143015259e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>5.819080754183032e-09</v>
+        <v>5.819080754183025e-09</v>
       </c>
       <c r="J2" t="n">
         <v>1.004544491927911e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>6.236037803633789e-09</v>
+        <v>6.236037803633779e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>7.781803818142619e-09</v>
+        <v>1.710183516096655e-08</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.920599877769784e-10</v>
+        <v>8.9205998777698e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>8.81565115841999e-10</v>
+        <v>8.81565115842001e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>8.920599877769784e-10</v>
+        <v>8.9205998777698e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>8.867013217318458e-10</v>
+        <v>8.86701321731845e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>8.867013217318449e-10</v>
+        <v>8.867013217318452e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>8.917484838256802e-10</v>
+        <v>8.917484838256806e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>8.920599877769784e-10</v>
+        <v>8.9205998777698e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>8.912684870594381e-10</v>
+        <v>8.912684870594371e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>8.920599877769784e-10</v>
+        <v>8.9205998777698e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.920599877769784e-10</v>
+        <v>8.9205998777698e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>8.920599877769784e-10</v>
+        <v>8.9205998777698e-10</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.232269680318497e-09</v>
+        <v>3.232269680318493e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.416946451560688e-09</v>
+        <v>1.416946451560687e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.430386041186545e-09</v>
+        <v>1.430384842559815e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.397690665126002e-09</v>
+        <v>1.397690665125992e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4231023639647e-09</v>
+        <v>1.423102363964701e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.423626548771411e-09</v>
+        <v>3.231958176367207e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.219148769601369e-09</v>
+        <v>3.219148769601349e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.231478179600947e-09</v>
+        <v>3.231478179600956e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.47739933693144e-09</v>
+        <v>1.477399336931437e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.421098641356747e-09</v>
+        <v>1.42109864135673e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.427099148197763e-09</v>
+        <v>1.427099148197754e-09</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.160309928643388e-09</v>
+        <v>5.16030992864338e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.159518427925851e-09</v>
+        <v>5.159518427925839e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.160140802230102e-09</v>
+        <v>5.160140802230104e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.159627816491229e-09</v>
+        <v>5.15962781649121e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.159627816491229e-09</v>
+        <v>5.15962781649121e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.159998424692098e-09</v>
+        <v>5.159998424692089e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.160309928643388e-09</v>
+        <v>5.16030992864338e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.159518427925851e-09</v>
+        <v>5.159518427925839e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.160309928643388e-09</v>
+        <v>5.16030992864338e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.160309928643388e-09</v>
+        <v>5.16030992864338e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.160309928643388e-09</v>
+        <v>5.16030992864338e-09</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.845530689472128e-09</v>
+        <v>4.845530689472122e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>7.695058352771295e-09</v>
+        <v>7.695058352771285e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.28582355254944e-09</v>
+        <v>8.285823552549442e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>6.915624095814378e-09</v>
+        <v>6.915624095814367e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>4.935228260994251e-09</v>
+        <v>4.935228260994246e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>7.694661601274359e-09</v>
+        <v>7.694661601274343e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>7.694973105225479e-09</v>
+        <v>7.694973105225457e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>7.694181604508114e-09</v>
+        <v>7.694181604508104e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>7.695533102670372e-09</v>
+        <v>7.695533102670347e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.792600833665174e-09</v>
+        <v>4.792600833665161e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.067145397531364e-08</v>
+        <v>1.067145397531362e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.702402247060112e-09</v>
+        <v>3.702402247060111e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.625701506239002e-09</v>
+        <v>4.625701506239013e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.626494220708582e-09</v>
+        <v>4.626494220708595e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.69208291618194e-09</v>
+        <v>5.692082916181938e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.625700842003031e-09</v>
+        <v>4.625700842003041e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.626181503005251e-09</v>
+        <v>4.626181503005236e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.626493006956548e-09</v>
+        <v>4.626493006956532e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.625701506239002e-09</v>
+        <v>4.625701506239013e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.626493006956548e-09</v>
+        <v>4.626493006956532e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.462897476051301e-09</v>
+        <v>4.091071701987563e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.626493006956548e-09</v>
+        <v>4.626493006956532e-09</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.407094104488715e-09</v>
+        <v>1.407094104488712e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.290541311360127e-09</v>
+        <v>1.290541311360124e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.295277051929484e-09</v>
+        <v>1.295277051929478e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.290541311360127e-09</v>
+        <v>1.290541311360124e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.290541311360127e-09</v>
+        <v>1.290541311360124e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.357029948268145e-09</v>
+        <v>1.35702994826814e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.360016327264188e-09</v>
+        <v>1.360016327264185e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.290541311360127e-09</v>
+        <v>1.290541311360124e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.325716277731283e-09</v>
+        <v>1.325716277731281e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.405459764023224e-09</v>
+        <v>1.405459764023221e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.18925167827763e-09</v>
+        <v>1.189251678277626e-09</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.438507555870309e-09</v>
+        <v>1.438507555870305e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.322123885244188e-09</v>
+        <v>1.322123885244183e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.392970399765484e-09</v>
+        <v>1.392970399765482e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.322123885244188e-09</v>
+        <v>1.322123885244183e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.322123885244188e-09</v>
+        <v>1.322123885244183e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.416053622678657e-09</v>
+        <v>1.416053622678653e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.419455308071966e-09</v>
+        <v>1.419455308071964e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.322123885244188e-09</v>
+        <v>1.322123885244183e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.405426045875273e-09</v>
+        <v>1.40542604587527e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.437846454203287e-09</v>
+        <v>1.437846454203284e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.350010399610464e-09</v>
+        <v>1.350010399610462e-09</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen human toxicity carcinogenic results.xlsx
+++ b/Results/Hydrogen/hydrogen human toxicity carcinogenic results.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,320 +511,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.29954651056357e-08</v>
+        <v>1.648898195727284e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>8.58041907819554e-09</v>
+        <v>1.564766777223816e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.50944179551744e-08</v>
+        <v>1.65080181374483e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>8.58041907819554e-09</v>
+        <v>1.564766777223816e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>8.58041907819554e-09</v>
+        <v>1.564766777223816e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.246447976248566e-08</v>
+        <v>1.644228052292029e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>2.565290456453527e-08</v>
+        <v>1.65920080462301e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>8.58041907819554e-09</v>
+        <v>1.564766777223816e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.367320129959212e-08</v>
+        <v>1.64880037429942e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>1.055521772573471e-08</v>
+        <v>1.646153879894205e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>3.056744720014586e-08</v>
+        <v>1.645703962390302e-09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.066905063684551e-09</v>
+        <v>1.656878482163377e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>1.052805798886896e-09</v>
+        <v>1.576000910305287e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.066905063684551e-09</v>
+        <v>1.656878482163377e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>1.05923453399717e-09</v>
+        <v>1.576000910305287e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.05923453399717e-09</v>
+        <v>1.576000910305287e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.066635895851772e-09</v>
+        <v>1.653193292680843e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>1.066905063684551e-09</v>
+        <v>1.656878482163377e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0664085175847e-09</v>
+        <v>1.576000910305287e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>1.066905063684551e-09</v>
+        <v>1.656878482163377e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>1.066905063684551e-09</v>
+        <v>1.656878482163377e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>1.066905063684551e-09</v>
+        <v>1.656878482163377e-09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.642253693357425e-09</v>
+        <v>1.299546510563572e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.632858079981056e-09</v>
+        <v>8.580419078195537e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.649377298367111e-09</v>
+        <v>1.509441795517439e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.609866355836165e-09</v>
+        <v>8.580419078195537e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.641813903005797e-09</v>
+        <v>8.580419078195537e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.789572712620438e-09</v>
+        <v>1.246447976248572e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.773948477211244e-09</v>
+        <v>2.565290456453552e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.789345334353367e-09</v>
+        <v>8.580419078195537e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.77499515234612e-09</v>
+        <v>1.367320129959214e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.640430573383064e-09</v>
+        <v>1.055521772573473e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.648814904429587e-09</v>
+        <v>3.056744720014595e-08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.234532964107402e-09</v>
+        <v>1.06690506368455e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>6.234036418007556e-09</v>
+        <v>1.052805798886897e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>6.234335687057969e-09</v>
+        <v>1.06690506368455e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>6.233754290479973e-09</v>
+        <v>1.059234533997168e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>6.233754290479973e-09</v>
+        <v>1.059234533997167e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>6.234263796274615e-09</v>
+        <v>1.066635895851772e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>6.234532964107402e-09</v>
+        <v>1.06690506368455e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>6.234036418007556e-09</v>
+        <v>1.066408517584696e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>6.234532964107402e-09</v>
+        <v>1.06690506368455e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>6.234532964107402e-09</v>
+        <v>1.06690506368455e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>6.234532964107402e-09</v>
+        <v>1.06690506368455e-09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.111760113646131e-09</v>
+        <v>1.642253693357427e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>9.754950721184343e-09</v>
+        <v>1.632858079981062e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.051015225595222e-08</v>
+        <v>1.649377298367114e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>8.758499611803896e-09</v>
+        <v>1.609866355836161e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>6.226690224070021e-09</v>
+        <v>1.6418139030058e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>9.754484618213559e-09</v>
+        <v>3.789572712620436e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>9.754753786046328e-09</v>
+        <v>3.773948477211247e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>9.754257239946479e-09</v>
+        <v>3.789345334353363e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>9.75546973921084e-09</v>
+        <v>3.774995152346124e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>6.04408963582346e-09</v>
+        <v>1.64043057338307e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.356016529952757e-08</v>
+        <v>1.648814904429588e-09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.933311445719954e-09</v>
+        <v>6.2345329641074e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>6.19253357200799e-09</v>
+        <v>6.234036418007543e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>6.193031439043045e-09</v>
+        <v>6.234335687057966e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>7.646222081669607e-09</v>
+        <v>6.233754290479973e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>6.192532514390761e-09</v>
+        <v>6.233754290479973e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>6.192760950275061e-09</v>
+        <v>6.234263796274615e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>6.193030118107843e-09</v>
+        <v>6.2345329641074e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>6.19253357200799e-09</v>
+        <v>6.234036418007543e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>6.193030118107843e-09</v>
+        <v>6.2345329641074e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.606819108225801e-09</v>
+        <v>6.2345329641074e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>6.193030118107843e-09</v>
+        <v>6.2345329641074e-09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.449147922548417e-09</v>
+        <v>6.111760113646131e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.458616191296102e-09</v>
+        <v>9.754950721184355e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.40938857524388e-09</v>
+        <v>1.051015225595224e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.458616191296102e-09</v>
+        <v>8.758499611803894e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.458616191296102e-09</v>
+        <v>6.226690224070015e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.466925974400101e-09</v>
+        <v>9.754484618213567e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.241408949265444e-09</v>
+        <v>9.754753786046338e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.458616191296102e-09</v>
+        <v>9.754257239946483e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.452869524231939e-09</v>
+        <v>9.755469739210845e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.506841466777264e-09</v>
+        <v>6.044089635823458e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.518345503244035e-09</v>
+        <v>1.356016529952758e-08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4.933311445719945e-09</v>
+      </c>
+      <c r="C9" t="n">
+        <v>6.192533572007981e-09</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.193031439043045e-09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>7.646222081669596e-09</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6.192532514390757e-09</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.192760950275059e-09</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6.193030118107839e-09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6.192533572007981e-09</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6.193030118107839e-09</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.6068191082258e-09</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6.193030118107839e-09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.449147922548417e-09</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.458616191296102e-09</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.409388575243883e-09</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.458616191296102e-09</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.458616191296102e-09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.4669259744001e-09</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.24140894926544e-09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.458616191296102e-09</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.45286952423194e-09</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.506841466777265e-09</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.518345503244036e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1.554380129104461e-09</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>1.55438012910446e-09</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.511356355991733e-09</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D11" t="n">
         <v>1.538193117392921e-09</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E11" t="n">
         <v>1.511356355991733e-09</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>1.511356355991733e-09</v>
       </c>
-      <c r="G9" t="n">
-        <v>1.559475828875566e-09</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.470160843131608e-09</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>1.559475828875567e-09</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.470160843131606e-09</v>
+      </c>
+      <c r="I11" t="n">
         <v>1.511356355991733e-09</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J11" t="n">
         <v>1.555975648302641e-09</v>
       </c>
-      <c r="K9" t="n">
-        <v>1.577886559753922e-09</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="K11" t="n">
+        <v>1.577886559753923e-09</v>
+      </c>
+      <c r="L11" t="n">
         <v>1.439569211839654e-09</v>
       </c>
     </row>
@@ -839,7 +919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,321 +987,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.152655218333446e-09</v>
+        <v>1.458897493390886e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.446420499375454e-09</v>
+        <v>1.341941306479402e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>6.845144606231492e-09</v>
+        <v>1.459755729829715e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.446420499375454e-09</v>
+        <v>1.341941306479402e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.446420499375454e-09</v>
+        <v>1.341941306479402e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.934582966240326e-09</v>
+        <v>1.456572207646247e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>7.507415735920832e-09</v>
+        <v>1.459803084770378e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.446420499375454e-09</v>
+        <v>1.341941306479402e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.394480882034654e-08</v>
+        <v>1.467365063659643e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>6.405773974726663e-09</v>
+        <v>1.459356589604142e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>8.85163936041545e-09</v>
+        <v>1.460125858378972e-09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.88966864482405e-10</v>
+        <v>1.470517891396934e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.81153202180871e-10</v>
+        <v>1.351125001011973e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>8.88966864482405e-10</v>
+        <v>1.470517891396934e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>8.861357667445785e-10</v>
+        <v>1.351125001011973e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.861357667445763e-10</v>
+        <v>1.351125001011973e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>8.88724238001718e-10</v>
+        <v>1.467349461846079e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>8.88966864482405e-10</v>
+        <v>1.470517891396934e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>8.886135370014463e-10</v>
+        <v>1.351125001011973e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>8.88966864482405e-10</v>
+        <v>1.470517891396934e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>8.88966864482405e-10</v>
+        <v>1.470517891396934e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>8.88966864482405e-10</v>
+        <v>1.470517891396934e-09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.423219208120912e-09</v>
+        <v>6.152655218333429e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.420098381792451e-09</v>
+        <v>6.446420499375471e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>3.217628277491014e-09</v>
+        <v>6.845144606231496e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.400534192846535e-09</v>
+        <v>6.446420499375471e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.423525783400481e-09</v>
+        <v>6.446420499375471e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.216972706142561e-09</v>
+        <v>6.934582966240374e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.206835997012276e-09</v>
+        <v>7.507415735920835e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.422865880639953e-09</v>
+        <v>6.446420499375471e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.477989672740518e-09</v>
+        <v>1.394480882034651e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.422595012091088e-09</v>
+        <v>6.405773974726663e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.423943741970443e-09</v>
+        <v>8.851639360415457e-09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.136544478668704e-09</v>
+        <v>8.889668644824048e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.136191151187736e-09</v>
+        <v>8.811532021808702e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>5.136375631446379e-09</v>
+        <v>8.889668644824048e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>5.136568389627597e-09</v>
+        <v>8.861357667445755e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>5.136568389627599e-09</v>
+        <v>8.861357667445759e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>5.136301852188017e-09</v>
+        <v>8.887242380017167e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>5.136544478668704e-09</v>
+        <v>8.889668644824048e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>5.136191151187736e-09</v>
+        <v>8.886135370014452e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>5.136544478668704e-09</v>
+        <v>8.889668644824048e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>5.136544478668704e-09</v>
+        <v>8.889668644824048e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>5.136544478668704e-09</v>
+        <v>8.889668644824048e-10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.790340094905912e-09</v>
+        <v>1.423219208120911e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>7.604772162165584e-09</v>
+        <v>1.420098381792444e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.187430656144971e-09</v>
+        <v>3.21762827749102e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>6.835097743513809e-09</v>
+        <v>1.400534192846544e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>4.87950120680694e-09</v>
+        <v>1.42352578340048e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>7.603757328386898e-09</v>
+        <v>3.216972706142558e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>7.603999954867446e-09</v>
+        <v>3.206835997012274e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>7.603646627386621e-09</v>
+        <v>1.422865880639953e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>7.604552920000282e-09</v>
+        <v>1.47798967274051e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.738074918444994e-09</v>
+        <v>1.422595012091086e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.054310295332836e-08</v>
+        <v>1.42394374197044e-09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.564266935396436e-09</v>
+        <v>5.1365444786687e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.449491128659587e-09</v>
+        <v>5.136191151187737e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.449845641746096e-09</v>
+        <v>5.136375631446376e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.471429105076533e-09</v>
+        <v>5.136568389627591e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.44949050705323e-09</v>
+        <v>5.136568389627591e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.44960182965986e-09</v>
+        <v>5.136301852188015e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.449844456140552e-09</v>
+        <v>5.1365444786687e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.449491128659587e-09</v>
+        <v>5.136191151187737e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.449844456140552e-09</v>
+        <v>5.1365444786687e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.936737861351302e-09</v>
+        <v>5.1365444786687e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.449844456140552e-09</v>
+        <v>5.1365444786687e-09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.392774089582688e-09</v>
+        <v>4.790340094905916e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.257617455384261e-09</v>
+        <v>7.604772162165589e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.374841642141159e-09</v>
+        <v>8.187430656144959e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.257617455384261e-09</v>
+        <v>6.835097743513814e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.257617455384261e-09</v>
+        <v>4.879501206806937e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.372312248365962e-09</v>
+        <v>7.603757328386888e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.375739125118933e-09</v>
+        <v>7.603999954867449e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.257617455384261e-09</v>
+        <v>7.603646627386613e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.217356284659512e-09</v>
+        <v>7.60455292000029e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.383253901965217e-09</v>
+        <v>4.738074918444991e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.35228764972163e-09</v>
+        <v>1.054310295332836e-08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.564266935396431e-09</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.449491128659585e-09</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.449845641746099e-09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5.471429105076525e-09</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.449490507053239e-09</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.449601829659858e-09</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.449844456140551e-09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.449491128659585e-09</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.449844456140551e-09</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.936737861351299e-09</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.449844456140551e-09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.39277408958269e-09</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.257617455384261e-09</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.37484164214116e-09</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.257617455384261e-09</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.257617455384261e-09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.372312248365965e-09</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.375739125118935e-09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.257617455384261e-09</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.217356284659512e-09</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.383253901965219e-09</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.352287649721634e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1.423523815810607e-09</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>1.423523815810608e-09</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.299395075227926e-09</v>
       </c>
-      <c r="D9" t="n">
-        <v>1.41622273151622e-09</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>1.416222731516222e-09</v>
+      </c>
+      <c r="E11" t="n">
         <v>1.299395075227926e-09</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>1.299395075227926e-09</v>
       </c>
-      <c r="G9" t="n">
-        <v>1.413329972647164e-09</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.416678444071878e-09</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>1.413329972647166e-09</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.416678444071881e-09</v>
+      </c>
+      <c r="I11" t="n">
         <v>1.299395075227926e-09</v>
       </c>
-      <c r="J9" t="n">
-        <v>1.352175725815943e-09</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="J11" t="n">
+        <v>1.352175725815944e-09</v>
+      </c>
+      <c r="K11" t="n">
         <v>1.419651196318877e-09</v>
       </c>
-      <c r="L9" t="n">
-        <v>1.407127139396286e-09</v>
+      <c r="L11" t="n">
+        <v>1.407127139396288e-09</v>
       </c>
     </row>
   </sheetData>
@@ -1235,7 +1395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,320 +1463,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.705149371202224e-09</v>
+        <v>2.036295993487051e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>8.147422426420949e-09</v>
+        <v>1.053920488598582e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.074514259321809e-08</v>
+        <v>1.477148115619092e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>7.608503305611621e-09</v>
+        <v>1.41664932758424e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>7.608503305611621e-09</v>
+        <v>1.41664932758424e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>8.661931898979385e-09</v>
+        <v>1.378217528220136e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.493546653471008e-08</v>
+        <v>1.480262313862427e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>7.608503305611621e-09</v>
+        <v>1.41664932758424e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>9.776903941730558e-09</v>
+        <v>1.751565026167544e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>7.86149601429333e-09</v>
+        <v>2.566645866399643e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.059028494736099e-08</v>
+        <v>1.447634658756105e-09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.991114687471709e-10</v>
+        <v>2.057225041751946e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>9.718564113222651e-10</v>
+        <v>1.056810742903723e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.991114687471698e-10</v>
+        <v>1.484084665611831e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>9.925040086332901e-10</v>
+        <v>1.426381988922498e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.925040086332895e-10</v>
+        <v>1.426381988922498e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.988703473128529e-10</v>
+        <v>1.386132679750858e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.991114687471709e-10</v>
+        <v>1.484084665611831e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.988007546303612e-10</v>
+        <v>1.426381988922498e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.991114687471709e-10</v>
+        <v>1.764352996970068e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.991114687471698e-10</v>
+        <v>2.594165984888682e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.991114687471698e-10</v>
+        <v>1.455522514038701e-09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.445097611726895e-09</v>
+        <v>4.705149371202232e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.507797421790874e-09</v>
+        <v>8.147422426420978e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.519381318877185e-09</v>
+        <v>1.074514259321809e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.488557985439438e-09</v>
+        <v>7.608503305611682e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.513665206806093e-09</v>
+        <v>7.608503305611682e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.513310784740766e-09</v>
+        <v>8.661931898979492e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.492187545975845e-09</v>
+        <v>1.493546653471025e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.513241192058279e-09</v>
+        <v>7.608503305611682e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.474888784139449e-09</v>
+        <v>9.776903941730603e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.513974938790864e-09</v>
+        <v>7.861496014293338e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.514684300234086e-09</v>
+        <v>1.059028494736099e-08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.759421579209073e-09</v>
+        <v>9.99111468747168e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.756915729426642e-09</v>
+        <v>9.718564113222667e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>5.759244312345997e-09</v>
+        <v>9.991114687471682e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>5.759076999020353e-09</v>
+        <v>9.92504008633287e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>5.759076999020353e-09</v>
+        <v>9.925040086332881e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>5.759180457774748e-09</v>
+        <v>9.988703473128457e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>5.759421579209073e-09</v>
+        <v>9.991114687471682e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>5.759110865092268e-09</v>
+        <v>9.988007546303601e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>5.759421579209073e-09</v>
+        <v>9.99111468747168e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>5.759421579209073e-09</v>
+        <v>9.991114687471682e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>5.759421579209073e-09</v>
+        <v>9.991114687471682e-10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.641320112042503e-09</v>
+        <v>3.445097611726896e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.997025964599098e-09</v>
+        <v>1.507797421790869e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.69485293658687e-09</v>
+        <v>1.519381318877186e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>8.0808762816277e-09</v>
+        <v>1.488557985439438e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.747518132956383e-09</v>
+        <v>1.5136652068061e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.998440943087499e-09</v>
+        <v>1.513310784740773e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.998682064523345e-09</v>
+        <v>3.492187545975842e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.99837135040502e-09</v>
+        <v>1.513241192058287e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.999341882820392e-09</v>
+        <v>3.474888784139445e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.578955390062201e-09</v>
+        <v>1.513974938790861e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.250572736237575e-08</v>
+        <v>1.51468430023409e-09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.308813937324299e-09</v>
+        <v>5.759421579209078e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.399099199333494e-09</v>
+        <v>5.756915729426636e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.401606322867917e-09</v>
+        <v>5.75924431234601e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.662352212490805e-09</v>
+        <v>5.759076999020354e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.401293498161734e-09</v>
+        <v>5.759076999020354e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.401363927681604e-09</v>
+        <v>5.759180457774748e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.401605049115933e-09</v>
+        <v>5.759421579209078e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.401294334999122e-09</v>
+        <v>5.75911086509227e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.401605049115933e-09</v>
+        <v>5.759421579209078e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.768438122957256e-09</v>
+        <v>5.759421579209078e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.401605049115934e-09</v>
+        <v>5.759421579209078e-09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.977658719212758e-09</v>
+        <v>5.641320112042497e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.385962189496377e-10</v>
+        <v>8.997025964599123e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.310921830494816e-09</v>
+        <v>9.69485293658686e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.327091377002484e-09</v>
+        <v>8.080876281627688e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.327091377002484e-09</v>
+        <v>5.747518132956372e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.264924162552473e-09</v>
+        <v>8.998440943087506e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.250220062239468e-09</v>
+        <v>8.998682064523332e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.327091377002484e-09</v>
+        <v>8.998371350405031e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.623013354628265e-09</v>
+        <v>8.999341882820378e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.488245033429892e-09</v>
+        <v>5.578955390062203e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.314025059128039e-09</v>
+        <v>1.250572736237572e-08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4.308813937324316e-09</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5.399099199333499e-09</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.401606322867915e-09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6.662352212490819e-09</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5.401293498161757e-09</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5.401363927681617e-09</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.401605049115942e-09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.401294334999136e-09</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5.401605049115942e-09</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.768438122957255e-09</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.401605049115942e-09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.977658719212759e-09</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.385962189496382e-10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.310921830494817e-09</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.327091377002483e-09</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.327091377002483e-09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.264924162552469e-09</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.250220062239465e-09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.327091377002483e-09</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.623013354628269e-09</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.488245033429892e-09</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.314025059128041e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.000093063168894e-09</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>2.000093063168893e-09</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.000132503472136e-09</v>
       </c>
-      <c r="D9" t="n">
-        <v>1.398358473803637e-09</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.371471782740227e-09</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.371471782740227e-09</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.323067266626244e-09</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="D11" t="n">
+        <v>1.398358473803639e-09</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.371471782740229e-09</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.371471782740229e-09</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.323067266626243e-09</v>
+      </c>
+      <c r="H11" t="n">
         <v>1.373853174045729e-09</v>
       </c>
-      <c r="I9" t="n">
-        <v>1.371471782740227e-09</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.687255038479304e-09</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.518451495935851e-09</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="I11" t="n">
+        <v>1.371471782740229e-09</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.687255038479305e-09</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.51845149593585e-09</v>
+      </c>
+      <c r="L11" t="n">
         <v>1.38325286584612e-09</v>
       </c>
     </row>
@@ -1631,7 +1871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1699,321 +1939,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.649903507523077e-09</v>
+        <v>2.035468567605356e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.936980283221793e-09</v>
+        <v>1.05367499247735e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>8.976720864376835e-09</v>
+        <v>1.478888378847308e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.977181543024407e-09</v>
+        <v>1.420890474344863e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.977181543024407e-09</v>
+        <v>1.420890474344863e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>7.233579185441143e-09</v>
+        <v>1.377354444342989e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.069220189058076e-08</v>
+        <v>1.479787861204899e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.977181543024407e-09</v>
+        <v>1.420890474344863e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>7.666036525938868e-09</v>
+        <v>1.754949627369265e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>6.339543512911576e-09</v>
+        <v>2.564902920967604e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>7.614449101890361e-09</v>
+        <v>1.449497514516134e-09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.765260641460046e-10</v>
+        <v>2.057336045530726e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>9.494980151763187e-10</v>
+        <v>1.057486211276143e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.765260641460046e-10</v>
+        <v>1.487296654679356e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>9.725795616776076e-10</v>
+        <v>1.43097679597143e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.725795616776076e-10</v>
+        <v>1.43097679597143e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.763138236583622e-10</v>
+        <v>1.386396421395612e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.765260641460046e-10</v>
+        <v>1.487296654679356e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.764010220260783e-10</v>
+        <v>1.43097679597143e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.765260641460046e-10</v>
+        <v>1.769618791633426e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.765260641460046e-10</v>
+        <v>2.593723195711934e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.765260641460046e-10</v>
+        <v>1.459947141891942e-09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.289663938983824e-09</v>
+        <v>3.649903507523064e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.447845580769012e-09</v>
+        <v>6.936980283221738e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>3.325963151022572e-09</v>
+        <v>8.976720864376832e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.431253825608551e-09</v>
+        <v>6.97718154302439e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.454199004332869e-09</v>
+        <v>6.97718154302439e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.289451698496178e-09</v>
+        <v>7.233579185441056e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.34201441230271e-09</v>
+        <v>1.069220189058067e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4533873819373e-09</v>
+        <v>6.97718154302439e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.508341155347814e-09</v>
+        <v>7.666036525938846e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.453351040025353e-09</v>
+        <v>6.339543512911567e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.454048535458815e-09</v>
+        <v>7.614449101890356e-09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.506031446339984e-09</v>
+        <v>9.765260641459965e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.50354152551099e-09</v>
+        <v>9.494980151763165e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>5.505863787879712e-09</v>
+        <v>9.765260641459965e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>5.506410929939204e-09</v>
+        <v>9.725795616776018e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>5.506410929939204e-09</v>
+        <v>9.725795616775985e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>5.505819205852334e-09</v>
+        <v>9.763138236583562e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>5.506031446339984e-09</v>
+        <v>9.765260641459965e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>5.505906404220057e-09</v>
+        <v>9.76401022026076e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>5.506031446339984e-09</v>
+        <v>9.765260641459965e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>5.506031446339984e-09</v>
+        <v>9.765260641459965e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>5.506031446339984e-09</v>
+        <v>9.765260641459965e-10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.399325144219067e-09</v>
+        <v>3.289663938983824e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.601911595925996e-09</v>
+        <v>1.447845580769031e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.267398692935112e-09</v>
+        <v>3.325963151022575e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.727894566077791e-09</v>
+        <v>1.43125382560856e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.501155154726298e-09</v>
+        <v>1.454199004332887e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.602867140832931e-09</v>
+        <v>3.289451698496173e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.603079381324502e-09</v>
+        <v>3.342014412302696e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.602954339200632e-09</v>
+        <v>1.453387381937296e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.603709011247968e-09</v>
+        <v>1.508341155347813e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.339813764417768e-09</v>
+        <v>1.45335104002535e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.194966857594983e-08</v>
+        <v>1.454048535458831e-09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.968987594808188e-09</v>
+        <v>5.506031446339975e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.965374762127121e-09</v>
+        <v>5.503541525510982e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.967865912470102e-09</v>
+        <v>5.505863787879698e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.120422804768688e-09</v>
+        <v>5.506410929939194e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.967738898732332e-09</v>
+        <v>5.506410929939194e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.96765244246848e-09</v>
+        <v>5.505819205852334e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.967864682956142e-09</v>
+        <v>5.506031446339975e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.967739640836201e-09</v>
+        <v>5.505906404220045e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.967864682956142e-09</v>
+        <v>5.506031446339975e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.389111892319093e-09</v>
+        <v>5.506031446339975e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.967864682956142e-09</v>
+        <v>5.506031446339975e-09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.997243147498465e-09</v>
+        <v>5.399325144219054e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.58211971973739e-10</v>
+        <v>8.601911595925968e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.343855619169024e-09</v>
+        <v>9.267398692935096e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.337648808767791e-09</v>
+        <v>7.727894566077772e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.337648808767791e-09</v>
+        <v>5.501155154726289e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.288588812052948e-09</v>
+        <v>8.602867140832901e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.32813174802077e-09</v>
+        <v>8.603079381324483e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.337648808767791e-09</v>
+        <v>8.602954339200627e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.665612086077075e-09</v>
+        <v>8.603709011247968e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.515111603012084e-09</v>
+        <v>5.339813764417746e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.36977931607148e-09</v>
+        <v>1.194966857594982e-08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.96898759480815e-09</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.965374762127086e-09</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.967865912470067e-09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6.120422804768673e-09</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.967738898732297e-09</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.96765244246847e-09</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.967864682956096e-09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.967739640836176e-09</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.967864682956096e-09</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.389111892319069e-09</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.967864682956096e-09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.997243147498461e-09</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.582119719737384e-10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.343855619169018e-09</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.33764880876779e-09</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.33764880876779e-09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.288588812052962e-09</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.32813174802077e-09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.33764880876779e-09</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.665612086077069e-09</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.515111603012046e-09</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.369779316071477e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.008126107495971e-09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.008504897226528e-09</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.413622250570649e-09</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.378425942748562e-09</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.378425942748562e-09</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.33285167039773e-09</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.407367321446783e-09</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.378425942748562e-09</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.707626244891425e-09</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.529134395768902e-09</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.408470866420013e-09</v>
+      <c r="B11" t="n">
+        <v>2.00812610749597e-09</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.008504897226527e-09</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.413622250570645e-09</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.378425942748558e-09</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.378425942748558e-09</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.332851670397732e-09</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.407367321446781e-09</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.378425942748558e-09</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.707626244891422e-09</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.529134395768914e-09</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.40847086642001e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2027,7 +2347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2095,321 +2415,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.278724687007106e-09</v>
+        <v>2.027612191051784e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.255136845954071e-09</v>
+        <v>1.043243690181324e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>8.015934967764487e-09</v>
+        <v>1.465517054006878e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.816720254253664e-09</v>
+        <v>1.408444092473898e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.816720254253664e-09</v>
+        <v>1.408444092473898e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.619960314773467e-09</v>
+        <v>1.36533432057075e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>8.747127956377257e-09</v>
+        <v>1.465499782827377e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.816720254253664e-09</v>
+        <v>1.408444092473898e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>6.114269869759888e-09</v>
+        <v>1.737986825953135e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>5.843367797364207e-09</v>
+        <v>2.549353422531288e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>7.298337715844215e-09</v>
+        <v>1.438143535422576e-09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.743286397400236e-10</v>
+        <v>2.049820251284196e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>9.455034819507149e-10</v>
+        <v>1.047716281435264e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.743286397400242e-10</v>
+        <v>1.474886965591295e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>9.716589691762424e-10</v>
+        <v>1.418554766624582e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.716589691762432e-10</v>
+        <v>1.418554766624582e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.741277792721152e-10</v>
+        <v>1.374929322336618e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.743286397400242e-10</v>
+        <v>1.474886965591295e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.74277291573049e-10</v>
+        <v>1.418554766624582e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.743286397400242e-10</v>
+        <v>1.754180464927055e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.743286397400242e-10</v>
+        <v>2.578548863696944e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.743286397400242e-10</v>
+        <v>1.448778601414707e-09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.453518488667854e-09</v>
+        <v>3.278724687007109e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.447144808306886e-09</v>
+        <v>6.255136845954058e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.457339436948652e-09</v>
+        <v>8.015934967764492e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.43201544643231e-09</v>
+        <v>6.816720254253661e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.454481491560354e-09</v>
+        <v>6.816720254253661e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.287029879098322e-09</v>
+        <v>6.619960314773393e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.345905935290281e-09</v>
+        <v>8.747127956377261e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.287179391399257e-09</v>
+        <v>6.816720254253661e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.318020900627597e-09</v>
+        <v>6.114269869759894e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.453303232084249e-09</v>
+        <v>5.843367797364202e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.454003292498771e-09</v>
+        <v>7.298337715844216e-09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.488348667206626e-09</v>
+        <v>9.743286397400234e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.485858510910746e-09</v>
+        <v>9.455034819507161e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>5.4881813725926e-09</v>
+        <v>9.743286397400234e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>5.489130968878827e-09</v>
+        <v>9.716589691762461e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>5.489130968878827e-09</v>
+        <v>9.716589691762467e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>5.488147806738715e-09</v>
+        <v>9.741277792721117e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>5.488348667206626e-09</v>
+        <v>9.743286397400234e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>5.488297319039643e-09</v>
+        <v>9.742772915730518e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>5.488348667206626e-09</v>
+        <v>9.743286397400234e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>5.488348667206626e-09</v>
+        <v>9.743286397400234e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>5.488348667206626e-09</v>
+        <v>9.743286397400234e-10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.375966186106685e-09</v>
+        <v>1.453518488667856e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.563317250348349e-09</v>
+        <v>1.44714480830689e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.225269645414139e-09</v>
+        <v>1.457339436948644e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.693592958236439e-09</v>
+        <v>1.432015446432313e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.477573214069208e-09</v>
+        <v>1.454481491560359e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.563973127880041e-09</v>
+        <v>3.287029879098327e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.56417398835362e-09</v>
+        <v>3.34590593529029e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.564122640180971e-09</v>
+        <v>3.287179391399261e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.564800562914555e-09</v>
+        <v>3.318020900627605e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.316743589315965e-09</v>
+        <v>1.453303232084337e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.189452363176302e-08</v>
+        <v>1.454003292498775e-09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.843859187745626e-09</v>
+        <v>5.488348667206628e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.805334608812402e-09</v>
+        <v>5.48585851091075e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.807826006566575e-09</v>
+        <v>5.488181372592604e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.920169485072878e-09</v>
+        <v>5.489130968878838e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.807772704120856e-09</v>
+        <v>5.489130968878838e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.807623904640356e-09</v>
+        <v>5.488147806738715e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.807824765108272e-09</v>
+        <v>5.488348667206628e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.807773416941301e-09</v>
+        <v>5.488297319039648e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.807824765108272e-09</v>
+        <v>5.488348667206628e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.226639734091704e-09</v>
+        <v>5.488348667206628e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.807824765108272e-09</v>
+        <v>5.488348667206628e-09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.998494164711012e-09</v>
+        <v>5.375966186106699e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.646433196105499e-10</v>
+        <v>8.56331725034834e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.354867847548695e-09</v>
+        <v>9.22526964541412e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.329083206937384e-09</v>
+        <v>7.693592958236444e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.329083206937384e-09</v>
+        <v>5.477573214069205e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.291634241660456e-09</v>
+        <v>8.563973127880036e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.357554590878291e-09</v>
+        <v>8.564173988353607e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.329083206937384e-09</v>
+        <v>8.564122640180979e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.686097740776559e-09</v>
+        <v>8.564800562914547e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.51197211795962e-09</v>
+        <v>5.316743589315968e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.365256959596995e-09</v>
+        <v>1.189452363176302e-08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.843859187745605e-09</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.805334608812386e-09</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.80782600656656e-09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5.920169485072873e-09</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.80777270412086e-09</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.807623904640348e-09</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.807824765108256e-09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.807773416941285e-09</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.807824765108256e-09</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.226639734091696e-09</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.807824765108256e-09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.998494164711014e-09</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.646433196105499e-10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.354867847548696e-09</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.329083206937382e-09</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.329083206937382e-09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.291634241660454e-09</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.357554590878294e-09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.329083206937382e-09</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.686097740776567e-09</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.511972117959655e-09</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.365256959596996e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.004258658094452e-09</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>2.004258658094453e-09</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.005445227813258e-09</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D11" t="n">
         <v>1.41090797281926e-09</v>
       </c>
-      <c r="E9" t="n">
-        <v>1.367734247687279e-09</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.367734247687279e-09</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.327434793417425e-09</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.41211317841687e-09</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.367734247687279e-09</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.70700896949789e-09</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.51906079105332e-09</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.400140922227838e-09</v>
+      <c r="E11" t="n">
+        <v>1.367734247687277e-09</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.367734247687277e-09</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.327434793417423e-09</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.412113178416869e-09</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.367734247687277e-09</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.707008969497891e-09</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.519060791053321e-09</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.400140922227839e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2423,7 +2823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2491,321 +2891,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.488558305098443e-09</v>
+        <v>2.071006224938011e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.010511810274741e-09</v>
+        <v>1.031651326336339e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>8.821852987044117e-09</v>
+        <v>1.45283293222519e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.919490253056208e-09</v>
+        <v>1.395746716185996e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.919490253056208e-09</v>
+        <v>1.395746716185996e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>7.686288958873723e-09</v>
+        <v>1.366179970822175e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.31034509621987e-08</v>
+        <v>1.456251485762498e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.919490253056208e-09</v>
+        <v>1.395746716185996e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>9.683785272213635e-09</v>
+        <v>1.726491136914413e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>7.089871711000011e-09</v>
+        <v>2.547794621305212e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.097471332451792e-08</v>
+        <v>1.431602861644714e-09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.884448483082794e-10</v>
+        <v>2.09386381172646e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>9.598757480649132e-10</v>
+        <v>1.037667487094808e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.884448483082794e-10</v>
+        <v>1.461586106662864e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>9.849655590049402e-10</v>
+        <v>1.405957587869482e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.849655590049402e-10</v>
+        <v>1.405957587869482e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.88209946660918e-10</v>
+        <v>1.375016963146206e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.884448483082794e-10</v>
+        <v>1.461586106662864e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.88168379296021e-10</v>
+        <v>1.405957587869482e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.884448483082794e-10</v>
+        <v>1.739028616589991e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.884448483082794e-10</v>
+        <v>2.575924538192992e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.884448483082794e-10</v>
+        <v>1.438906613291023e-09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.494435148086263e-09</v>
+        <v>3.488558305098433e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.484526607282423e-09</v>
+        <v>5.010511810274691e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.498276071782072e-09</v>
+        <v>8.821852987044152e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.470971172262234e-09</v>
+        <v>6.919490253056231e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.494969129336284e-09</v>
+        <v>6.919490253056231e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.494200246438903e-09</v>
+        <v>7.686288958873523e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.465271155177414e-09</v>
+        <v>1.310345096219902e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.419834868831e-09</v>
+        <v>6.919490253056231e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.552241712264753e-09</v>
+        <v>9.683785272213682e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.495082363933211e-09</v>
+        <v>7.089871711000025e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.496078528855973e-09</v>
+        <v>1.097471332451808e-08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.738006266485299e-09</v>
+        <v>9.884448483082761e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.735457482590583e-09</v>
+        <v>9.598757480649159e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>5.737829368691308e-09</v>
+        <v>9.884448483082761e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>5.738507840847699e-09</v>
+        <v>9.849655590049599e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>5.738507840847699e-09</v>
+        <v>9.849655590049603e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>5.737771364837942e-09</v>
+        <v>9.882099466609223e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>5.738006266485299e-09</v>
+        <v>9.884448483082761e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>5.737729797473042e-09</v>
+        <v>9.881683792960055e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>5.738006266485299e-09</v>
+        <v>9.884448483082761e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>5.738006266485299e-09</v>
+        <v>9.884448483082761e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>5.738006266485299e-09</v>
+        <v>9.884448483082761e-10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.60670835218927e-09</v>
+        <v>1.494435148086285e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.946471700685646e-09</v>
+        <v>1.484526607282824e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.640112563632043e-09</v>
+        <v>1.498276071782089e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>8.034877422130618e-09</v>
+        <v>1.470971172262245e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.71289627618767e-09</v>
+        <v>1.494969129336316e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.947163763069203e-09</v>
+        <v>1.494200246438987e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.947398664717877e-09</v>
+        <v>3.465271155177317e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.947122195704315e-09</v>
+        <v>3.419834868830888e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.948055206565805e-09</v>
+        <v>1.552241712264794e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.544653314480083e-09</v>
+        <v>1.495082363933204e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.243702904058537e-08</v>
+        <v>1.496078528855971e-09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.251868851098269e-09</v>
+        <v>5.738006266485176e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.32867838451063e-09</v>
+        <v>5.735457482590652e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.331228451259019e-09</v>
+        <v>5.737829368691358e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.576507469379127e-09</v>
+        <v>5.738507840847755e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.330949897980149e-09</v>
+        <v>5.738507840847755e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.330992266757996e-09</v>
+        <v>5.737771364837703e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.33122716840536e-09</v>
+        <v>5.738006266485176e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.3309506993931e-09</v>
+        <v>5.737729797473208e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.331227168405356e-09</v>
+        <v>5.738006266485176e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.705843259953801e-09</v>
+        <v>5.738006266485176e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.331227168405356e-09</v>
+        <v>5.738006266485176e-09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.041277281156253e-09</v>
+        <v>5.6067083521892e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.896256896939151e-10</v>
+        <v>8.946471700685605e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.332574282523663e-09</v>
+        <v>9.640112563632245e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.322134369892253e-09</v>
+        <v>8.034877422130639e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.322134369892253e-09</v>
+        <v>5.712896276187938e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.275402992214552e-09</v>
+        <v>8.947163763069038e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.264791681253995e-09</v>
+        <v>8.94739866471763e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.322134369892253e-09</v>
+        <v>8.947122195704166e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.59944731905274e-09</v>
+        <v>8.948055206565547e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.487465154962063e-09</v>
+        <v>5.544653314479953e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.289464848172471e-09</v>
+        <v>1.243702904058531e-08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4.251868851098174e-09</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5.328678384510558e-09</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.331228451259126e-09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6.576507469379149e-09</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5.330949897980209e-09</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5.330992266758037e-09</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.331227168405467e-09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.330950699393045e-09</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5.331227168405467e-09</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.705843259953744e-09</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.331227168405467e-09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.041277281156277e-09</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.896256896939147e-10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.332574282523622e-09</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.322134369892254e-09</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.322134369892254e-09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.27540299221452e-09</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.26479168125394e-09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.322134369892254e-09</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.599447319052747e-09</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.487465154962097e-09</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.289464848172477e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.047079185945224e-09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.009792155418817e-09</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.394132141105584e-09</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.357606884877644e-09</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.357606884877644e-09</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.320855296597361e-09</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="B11" t="n">
+        <v>2.047079185945207e-09</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.009792155418834e-09</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.394132141105573e-09</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.357606884877696e-09</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.357606884877696e-09</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.320855296597338e-09</v>
+      </c>
+      <c r="H11" t="n">
         <v>1.366709395054845e-09</v>
       </c>
-      <c r="I9" t="n">
-        <v>1.357606884877644e-09</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.662981201715723e-09</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.507545320031858e-09</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.363606382273129e-09</v>
+      <c r="I11" t="n">
+        <v>1.357606884877696e-09</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.662981201715765e-09</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.507545320031871e-09</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.363606382273114e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2819,7 +3299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,321 +3367,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.295826026468636e-09</v>
+        <v>2.066887315607053e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.054963698712062e-09</v>
+        <v>1.007435409707723e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>6.724885518417452e-09</v>
+        <v>1.40645375521501e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.837377314594718e-09</v>
+        <v>1.353205250798999e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.837377314594718e-09</v>
+        <v>1.353205250798999e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.149421928549149e-09</v>
+        <v>1.332533772220813e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>7.052599614001293e-09</v>
+        <v>1.406164787213928e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.837377314594718e-09</v>
+        <v>1.353205250798999e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>7.425673824494431e-09</v>
+        <v>1.660527006366704e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>5.69350373154553e-09</v>
+        <v>2.501225140400281e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>7.898683848843459e-09</v>
+        <v>1.389670165300567e-09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.489173536884162e-10</v>
+        <v>2.08978622697872e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>9.226823990635013e-10</v>
+        <v>1.012798855568867e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.489173536884162e-10</v>
+        <v>1.416491484830604e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>9.476397947509957e-10</v>
+        <v>1.362487815670087e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.476397947509957e-10</v>
+        <v>1.362487815670087e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.487187408774091e-10</v>
+        <v>1.342228383183868e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.489173536884162e-10</v>
+        <v>1.416491484830604e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.488688539930071e-10</v>
+        <v>1.362487815670087e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.489173536884162e-10</v>
+        <v>1.674084498828236e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.489173536884162e-10</v>
+        <v>2.529911495794727e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.489173536884162e-10</v>
+        <v>1.398992113518015e-09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.426215645395613e-09</v>
+        <v>3.295826026468638e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.418858590413593e-09</v>
+        <v>5.054963698712063e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>3.280729115981344e-09</v>
+        <v>6.724885518417452e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.406455524242455e-09</v>
+        <v>6.83737731459473e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.427309415743639e-09</v>
+        <v>6.83737731459473e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.426017032584605e-09</v>
+        <v>6.149421928549168e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.295631677693815e-09</v>
+        <v>7.052599614001299e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.245597889518915e-09</v>
+        <v>6.83737731459473e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.274291625484602e-09</v>
+        <v>7.425673824494401e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.426082537912782e-09</v>
+        <v>5.693503731545544e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.426979967006436e-09</v>
+        <v>7.898683848843452e-09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.416190625375393e-09</v>
+        <v>9.489173536884162e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.413704358611736e-09</v>
+        <v>9.226823990635008e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>5.41602402523496e-09</v>
+        <v>9.489173536884149e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>5.417207915961782e-09</v>
+        <v>9.476397947510015e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>5.417207915961782e-09</v>
+        <v>9.476397947510011e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>5.415992012564382e-09</v>
+        <v>9.487187408774089e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>5.416190625375393e-09</v>
+        <v>9.489173536884162e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>5.416142125679989e-09</v>
+        <v>9.488688539930131e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>5.416190625375393e-09</v>
+        <v>9.489173536884162e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>5.416190625375393e-09</v>
+        <v>9.489173536884162e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>5.416190625375393e-09</v>
+        <v>9.489173536884162e-10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.24525212940288e-09</v>
+        <v>1.426215645395613e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.356016439458127e-09</v>
+        <v>1.418858590413595e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.00183504001346e-09</v>
+        <v>3.280729115981336e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.507272849616033e-09</v>
+        <v>1.406455524242458e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.34456574950663e-09</v>
+        <v>1.427309415743642e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.356464989335455e-09</v>
+        <v>1.42601703258461e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.356663602150453e-09</v>
+        <v>3.295631677693815e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.356615102451045e-09</v>
+        <v>3.245597889518926e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.357275084076365e-09</v>
+        <v>3.2742916254846e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.187456063858695e-09</v>
+        <v>1.426082537912801e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.160679305782924e-08</v>
+        <v>1.426979967006439e-09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.841930511248202e-09</v>
+        <v>5.416190625375391e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.805600192443487e-09</v>
+        <v>5.413704358611732e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.808087705175701e-09</v>
+        <v>5.416024025234971e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.92296171236596e-09</v>
+        <v>5.417207915961788e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.808037278227865e-09</v>
+        <v>5.417207915961788e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.80788784639613e-09</v>
+        <v>5.415992012564382e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.808086459207137e-09</v>
+        <v>5.416190625375391e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.808037959511737e-09</v>
+        <v>5.416142125679985e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.808086459207137e-09</v>
+        <v>5.416190625375391e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.248292432622178e-09</v>
+        <v>5.416190625375391e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.808086459207137e-09</v>
+        <v>5.416190625375391e-09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.037666558803766e-09</v>
+        <v>5.245252129402889e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.575178302587825e-10</v>
+        <v>8.356016439458144e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.327421215936e-09</v>
+        <v>9.00183504001345e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.271969627588067e-09</v>
+        <v>7.50727284961605e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.271969627588068e-09</v>
+        <v>5.34456574950664e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.269535486495101e-09</v>
+        <v>8.356464989335453e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.335116253111503e-09</v>
+        <v>8.35666360215046e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.271969627588067e-09</v>
+        <v>8.356615102451067e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.575092958931605e-09</v>
+        <v>8.357275084076379e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.466425759305564e-09</v>
+        <v>5.187456063858699e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.302308739710452e-09</v>
+        <v>1.160679305782923e-08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.841930511248209e-09</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.805600192443495e-09</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.808087705175706e-09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5.922961712365959e-09</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.808037278227865e-09</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.807887846396147e-09</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.808086459207152e-09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.808037959511755e-09</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.808086459207152e-09</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.248292432622198e-09</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.808086459207152e-09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.037666558803768e-09</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.575178302587846e-10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.327421215936004e-09</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.271969627588068e-09</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.271969627588068e-09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.26953548649511e-09</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.335116253111503e-09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.271969627588068e-09</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.575092958931601e-09</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.466425759305604e-09</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.302308739710454e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.043172700491922e-09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>9.822823670214567e-10</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.36592649901786e-09</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.312019186757336e-09</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.312019186757336e-09</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.299458272568902e-09</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.369138797454261e-09</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.312019186757336e-09</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.615485540246414e-09</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.472338927980658e-09</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.345678922106492e-09</v>
+      <c r="B11" t="n">
+        <v>2.043172700491923e-09</v>
+      </c>
+      <c r="C11" t="n">
+        <v>9.822823670214587e-10</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.365926499017863e-09</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.312019186757333e-09</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.312019186757333e-09</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.299458272568908e-09</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.369138797454262e-09</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.312019186757333e-09</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.615485540246418e-09</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.47233892798069e-09</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.345678922106494e-09</v>
       </c>
     </row>
   </sheetData>
@@ -3215,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3283,321 +3843,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.530837668268711e-09</v>
+        <v>2.085919097032776e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.375530966039335e-09</v>
+        <v>9.922393238540342e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>6.80018961247641e-09</v>
+        <v>1.378389690824577e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.981445024268084e-09</v>
+        <v>1.326472398915341e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.981445024268084e-09</v>
+        <v>1.326472398915341e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.225579647932842e-09</v>
+        <v>1.314970821596279e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>6.851338259433648e-09</v>
+        <v>1.377802657451859e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.981445024268084e-09</v>
+        <v>1.326472398915341e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>7.485966526320102e-09</v>
+        <v>1.626099401647564e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>5.674266997326616e-09</v>
+        <v>2.474411358021444e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>7.829769527524517e-09</v>
+        <v>1.363503229197476e-09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.508140596846759e-10</v>
+        <v>2.108870016282294e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>9.232762526101049e-10</v>
+        <v>9.970107856680602e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.508140596846759e-10</v>
+        <v>1.387906552351362e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>9.51363490940557e-10</v>
+        <v>1.335175119364435e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.513634909405568e-10</v>
+        <v>1.335175119364435e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.506028826584522e-10</v>
+        <v>1.324312786985816e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.508140596846761e-10</v>
+        <v>1.387906552351362e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.506875071412473e-10</v>
+        <v>1.335175119364435e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.508140596846761e-10</v>
+        <v>1.639055548961181e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.508140596846759e-10</v>
+        <v>2.502708495463569e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.508140596846759e-10</v>
+        <v>1.372494852117568e-09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.263862748596403e-09</v>
+        <v>3.530837668268706e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.434739302923285e-09</v>
+        <v>5.37553096603933e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.443157441804012e-09</v>
+        <v>6.800189612476402e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.421397913710422e-09</v>
+        <v>6.981445024268074e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.443213072758616e-09</v>
+        <v>6.981445024268074e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.263651571570479e-09</v>
+        <v>6.225579647933125e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.44251422689404e-09</v>
+        <v>6.851338259433604e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.26373619605296e-09</v>
+        <v>6.981445024268074e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.496485462086125e-09</v>
+        <v>7.485966526320105e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.441873960693876e-09</v>
+        <v>5.674266997326624e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.442772652900659e-09</v>
+        <v>7.829769527524513e-09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.379395349992626e-09</v>
+        <v>9.508140596846856e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.376900828958488e-09</v>
+        <v>9.232762526100943e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>5.379229530503621e-09</v>
+        <v>9.508140596846856e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>5.380964417702937e-09</v>
+        <v>9.513634909405543e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>5.380964417702937e-09</v>
+        <v>9.513634909405535e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>5.379184172966688e-09</v>
+        <v>9.506028826587641e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>5.379395349992626e-09</v>
+        <v>9.508140596846856e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>5.379268797449185e-09</v>
+        <v>9.506875071412419e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>5.379395349992626e-09</v>
+        <v>9.508140596846856e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>5.379395349992626e-09</v>
+        <v>9.508140596846856e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>5.379395349992626e-09</v>
+        <v>9.508140596846856e-10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.177791003873822e-09</v>
+        <v>3.263862748596406e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.242093076557907e-09</v>
+        <v>1.434739302923281e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.877572394709506e-09</v>
+        <v>1.443157441804003e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.406083612575028e-09</v>
+        <v>1.421397913710431e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.275910538195043e-09</v>
+        <v>1.443213072758579e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.241945113079603e-09</v>
+        <v>3.263651571570484e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.242156290111266e-09</v>
+        <v>1.442514226893999e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.242029737562083e-09</v>
+        <v>3.263736196052983e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.242758525971387e-09</v>
+        <v>1.496485462086108e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.120868845408711e-09</v>
+        <v>1.441873960693854e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.144314206991464e-08</v>
+        <v>1.44277265290066e-09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.710070675730428e-09</v>
+        <v>5.379395349992625e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.635445284254577e-09</v>
+        <v>5.376900828958487e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.63794105942754e-09</v>
+        <v>5.379229530503616e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.708554849041652e-09</v>
+        <v>5.380964417702933e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.637812581604684e-09</v>
+        <v>5.380964417702933e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.637728628262771e-09</v>
+        <v>5.379184172966698e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.637939805288676e-09</v>
+        <v>5.379395349992625e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.637813252745263e-09</v>
+        <v>5.379268797449161e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.637939805288676e-09</v>
+        <v>5.379395349992625e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.100329315085406e-09</v>
+        <v>5.379395349992625e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.637939805288676e-09</v>
+        <v>5.379395349992625e-09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.051245681342975e-09</v>
+        <v>5.177791003873809e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.341707970231316e-10</v>
+        <v>8.242093076557907e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.296921629486861e-09</v>
+        <v>8.877572394709476e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.241098031770943e-09</v>
+        <v>7.40608361257502e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.241098031770943e-09</v>
+        <v>5.275910538195037e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.249743106774236e-09</v>
+        <v>8.241945113079574e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.310780162084653e-09</v>
+        <v>8.242156290111256e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.241098031770943e-09</v>
+        <v>8.242029737562089e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.538588215236556e-09</v>
+        <v>8.242758525971384e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.439612699354465e-09</v>
+        <v>5.12086884540871e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.277181713164796e-09</v>
+        <v>1.144314206991463e-08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.710070675730399e-09</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.635445284254572e-09</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.637941059427471e-09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5.708554849041631e-09</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.637812581604655e-09</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.637728628262754e-09</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.637939805288686e-09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.637813252745261e-09</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.637939805288686e-09</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.100329315085382e-09</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.637939805288686e-09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.051245681342973e-09</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.341707970231293e-10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.296921629486859e-09</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.24109803177094e-09</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.24109803177094e-09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.249743106774234e-09</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.310780162084654e-09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.24109803177094e-09</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.538588215236556e-09</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.439612699354465e-09</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.277181713164791e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.05969984099753e-09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>9.636469287614315e-10</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.336991260969486e-09</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.283667024254412e-09</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.283667024254412e-09</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.281041379460535e-09</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="B11" t="n">
+        <v>2.059699840997526e-09</v>
+      </c>
+      <c r="C11" t="n">
+        <v>9.636469287614301e-10</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.336991260969484e-09</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.28366702425441e-09</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.28366702425441e-09</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.281041379460539e-09</v>
+      </c>
+      <c r="H11" t="n">
         <v>1.342709904093281e-09</v>
       </c>
-      <c r="I9" t="n">
-        <v>1.283667024254412e-09</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.58038644463247e-09</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.445702569717411e-09</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.32013544722901e-09</v>
+      <c r="I11" t="n">
+        <v>1.28366702425441e-09</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.580386444632467e-09</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.445702569717418e-09</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.320135447229015e-09</v>
       </c>
     </row>
   </sheetData>
@@ -3611,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3679,321 +4319,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.474762955359477e-09</v>
+        <v>2.077765630497216e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.113561044069018e-09</v>
+        <v>1.026038092426345e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>7.084321299486322e-09</v>
+        <v>1.431671063052631e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>7.011703714517111e-09</v>
+        <v>1.377281881638587e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>7.011703714517111e-09</v>
+        <v>1.377281881638587e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.739838905054027e-09</v>
+        <v>1.352549639205553e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.202175287946247e-08</v>
+        <v>1.435933562304193e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>7.011703714517111e-09</v>
+        <v>1.377281881638587e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>6.791922004049813e-09</v>
+        <v>1.693583360181335e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>6.323934679513944e-09</v>
+        <v>2.527805884986359e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.038832292851579e-08</v>
+        <v>1.414367532025484e-09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.852488872446704e-10</v>
+        <v>2.100773841982794e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>9.573889684218536e-10</v>
+        <v>1.031880740225167e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.852488872446704e-10</v>
+        <v>1.442058781670384e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>9.831365296458137e-10</v>
+        <v>1.387112339005871e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.831365296458137e-10</v>
+        <v>1.387112339005871e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.850430577823202e-10</v>
+        <v>1.362225275019979e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.852488872446704e-10</v>
+        <v>1.442058781670384e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.851547619651123e-10</v>
+        <v>1.387112339005871e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.852488872446704e-10</v>
+        <v>1.70872250607909e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.852488872446704e-10</v>
+        <v>2.556497084119483e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.852488872446704e-10</v>
+        <v>1.421998872417167e-09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.486892543655702e-09</v>
+        <v>3.474762955359472e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.478591936745892e-09</v>
+        <v>5.113561044069025e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.488498309776168e-09</v>
+        <v>7.084321299486298e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.465409428919708e-09</v>
+        <v>7.011703714517105e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.487830437251153e-09</v>
+        <v>7.011703714517105e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.486686714193353e-09</v>
+        <v>6.739838905054364e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.454250490269766e-09</v>
+        <v>1.202175287946242e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.48679841837614e-09</v>
+        <v>7.011703714517105e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.543454412240272e-09</v>
+        <v>6.791922004049801e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.48726904052649e-09</v>
+        <v>6.323934679513926e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.48835733328404e-09</v>
+        <v>1.038832292851577e-08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.72035244852589e-09</v>
+        <v>9.852488872446683e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.717851451673736e-09</v>
+        <v>9.573889684218745e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>5.720175976916804e-09</v>
+        <v>9.852488872446683e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>5.721197081798042e-09</v>
+        <v>9.831365296458108e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>5.721197081798042e-09</v>
+        <v>9.831365296458166e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>5.720146619063561e-09</v>
+        <v>9.850430577823266e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>5.72035244852589e-09</v>
+        <v>9.852488872446683e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>5.720258323246328e-09</v>
+        <v>9.851547619651129e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>5.72035244852589e-09</v>
+        <v>9.852488872446683e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>5.72035244852589e-09</v>
+        <v>9.852488872446683e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>5.72035244852589e-09</v>
+        <v>9.852488872446683e-10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.561841167840713e-09</v>
+        <v>1.486892543655691e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.874253356376118e-09</v>
+        <v>1.4785919367459e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.561986856797773e-09</v>
+        <v>1.488498309776149e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.970311920473842e-09</v>
+        <v>1.465409428919697e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.667433872222243e-09</v>
+        <v>1.487830437251139e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.874779087741709e-09</v>
+        <v>1.486686714193352e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.874984917205287e-09</v>
+        <v>3.454250490269757e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.874890791924474e-09</v>
+        <v>1.486798418376127e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.875636045357866e-09</v>
+        <v>1.54345441224025e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.500297821685366e-09</v>
+        <v>1.487269040526481e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.233584060443571e-08</v>
+        <v>1.488357333284031e-09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.204157171962919e-09</v>
+        <v>5.720352448525876e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.268238116263246e-09</v>
+        <v>5.717851451673726e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.270740373041173e-09</v>
+        <v>5.720175976916785e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.501458093424652e-09</v>
+        <v>5.721197081798042e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.270644205229767e-09</v>
+        <v>5.721197081798042e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.270533283653065e-09</v>
+        <v>5.720146619063539e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.270739113115399e-09</v>
+        <v>5.720352448525876e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.270644987835842e-09</v>
+        <v>5.720258323246314e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.270739113115399e-09</v>
+        <v>5.720352448525876e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.652757877541144e-09</v>
+        <v>5.720352448525876e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.270739113115399e-09</v>
+        <v>5.720352448525876e-09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.048419087079583e-09</v>
+        <v>5.561841167840703e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.814594081110376e-10</v>
+        <v>8.874253356376134e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.353022577395634e-09</v>
+        <v>9.561986856797783e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.301005491085901e-09</v>
+        <v>7.970311920473848e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.301005491085901e-09</v>
+        <v>5.667433872222241e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.283669974378745e-09</v>
+        <v>8.874779087741677e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.267143568626221e-09</v>
+        <v>8.874984917205292e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.301005491085901e-09</v>
+        <v>8.874890791924471e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.63241504892524e-09</v>
+        <v>8.875636045357859e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.485485365572778e-09</v>
+        <v>5.500297821685364e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.284106282528469e-09</v>
+        <v>1.23358406044357e-08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4.204157171962924e-09</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5.268238116263248e-09</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.270740373041174e-09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6.50145809342465e-09</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5.270644205229768e-09</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5.270533283653063e-09</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.27073911311539e-09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.27064498783584e-09</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5.27073911311539e-09</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.652757877541134e-09</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.27073911311539e-09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.04841908707958e-09</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.814594081110502e-10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.353022577395633e-09</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.301005491085896e-09</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.301005491085896e-09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.28366997437874e-09</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.267143568626218e-09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.301005491085896e-09</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.632415048925244e-09</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.485485365572767e-09</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.284106282528464e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.053944050171556e-09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.003096225631158e-09</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.391159306366073e-09</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.338102991428762e-09</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.338102991428762e-09</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.316806727072899e-09</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.356346582947393e-09</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.338102991428762e-09</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.658863223998897e-09</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.495495326746695e-09</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.351625964188516e-09</v>
+      <c r="B11" t="n">
+        <v>2.053944050171549e-09</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.003096225631167e-09</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.391159306366074e-09</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.338102991428753e-09</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.338102991428753e-09</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.316806727072898e-09</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.356346582947389e-09</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.338102991428753e-09</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.658863223998898e-09</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.495495326746685e-09</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.351625964188514e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4007,7 +4727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4075,321 +4795,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.350906603337671e-09</v>
+        <v>2.209970058188156e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.072345611951428e-09</v>
+        <v>9.898936359349336e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>6.713179139907115e-09</v>
+        <v>1.357762243517979e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.829987713126075e-09</v>
+        <v>1.309034034139029e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.829987713126075e-09</v>
+        <v>1.309034034139029e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.108039834250803e-09</v>
+        <v>1.316128908727243e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>6.83899184934061e-09</v>
+        <v>1.357262377631809e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.829987713126075e-09</v>
+        <v>1.309034034139029e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>7.3637733340511e-09</v>
+        <v>1.594837009846543e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>5.827499443030998e-09</v>
+        <v>2.468575463443814e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>7.625342154016909e-09</v>
+        <v>1.347462018739445e-09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.351268240188106e-10</v>
+        <v>2.235118319869503e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>9.083292802760468e-10</v>
+        <v>9.950021570600432e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.351268240188106e-10</v>
+        <v>1.367070926281766e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>9.347342451471707e-10</v>
+        <v>1.317653890098933e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.347342451471707e-10</v>
+        <v>1.317653890098933e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.349049921086092e-10</v>
+        <v>1.32564205572819e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.351268240188106e-10</v>
+        <v>1.367070926281766e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.34923064648527e-10</v>
+        <v>1.317653890098933e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.351268240188106e-10</v>
+        <v>1.607451778851527e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.351268240188106e-10</v>
+        <v>2.496616096221587e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.351268240188106e-10</v>
+        <v>1.356429438627966e-09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.231849326555208e-09</v>
+        <v>3.350906603337683e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.410334659590014e-09</v>
+        <v>5.072345611951423e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.419493891897124e-09</v>
+        <v>6.713179139907106e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.397937378153981e-09</v>
+        <v>6.829987713126073e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.41878695861759e-09</v>
+        <v>6.829987713126073e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.417576586709849e-09</v>
+        <v>6.108039834252301e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2804475689013e-09</v>
+        <v>6.838991849340642e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.231645567184899e-09</v>
+        <v>6.829987713126073e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.471303993792406e-09</v>
+        <v>7.363773334051096e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.418382277352244e-09</v>
+        <v>5.827499443030994e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.418445392300757e-09</v>
+        <v>7.625342154016951e-09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.351226792274944e-09</v>
+        <v>9.351268240188197e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.348742099092316e-09</v>
+        <v>9.083292802760478e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>5.351061408273903e-09</v>
+        <v>9.351268240188197e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>5.35239136188876e-09</v>
+        <v>9.347342451471731e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>5.35239136188876e-09</v>
+        <v>9.347342451471731e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>5.351004960364757e-09</v>
+        <v>9.349049921085899e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>5.351226792274944e-09</v>
+        <v>9.351268240188197e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>5.351023032904677e-09</v>
+        <v>9.349230646485266e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>5.351226792274944e-09</v>
+        <v>9.351268240188189e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>5.351226792274944e-09</v>
+        <v>9.351268240188197e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>5.351226792274944e-09</v>
+        <v>9.351268240188197e-10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.117087738622464e-09</v>
+        <v>3.231849326555215e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.148635851756094e-09</v>
+        <v>1.410334659590036e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.77769828086797e-09</v>
+        <v>1.419493891897152e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.32144681910867e-09</v>
+        <v>1.39793737815398e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.21390615287105e-09</v>
+        <v>1.418786958617622e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.148787711558244e-09</v>
+        <v>1.417576586709841e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.149009543472253e-09</v>
+        <v>3.280447568901298e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.148805784098149e-09</v>
+        <v>3.231645567184932e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.149605403372177e-09</v>
+        <v>1.471303993792407e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.060768234472297e-09</v>
+        <v>1.418382277352288e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.131610539418709e-08</v>
+        <v>1.4184453923008e-09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.769370372649274e-09</v>
+        <v>5.351226792274926e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.713821116367849e-09</v>
+        <v>5.348742099092315e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.71630704408283e-09</v>
+        <v>5.351061408273895e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.808845774181458e-09</v>
+        <v>5.352391361888766e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.716101403860349e-09</v>
+        <v>5.352391361888766e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.716083977640303e-09</v>
+        <v>5.351004960364757e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.716305809550482e-09</v>
+        <v>5.351226792274926e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.716102050180224e-09</v>
+        <v>5.351023032904671e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.716305809550482e-09</v>
+        <v>5.351226792274926e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.523944747149989e-09</v>
+        <v>5.351226792274926e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.716305809550482e-09</v>
+        <v>5.351226792274926e-09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.181470436559188e-09</v>
+        <v>5.117087738622436e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.392255241093975e-10</v>
+        <v>8.148635851756086e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.277913540657831e-09</v>
+        <v>8.777698280868063e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.226939971604435e-09</v>
+        <v>7.321446819108656e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.226939971604435e-09</v>
+        <v>5.21390615287105e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.253572058282463e-09</v>
+        <v>8.148787711558277e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.289945830037504e-09</v>
+        <v>8.149009543472276e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.226939971604435e-09</v>
+        <v>8.148805784098169e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.509532778306432e-09</v>
+        <v>8.149605403372181e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.429502900515227e-09</v>
+        <v>5.060768234472294e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.26516807280281e-09</v>
+        <v>1.131610539418714e-08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.769370372649276e-09</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.713821116367892e-09</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.716307044082923e-09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5.808845774181448e-09</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.716101403860364e-09</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.716083977640326e-09</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.716305809550563e-09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.716102050180263e-09</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.716305809550563e-09</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.523944747149988e-09</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.716305809550563e-09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.181470436559185e-09</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.392255241093983e-10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.277913540657828e-09</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.226939971604437e-09</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.226939971604437e-09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.253572058282455e-09</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.289945830037516e-09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.226939971604437e-09</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.509532778306431e-09</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.429502900515213e-09</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.26516807280282e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.185560100316292e-09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>9.645150901928077e-10</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.317195348931364e-09</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.267758912135922e-09</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.267758912135922e-09</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.283336830215983e-09</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.322170213057579e-09</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.267758912135922e-09</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.550283552549194e-09</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.438038745520371e-09</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.305937806456263e-09</v>
+      <c r="B11" t="n">
+        <v>2.185560100316302e-09</v>
+      </c>
+      <c r="C11" t="n">
+        <v>9.645150901928073e-10</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.317195348931358e-09</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.267758912135928e-09</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.267758912135928e-09</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.283336830215988e-09</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.322170213057563e-09</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.267758912135928e-09</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.550283552549197e-09</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.438038745520354e-09</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.305937806456265e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4403,7 +5203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4471,320 +5271,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.495144453265471e-09</v>
+        <v>2.65428701420272e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.281277789411369e-09</v>
+        <v>9.762187623221797e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>6.645782238016185e-09</v>
+        <v>1.325959329295436e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.951332916584626e-09</v>
+        <v>1.277051088641978e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.951332916584626e-09</v>
+        <v>1.277051088641978e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.17046467959601e-09</v>
+        <v>1.334866350105304e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>6.841004302082328e-09</v>
+        <v>1.325540172403987e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.951332916584626e-09</v>
+        <v>1.277051088641978e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>7.803424262218726e-09</v>
+        <v>1.55567481106375e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>5.789481337305359e-09</v>
+        <v>2.434794188011372e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>7.728001760523209e-09</v>
+        <v>1.3186888442498e-09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.353949350272432e-10</v>
+        <v>2.686355343022705e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>9.064064278539279e-10</v>
+        <v>9.808891192145979e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>9.353949350272432e-10</v>
+        <v>1.334858829558114e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>9.363508354878108e-10</v>
+        <v>1.28503652471961e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.363508354878108e-10</v>
+        <v>1.28503652471961e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.351336677108373e-10</v>
+        <v>1.344622293688348e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.353949350272432e-10</v>
+        <v>1.334858829558114e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.34933783830433e-10</v>
+        <v>1.28503652471961e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.353949350272432e-10</v>
+        <v>1.567185850271776e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.353949350272432e-10</v>
+        <v>2.462359250918751e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.353949350272432e-10</v>
+        <v>1.327108685537436e-09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.246427232398649e-09</v>
+        <v>3.495144453265477e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.422735494613991e-09</v>
+        <v>5.281277789411376e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.43171691295431e-09</v>
+        <v>6.645782238016211e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.409642801899615e-09</v>
+        <v>6.951332916584627e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.431311600043477e-09</v>
+        <v>6.951332916584627e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.430203020371548e-09</v>
+        <v>6.170464679596072e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.302898728896654e-09</v>
+        <v>6.841004302082342e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.430003136491145e-09</v>
+        <v>6.951332916584627e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.276889464119026e-09</v>
+        <v>7.803424262218746e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.430848471047852e-09</v>
+        <v>5.789481337305364e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.431295675939363e-09</v>
+        <v>7.728001760523223e-09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.309366828890556e-09</v>
+        <v>9.353949350272397e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.306869780135842e-09</v>
+        <v>9.064064278539293e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>5.3092023841161e-09</v>
+        <v>9.353949350272397e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>5.310820677839046e-09</v>
+        <v>9.363508354878079e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>5.310820677839046e-09</v>
+        <v>9.363508354878083e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>5.309105561574155e-09</v>
+        <v>9.351336677108358e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>5.309366828890556e-09</v>
+        <v>9.353949350272397e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>5.308905677693745e-09</v>
+        <v>9.34933783830428e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>5.309366828890556e-09</v>
+        <v>9.353949350272397e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>5.309366828890556e-09</v>
+        <v>9.353949350272397e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>5.309366828890556e-09</v>
+        <v>9.353949350272397e-10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.037312294426529e-09</v>
+        <v>3.246427232398651e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.015246047468247e-09</v>
+        <v>1.422735494613991e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.632589054431998e-09</v>
+        <v>1.431716912954306e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.20255730029644e-09</v>
+        <v>1.409642801899618e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.132483571364456e-09</v>
+        <v>1.43131160004348e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.014859749821769e-09</v>
+        <v>1.430203020371553e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.015121017143588e-09</v>
+        <v>3.302898728896653e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.014659865941364e-09</v>
+        <v>1.430003136491144e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.015706242140418e-09</v>
+        <v>3.276889464119018e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.981997968569125e-09</v>
+        <v>1.430848471047855e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.11256912285903e-08</v>
+        <v>1.431295675939367e-09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.63290143552763e-09</v>
+        <v>5.309366828890556e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.538108037127977e-09</v>
+        <v>5.306869780135845e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.540606322169044e-09</v>
+        <v>5.309202384116095e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.587615034318054e-09</v>
+        <v>5.310820677839047e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.540143307463163e-09</v>
+        <v>5.310820677839047e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.540343818566285e-09</v>
+        <v>5.309105561574152e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.540605085882691e-09</v>
+        <v>5.309366828890556e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.540143934685876e-09</v>
+        <v>5.308905677693747e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.540605085882691e-09</v>
+        <v>5.309366828890556e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.993340991792227e-09</v>
+        <v>5.309366828890556e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.540605085882691e-09</v>
+        <v>5.309366828890556e-09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.629259255118634e-09</v>
+        <v>5.037312294426524e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.201164891368338e-10</v>
+        <v>8.015246047468247e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.247221209428617e-09</v>
+        <v>8.632589054431992e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.191261144268356e-09</v>
+        <v>7.202557300296445e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.191261144268356e-09</v>
+        <v>5.132483571364455e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.270951952282687e-09</v>
+        <v>8.014859749821767e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.257565705381464e-09</v>
+        <v>8.015121017143593e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.191261144268356e-09</v>
+        <v>8.014659865941371e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.458958246507121e-09</v>
+        <v>8.015706242140416e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3960450962824e-09</v>
+        <v>4.981997968569127e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.233556463819079e-09</v>
+        <v>1.112569122859031e-08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.632901435527654e-09</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.53810803712801e-09</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.540606322169081e-09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5.587615034318097e-09</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.540143307463192e-09</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.54034381856632e-09</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.540605085882718e-09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.540143934685916e-09</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.540605085882718e-09</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.993340991792251e-09</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.540605085882718e-09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.629259255118636e-09</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.201164891368353e-10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.247221209428618e-09</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.191261144268358e-09</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.191261144268358e-09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.270951952282688e-09</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.257565705381462e-09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.191261144268358e-09</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.458958246507121e-09</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.396045096282372e-09</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.233556463819083e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.628308112251932e-09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>9.48567021965916e-10</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>2.628308112251934e-09</v>
+      </c>
+      <c r="C11" t="n">
+        <v>9.485670219659173e-10</v>
+      </c>
+      <c r="D11" t="n">
         <v>1.286083932851989e-09</v>
       </c>
-      <c r="E9" t="n">
-        <v>1.234382991692251e-09</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.234382991692251e-09</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.301346109992281e-09</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.290371554585036e-09</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.234382991692251e-09</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.506430906449923e-09</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.404621036321147e-09</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="E11" t="n">
+        <v>1.234382991692253e-09</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.234382991692253e-09</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.301346109992284e-09</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.290371554585037e-09</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.234382991692253e-09</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.506430906449922e-09</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.404621036321162e-09</v>
+      </c>
+      <c r="L11" t="n">
         <v>1.276122285234708e-09</v>
       </c>
     </row>
@@ -4799,7 +5679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4867,321 +5747,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.101473451462518e-08</v>
+        <v>1.596119556695153e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.85364729868307e-09</v>
+        <v>1.498238995003941e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.381277346204408e-08</v>
+        <v>1.599015260355131e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.85364729868307e-09</v>
+        <v>1.498238995003941e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.85364729868307e-09</v>
+        <v>1.498238995003941e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.12913708227468e-08</v>
+        <v>1.592212093345552e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>2.232150764669352e-08</v>
+        <v>1.606098535918928e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.85364729868307e-09</v>
+        <v>1.498238995003941e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.332866220391e-08</v>
+        <v>1.597824078071044e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>9.030268345176274e-09</v>
+        <v>1.5937292485338e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>9.329610129824316e-09</v>
+        <v>1.593303855522251e-09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.930823170238234e-10</v>
+        <v>1.6046520357835e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>9.786666939771516e-10</v>
+        <v>1.509827040277853e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.930823170238234e-10</v>
+        <v>1.6046520357835e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>9.846504655696588e-10</v>
+        <v>1.509827040277853e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.846504655696588e-10</v>
+        <v>1.509827040277853e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.927575385396513e-10</v>
+        <v>1.600825699128115e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.930823170238234e-10</v>
+        <v>1.6046520357835e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.922224970009319e-10</v>
+        <v>1.509827040277853e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.930823170238234e-10</v>
+        <v>1.6046520357835e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.930823170238234e-10</v>
+        <v>1.6046520357835e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.930823170238234e-10</v>
+        <v>1.6046520357835e-09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.541876601379897e-09</v>
+        <v>1.101473451462514e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.531129992763664e-09</v>
+        <v>6.853647298683092e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.549546875397775e-09</v>
+        <v>1.381277346204406e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.509909517564112e-09</v>
+        <v>6.853647298683092e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.540598406190699e-09</v>
+        <v>6.853647298683092e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.541551822895728e-09</v>
+        <v>1.129137082274692e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.520257057153996e-09</v>
+        <v>2.232150764669359e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.534562051390276e-09</v>
+        <v>6.853647298683092e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.601434864672627e-09</v>
+        <v>1.332866220390996e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.539375661636949e-09</v>
+        <v>9.030268345176284e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.547856382972277e-09</v>
+        <v>9.329610129824313e-09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.757294627112995e-09</v>
+        <v>9.930823170238284e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.756434807090099e-09</v>
+        <v>9.7866669397715e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>5.757110974900153e-09</v>
+        <v>9.930823170238284e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>5.756068266478771e-09</v>
+        <v>9.846504655696559e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>5.756068266478771e-09</v>
+        <v>9.846504655696568e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>5.756969848628797e-09</v>
+        <v>9.927575385396589e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>5.757294627112995e-09</v>
+        <v>9.930823170238284e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>5.756434807090099e-09</v>
+        <v>9.922224970009335e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>5.757294627112995e-09</v>
+        <v>9.930823170238284e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>5.757294627112995e-09</v>
+        <v>9.930823170238284e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>5.757294627112995e-09</v>
+        <v>9.930823170238284e-10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.584007990192903e-09</v>
+        <v>1.541876601379892e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.895975921152009e-09</v>
+        <v>1.531129992763652e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.583131368149198e-09</v>
+        <v>1.549546875397772e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.989988138923709e-09</v>
+        <v>1.509909517564109e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.688033768923427e-09</v>
+        <v>1.540598406190695e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.895980226090983e-09</v>
+        <v>1.541551822895727e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.896305004575027e-09</v>
+        <v>3.520257057153989e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.895445184552256e-09</v>
+        <v>3.534562051390264e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.896955966307297e-09</v>
+        <v>1.601434864672628e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.522480372578111e-09</v>
+        <v>1.539375661636945e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.235627620629303e-08</v>
+        <v>1.547856382972274e-09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.346336886626927e-09</v>
+        <v>5.757294627112981e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.444880649506679e-09</v>
+        <v>5.756434807090091e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.445741717930491e-09</v>
+        <v>5.75711097490014e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.713569005735536e-09</v>
+        <v>5.756068266478756e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.444879692828446e-09</v>
+        <v>5.756068266478756e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.445415691045408e-09</v>
+        <v>5.756969848628807e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.445740469529592e-09</v>
+        <v>5.757294627112981e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.444880649506679e-09</v>
+        <v>5.756434807090091e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.445740469529592e-09</v>
+        <v>5.757294627112981e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.808742240977461e-09</v>
+        <v>5.757294627112981e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.445740469529592e-09</v>
+        <v>5.757294627112981e-09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.423185471034088e-09</v>
+        <v>5.584007990192903e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.418928486246934e-09</v>
+        <v>8.895975921151987e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.362628795209187e-09</v>
+        <v>9.583131368149201e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.418928486246934e-09</v>
+        <v>7.989988138923722e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.418928486246934e-09</v>
+        <v>5.688033768923438e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.421838615044271e-09</v>
+        <v>8.895980226090991e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.221597100373153e-09</v>
+        <v>8.896305004574991e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.418928486246934e-09</v>
+        <v>8.895445184552233e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.389220931494066e-09</v>
+        <v>8.896955966307299e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.473438069563374e-09</v>
+        <v>5.522480372578106e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.484166449703357e-09</v>
+        <v>1.235627620629301e-08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4.346336886626913e-09</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5.444880649506664e-09</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.445741717930466e-09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6.713569005735511e-09</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5.44487969282844e-09</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5.445415691045411e-09</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.445740469529559e-09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.444880649506664e-09</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5.445740469529559e-09</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.808742240977408e-09</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.445740469529559e-09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.423185471034086e-09</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.418928486246939e-09</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.362628795209186e-09</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.418928486246939e-09</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.418928486246939e-09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.421838615044274e-09</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.221597100373151e-09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.418928486246939e-09</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.389220931494069e-09</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.473438069563376e-09</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.484166449703356e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1.51355169143454e-09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.456879863243371e-09</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.488893914611514e-09</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.456879863243371e-09</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.456879863243371e-09</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.510772399689415e-09</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="B11" t="n">
+        <v>1.513551691434538e-09</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.456879863243367e-09</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.488893914611513e-09</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.456879863243367e-09</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.456879863243367e-09</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.510772399689409e-09</v>
+      </c>
+      <c r="H11" t="n">
         <v>1.431807319583569e-09</v>
       </c>
-      <c r="I9" t="n">
-        <v>1.456879863243371e-09</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="I11" t="n">
+        <v>1.456879863243367e-09</v>
+      </c>
+      <c r="J11" t="n">
         <v>1.499802239081158e-09</v>
       </c>
-      <c r="K9" t="n">
-        <v>1.534026475749546e-09</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.393426679981729e-09</v>
+      <c r="K11" t="n">
+        <v>1.534026475749542e-09</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.393426679981731e-09</v>
       </c>
     </row>
   </sheetData>
@@ -5195,7 +6155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5263,321 +6223,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.380211211204424e-09</v>
+        <v>1.564998215798214e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.900897499743572e-09</v>
+        <v>1.462562291013316e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.22300343824183e-08</v>
+        <v>1.568445191964322e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.900897499743572e-09</v>
+        <v>1.462562291013316e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.900897499743572e-09</v>
+        <v>1.462562291013316e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.027352818276203e-08</v>
+        <v>1.562199512257833e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.913675930521491e-08</v>
+        <v>1.57435318676981e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.900897499743572e-09</v>
+        <v>1.462562291013316e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.173060969205511e-08</v>
+        <v>1.5671017296184e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>8.273136371102357e-09</v>
+        <v>1.563902872660573e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>9.912377694927768e-09</v>
+        <v>1.564706473924313e-09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.42546841738569e-10</v>
+        <v>1.574254194687658e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>9.310851116645521e-10</v>
+        <v>1.472922554026211e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.425468417385686e-10</v>
+        <v>1.574254194687658e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>9.365258185351337e-10</v>
+        <v>1.472922554026211e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.36525818535135e-10</v>
+        <v>1.472922554026211e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.422371764020349e-10</v>
+        <v>1.570570158871212e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.425468417385686e-10</v>
+        <v>1.574254194687658e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.417785872463147e-10</v>
+        <v>1.472922554026211e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.425468417385686e-10</v>
+        <v>1.574254194687658e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.425468417385686e-10</v>
+        <v>1.574254194687658e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.425468417385686e-10</v>
+        <v>1.574254194687658e-09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.459664688196435e-09</v>
+        <v>9.380211211204446e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.451149041505952e-09</v>
+        <v>6.900897499743575e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.465672102711736e-09</v>
+        <v>1.223003438241833e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.431278736860142e-09</v>
+        <v>6.900897499743575e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.458760386650038e-09</v>
+        <v>6.900897499743575e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4593550228599e-09</v>
+        <v>1.027352818276204e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.295431769621094e-09</v>
+        <v>1.91367593052149e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.308981660824165e-09</v>
+        <v>6.900897499743575e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.514550050577642e-09</v>
+        <v>1.17306096920551e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.457408761090283e-09</v>
+        <v>8.273136371102355e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.464634569503708e-09</v>
+        <v>9.91237769492762e-09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.338485865992414e-09</v>
+        <v>9.425468417385672e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.337717611500155e-09</v>
+        <v>9.310851116645495e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>5.33831506503053e-09</v>
+        <v>9.425468417385668e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>5.337751527476473e-09</v>
+        <v>9.365258185351292e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>5.337751527476473e-09</v>
+        <v>9.365258185351341e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>5.338176200655877e-09</v>
+        <v>9.422371764020314e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>5.338485865992412e-09</v>
+        <v>9.425468417385668e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>5.337717611500155e-09</v>
+        <v>9.417785872463087e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>5.338485865992412e-09</v>
+        <v>9.425468417385668e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>5.338485865992412e-09</v>
+        <v>9.425468417385668e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>5.338485865992412e-09</v>
+        <v>9.425468417385668e-10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.123834782635142e-09</v>
+        <v>1.459664688196436e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.142892389538757e-09</v>
+        <v>1.451149041505948e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.768827115064875e-09</v>
+        <v>1.465672102711736e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.317093071656065e-09</v>
+        <v>1.431278736860139e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.218885843936953e-09</v>
+        <v>1.458760386650033e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.142511049743006e-09</v>
+        <v>1.459355022859902e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.142820715079357e-09</v>
+        <v>3.295431769621099e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.142052460587287e-09</v>
+        <v>3.308981660824165e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.143414032715367e-09</v>
+        <v>1.514550050577646e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.067755568959112e-09</v>
+        <v>1.457408761090286e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.129640396537941e-08</v>
+        <v>1.46463456950371e-09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.896314631386434e-09</v>
+        <v>5.338485865992412e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.87009264980977e-09</v>
+        <v>5.337717611500158e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.870862068278735e-09</v>
+        <v>5.338315065030534e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.994698390621181e-09</v>
+        <v>5.337751527476473e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.870091812509693e-09</v>
+        <v>5.337751527476473e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.870551238965491e-09</v>
+        <v>5.338176200655886e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.870860904302034e-09</v>
+        <v>5.338485865992412e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.87009264980977e-09</v>
+        <v>5.337717611500158e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.870860904302034e-09</v>
+        <v>5.338485865992412e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.306205456000375e-09</v>
+        <v>5.338485865992412e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.870860904302034e-09</v>
+        <v>5.338485865992412e-09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.417682539942872e-09</v>
+        <v>5.123834782635136e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.368348239295671e-09</v>
+        <v>8.14289238953874e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.345563676002931e-09</v>
+        <v>8.768827115064868e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.368348239295671e-09</v>
+        <v>7.317093071656057e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.368348239295671e-09</v>
+        <v>5.218885843936946e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.396205184191689e-09</v>
+        <v>8.142511049742991e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.228446395324649e-09</v>
+        <v>8.142820715079347e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.368348239295671e-09</v>
+        <v>8.142052460587282e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.375223794506487e-09</v>
+        <v>8.143414032715346e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.440794929066863e-09</v>
+        <v>5.067755568959103e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.426192146568061e-09</v>
+        <v>1.12964039653794e-08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.896314631386436e-09</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.870092649809775e-09</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.870862068278745e-09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5.994698390621181e-09</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.870091812509686e-09</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.870551238965496e-09</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.870860904302031e-09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.870092649809775e-09</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.870860904302031e-09</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.306205456000378e-09</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.870860904302031e-09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.41768253994287e-09</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.368348239295672e-09</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.345563676002932e-09</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.368348239295672e-09</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.368348239295672e-09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.396205184191691e-09</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.228446395324655e-09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.368348239295672e-09</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.375223794506486e-09</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.440794929066862e-09</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.426192146568062e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1.493757613925079e-09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.414980644552352e-09</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.464390277169334e-09</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.414980644552352e-09</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.414980644552352e-09</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.482862893110445e-09</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.417009536035574e-09</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.414980644552352e-09</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.476542263263719e-09</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.503178481493668e-09</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.375586390665336e-09</v>
+      <c r="B11" t="n">
+        <v>1.493757613925077e-09</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.414980644552351e-09</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.464390277169329e-09</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.414980644552351e-09</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.414980644552351e-09</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.482862893110447e-09</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.417009536035573e-09</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.414980644552351e-09</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.476542263263717e-09</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.503178481493666e-09</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.375586390665332e-09</v>
       </c>
     </row>
   </sheetData>
@@ -5591,7 +6631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5659,321 +6699,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.598844497403889e-09</v>
+        <v>1.545944836422426e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>8.145302718929347e-09</v>
+        <v>1.444869207385119e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.121235375938749e-08</v>
+        <v>1.549199839937184e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>8.145302718929347e-09</v>
+        <v>1.444869207385119e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>8.145302718929347e-09</v>
+        <v>1.444869207385119e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>9.796997280369041e-09</v>
+        <v>1.543830890513871e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.671491779419805e-08</v>
+        <v>1.554049152416103e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>8.145302718929347e-09</v>
+        <v>1.444869207385119e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.153208087326023e-08</v>
+        <v>1.548592809720726e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>7.99445412489397e-09</v>
+        <v>1.545538989394155e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>8.829082634169093e-09</v>
+        <v>1.559605013136476e-09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.407230793422945e-10</v>
+        <v>1.555691111122146e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>9.328142248181726e-10</v>
+        <v>1.453284599520051e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.407230793422947e-10</v>
+        <v>1.555691111122146e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>9.380432829796596e-10</v>
+        <v>1.453284599520051e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.380432829796581e-10</v>
+        <v>1.453284599520051e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.404723042726849e-10</v>
+        <v>1.552329483921831e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.407230793422947e-10</v>
+        <v>1.555691111122146e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.403284592562709e-10</v>
+        <v>1.453284599520051e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.407230793422952e-10</v>
+        <v>1.555691111122146e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.407230793422947e-10</v>
+        <v>1.555691111122146e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.407230793422947e-10</v>
+        <v>1.555691111122146e-09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.463487955394791e-09</v>
+        <v>8.598844497403884e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.459001741029335e-09</v>
+        <v>8.145302718929305e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.468056354286565e-09</v>
+        <v>1.12123537593875e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.43891627577561e-09</v>
+        <v>8.145302718929305e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.464011635669815e-09</v>
+        <v>8.145302718929305e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.307504270381995e-09</v>
+        <v>9.796997280368598e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.293559597471254e-09</v>
+        <v>1.671491779419796e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.463093335308774e-09</v>
+        <v>8.145302718929305e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.296011067809982e-09</v>
+        <v>1.153208087326026e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.461313352282126e-09</v>
+        <v>7.99445412489398e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.468235694432022e-09</v>
+        <v>8.829082634169105e-09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.309595492065206e-09</v>
+        <v>9.407230793422958e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.309200871979177e-09</v>
+        <v>9.328142248181687e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>5.309424814392329e-09</v>
+        <v>9.407230793422954e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>5.309783426183902e-09</v>
+        <v>9.380432829796552e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>5.309783426183902e-09</v>
+        <v>9.380432829796555e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>5.309344716995594e-09</v>
+        <v>9.404723042726911e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>5.309595492065203e-09</v>
+        <v>9.407230793422954e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>5.309200871979177e-09</v>
+        <v>9.403284592562691e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>5.309595492065203e-09</v>
+        <v>9.407230793422954e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>5.309595492065203e-09</v>
+        <v>9.407230793422954e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>5.309595492065203e-09</v>
+        <v>9.407230793422954e-10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.060831220452796e-09</v>
+        <v>1.463487955394799e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.037696442601217e-09</v>
+        <v>1.459001741029328e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.653808104320982e-09</v>
+        <v>1.468056354286564e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.22362489171553e-09</v>
+        <v>1.438916275775608e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.155217496057249e-09</v>
+        <v>1.464011635669827e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.036484282406924e-09</v>
+        <v>3.307504270382004e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.036735057476419e-09</v>
+        <v>3.293559597471221e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.036340437390522e-09</v>
+        <v>1.463093335308764e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.037319908225599e-09</v>
+        <v>3.296011067809981e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.0055522788196e-09</v>
+        <v>1.461313352282133e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.114531545662369e-08</v>
+        <v>1.468235694432029e-09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.768780050850809e-09</v>
+        <v>5.309595492065216e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.706333691205455e-09</v>
+        <v>5.309200871979187e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.706729471722646e-09</v>
+        <v>5.309424814392337e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.788706160893189e-09</v>
+        <v>5.309783426183911e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.706332903884796e-09</v>
+        <v>5.309783426183911e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.706477536221859e-09</v>
+        <v>5.309344716995606e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.706728311291455e-09</v>
+        <v>5.309595492065212e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.706333691205455e-09</v>
+        <v>5.309200871979187e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.706728311291455e-09</v>
+        <v>5.309595492065212e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.163277893658041e-09</v>
+        <v>5.309595492065212e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.706728311291455e-09</v>
+        <v>5.309595492065212e-09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.415352266408601e-09</v>
+        <v>5.060831220452819e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.31464999221038e-09</v>
+        <v>8.037696442601231e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.347245915813562e-09</v>
+        <v>8.653808104321004e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.31464999221038e-09</v>
+        <v>7.223624891715542e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.31464999221038e-09</v>
+        <v>5.15521749605726e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.386563972512646e-09</v>
+        <v>8.036484282406944e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.251517447324644e-09</v>
+        <v>8.036735057476436e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.31464999221038e-09</v>
+        <v>8.03634043739053e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.361443247782386e-09</v>
+        <v>8.03731990822561e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.424010718896224e-09</v>
+        <v>5.005552278819599e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.135776324504379e-09</v>
+        <v>1.114531545662374e-08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.76878005085087e-09</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.70633369120551e-09</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.70672947172271e-09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5.788706160893255e-09</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.706332903884847e-09</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.706477536221929e-09</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.70672831129154e-09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.70633369120551e-09</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.70672831129154e-09</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.163277893658107e-09</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.70672831129154e-09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.415352266408604e-09</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.314649992210382e-09</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.347245915813568e-09</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.314649992210382e-09</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.314649992210382e-09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.386563972512629e-09</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.251517447324647e-09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.314649992210382e-09</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.36144324778239e-09</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.424010718896228e-09</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.135776324504381e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1.482090214844399e-09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.381790019256942e-09</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.454356611796353e-09</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.381790019256942e-09</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.381790019256942e-09</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.468407054559355e-09</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.415649166044285e-09</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.381790019256942e-09</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.46020941286992e-09</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.485623991290844e-09</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.368542447036363e-09</v>
+      <c r="B11" t="n">
+        <v>1.482090214844403e-09</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.38179001925694e-09</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.454356611796357e-09</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.38179001925694e-09</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.38179001925694e-09</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.468407054559342e-09</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.415649166044289e-09</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.38179001925694e-09</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.460209412869925e-09</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.485623991290849e-09</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.368542447036367e-09</v>
       </c>
     </row>
   </sheetData>
@@ -5987,7 +7107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6055,321 +7175,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.570404830672531e-09</v>
+        <v>1.454391127729326e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.848210732924518e-09</v>
+        <v>1.33350717967641e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>7.58419132919937e-09</v>
+        <v>1.455616819053531e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>5.848210732924518e-09</v>
+        <v>1.33350717967641e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>5.848210732924518e-09</v>
+        <v>1.33350717967641e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>7.393565098470043e-09</v>
+        <v>1.451880831132718e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.137243869540513e-08</v>
+        <v>1.459120760241872e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>5.848210732924518e-09</v>
+        <v>1.33350717967641e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.050430444598417e-08</v>
+        <v>1.458176495642883e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>7.072097318994648e-09</v>
+        <v>1.455029603575412e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.179364329811337e-08</v>
+        <v>1.457266294546099e-09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.106705180566696e-10</v>
+        <v>1.466047474327608e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>9.007370555923649e-10</v>
+        <v>1.343905176517196e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.106705180566696e-10</v>
+        <v>1.466047474327608e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>9.060849570192045e-10</v>
+        <v>1.343905176517196e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.060849570192048e-10</v>
+        <v>1.343905176517196e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.103857555599054e-10</v>
+        <v>1.462690496025433e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.106705180566696e-10</v>
+        <v>1.466047474327608e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.100461776541379e-10</v>
+        <v>1.343905176517196e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.106705180566696e-10</v>
+        <v>1.466047474327608e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.106705180566696e-10</v>
+        <v>1.466047474327608e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.106705180566696e-10</v>
+        <v>1.466047474327608e-09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.408206935268432e-09</v>
+        <v>6.570404830672474e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.481866634426377e-09</v>
+        <v>5.848210732924514e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>3.405910440140168e-09</v>
+        <v>7.58419132919937e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.461534946544503e-09</v>
+        <v>5.848210732924514e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.487288715624982e-09</v>
+        <v>5.848210732924514e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.407922172771664e-09</v>
+        <v>7.393565098470057e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.489523398629824e-09</v>
+        <v>1.137243869540513e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.407582594865895e-09</v>
+        <v>5.848210732924514e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.39866550708938e-09</v>
+        <v>1.050430444598423e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.487521211613152e-09</v>
+        <v>7.072097318994641e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.489371005624552e-09</v>
+        <v>1.179364329811336e-08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.455188182153088e-09</v>
+        <v>9.106705180566676e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.454563841750547e-09</v>
+        <v>9.007370555923659e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>5.455006898097638e-09</v>
+        <v>9.106705180566676e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>5.454800976070635e-09</v>
+        <v>9.060849570192061e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>5.454800976070635e-09</v>
+        <v>9.060849570192061e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>5.454903419656323e-09</v>
+        <v>9.103857555599053e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>5.455188182153088e-09</v>
+        <v>9.106705180566686e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>5.454563841750547e-09</v>
+        <v>9.100461776541351e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>5.455188182153088e-09</v>
+        <v>9.106705180566677e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>5.455188182153088e-09</v>
+        <v>9.106705180566676e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>5.455188182153088e-09</v>
+        <v>9.106705180566676e-10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.110903087599597e-09</v>
+        <v>3.408206935268427e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.132020707445576e-09</v>
+        <v>1.481866634426373e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.757957767805761e-09</v>
+        <v>3.405910440140173e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.305729245310653e-09</v>
+        <v>1.461534946544503e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.206279692032458e-09</v>
+        <v>1.487288715624987e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.131312408993393e-09</v>
+        <v>3.407922172771663e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.13159717148997e-09</v>
+        <v>1.489523398629826e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.130972831087628e-09</v>
+        <v>3.407582594865893e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.132190824830294e-09</v>
+        <v>3.398665507089389e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.054792144133319e-09</v>
+        <v>1.487521211613153e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.128696472881188e-08</v>
+        <v>1.489371005624552e-09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.001859277686149e-09</v>
+        <v>5.455188182153096e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.00928984660215e-09</v>
+        <v>5.454563841750557e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.009915427239648e-09</v>
+        <v>5.45500689809765e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.172564029325164e-09</v>
+        <v>5.454800976070647e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.009289102953773e-09</v>
+        <v>5.454800976070648e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.009629424507923e-09</v>
+        <v>5.45490341965633e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.009914187004682e-09</v>
+        <v>5.455188182153096e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.00928984660215e-09</v>
+        <v>5.454563841750557e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.009914187004682e-09</v>
+        <v>5.455188182153096e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.425843735246526e-09</v>
+        <v>5.455188182153096e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.009914187004682e-09</v>
+        <v>5.455188182153096e-09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.388788934226192e-09</v>
+        <v>5.110903087599604e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.276208437445065e-09</v>
+        <v>8.13202070744558e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.36315858770093e-09</v>
+        <v>8.757957767805763e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.276208437445065e-09</v>
+        <v>7.305729245310662e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.276208437445065e-09</v>
+        <v>5.206279692032462e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.368051224418416e-09</v>
+        <v>8.131312408993411e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.293126468911788e-09</v>
+        <v>8.131597171489993e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.276208437445065e-09</v>
+        <v>8.130972831087639e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.310728496082798e-09</v>
+        <v>8.132190824830309e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.375512556690358e-09</v>
+        <v>5.054792144133329e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.299070701751219e-09</v>
+        <v>1.128696472881189e-08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4.001859277686151e-09</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5.009289846602155e-09</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.009915427239662e-09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6.172564029325169e-09</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5.009289102953773e-09</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5.009629424507923e-09</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.009914187004687e-09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.009289846602155e-09</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5.009914187004687e-09</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.425843735246535e-09</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.009914187004687e-09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.388788934226194e-09</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.276208437445069e-09</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.363158587700933e-09</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.276208437445069e-09</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.276208437445069e-09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.368051224418419e-09</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.29312646891179e-09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.276208437445069e-09</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.310728496082799e-09</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.375512556690363e-09</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.299070701751222e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1.419238245774819e-09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.302704947661883e-09</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.408802047750965e-09</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.302704947661883e-09</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.302704947661883e-09</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.40881966095406e-09</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.380441151711123e-09</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.302704947661883e-09</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.387505865569275e-09</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.413835927532797e-09</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.382826704839092e-09</v>
+      <c r="B11" t="n">
+        <v>1.419238245774823e-09</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.302704947661886e-09</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.408802047750969e-09</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.302704947661886e-09</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.302704947661886e-09</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.408819660954064e-09</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.380441151711127e-09</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.302704947661886e-09</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.387505865569279e-09</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.413835927532801e-09</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.382826704839095e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6383,7 +7583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6451,321 +7651,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.347435497817502e-09</v>
+        <v>1.409898486661204e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.012131700272444e-09</v>
+        <v>1.277720011305848e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>6.015556132479083e-09</v>
+        <v>1.408307447732679e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.012131700272444e-09</v>
+        <v>1.277720011305848e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.012131700272444e-09</v>
+        <v>1.277720011305848e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.676419765533059e-09</v>
+        <v>1.405874597934305e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>7.121060643710506e-09</v>
+        <v>1.409161309199831e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.012131700272444e-09</v>
+        <v>1.277720011305848e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.015965757438824e-08</v>
+        <v>1.412997782548637e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>6.869527301634658e-09</v>
+        <v>1.409477851966875e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>8.030860130898671e-09</v>
+        <v>1.410165824304463e-09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.601473025955875e-10</v>
+        <v>1.419414459535723e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.51765284724545e-10</v>
+        <v>1.286518871301637e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>8.601473025955875e-10</v>
+        <v>1.419414459535723e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>8.56616137205413e-10</v>
+        <v>1.286518871301637e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.56616137205414e-10</v>
+        <v>1.286518871301637e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>8.598692079781946e-10</v>
+        <v>1.416204193423127e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>8.601473025955875e-10</v>
+        <v>1.419414459535723e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>8.595594228275295e-10</v>
+        <v>1.286518871301637e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>8.601473025955875e-10</v>
+        <v>1.419414459535723e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>8.601473025955875e-10</v>
+        <v>1.419414459535723e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>8.601473025955875e-10</v>
+        <v>1.419414459535723e-09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.185320325867274e-09</v>
+        <v>7.347435497817497e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.400861165107999e-09</v>
+        <v>6.012131700272432e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.403551340945979e-09</v>
+        <v>6.015556132479075e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.381722254182329e-09</v>
+        <v>6.012131700272432e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.404794071737694e-09</v>
+        <v>6.012131700272432e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.185042231249879e-09</v>
+        <v>6.676419765532906e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.172447350679323e-09</v>
+        <v>7.121060643710502e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.184732446099213e-09</v>
+        <v>6.012131700272432e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.457932722418236e-09</v>
+        <v>1.015965757438821e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.405562978516039e-09</v>
+        <v>6.869527301634652e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.40532140443929e-09</v>
+        <v>8.030860130898661e-09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.037489194300482e-09</v>
+        <v>8.601473025955887e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.036901314532418e-09</v>
+        <v>8.517652847245449e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>5.037321305201701e-09</v>
+        <v>8.601473025955887e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>5.037183481085583e-09</v>
+        <v>8.566161372054144e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>5.037183481085583e-09</v>
+        <v>8.56616137205415e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>5.037211099683079e-09</v>
+        <v>8.598692079781945e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>5.037489194300482e-09</v>
+        <v>8.601473025955887e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>5.036901314532418e-09</v>
+        <v>8.595594228275304e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>5.037489194300482e-09</v>
+        <v>8.601473025955887e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>5.037489194300482e-09</v>
+        <v>8.601473025955887e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>5.037489194300482e-09</v>
+        <v>8.601473025955887e-10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.643190494798033e-09</v>
+        <v>3.185320325867269e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>7.367669370660263e-09</v>
+        <v>1.40086116510799e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>7.932091124219602e-09</v>
+        <v>1.403551340945979e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>6.622514044870448e-09</v>
+        <v>1.381722254182328e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>4.729219302974463e-09</v>
+        <v>1.404794071737694e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>7.366963324814138e-09</v>
+        <v>3.185042231249877e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>7.367241419431486e-09</v>
+        <v>3.172447350679318e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>7.36665353966347e-09</v>
+        <v>3.184732446099213e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>7.367776773824948e-09</v>
+        <v>1.457932722418233e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.592589850317398e-09</v>
+        <v>1.405562978516038e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.021274039195008e-08</v>
+        <v>1.405321404439289e-09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.560490435941786e-09</v>
+        <v>5.037489194300487e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.446128035980275e-09</v>
+        <v>5.036901314532421e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.446717093275637e-09</v>
+        <v>5.037321305201708e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.468813759886133e-09</v>
+        <v>5.037183481085584e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.446127433391852e-09</v>
+        <v>5.037183481085584e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.446437821130935e-09</v>
+        <v>5.037211099683088e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.446715915748317e-09</v>
+        <v>5.037489194300487e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.446128035980275e-09</v>
+        <v>5.036901314532421e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.446715915748317e-09</v>
+        <v>5.037489194300487e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.933233887535907e-09</v>
+        <v>5.037489194300487e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.446715915748317e-09</v>
+        <v>5.037489194300487e-09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.311667000227151e-09</v>
+        <v>4.643190494798032e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.203387045452729e-09</v>
+        <v>7.36766937066026e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.345059913488606e-09</v>
+        <v>7.932091124219604e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.203387045452729e-09</v>
+        <v>6.622514044870442e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.203387045452729e-09</v>
+        <v>4.729219302974454e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.325857018975625e-09</v>
+        <v>7.366963324814132e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.328979862143125e-09</v>
+        <v>7.367241419431465e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.203387045452729e-09</v>
+        <v>7.36665353966345e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.248114434309938e-09</v>
+        <v>7.367776773824933e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.320598924000406e-09</v>
+        <v>4.592589850317398e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.307886039731296e-09</v>
+        <v>1.021274039195009e-08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.560490435941779e-09</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.446128035980247e-09</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.446717093275617e-09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5.468813759886115e-09</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.446127433391835e-09</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.446437821130912e-09</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.446715915748303e-09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.446128035980247e-09</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.446715915748303e-09</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.933233887535888e-09</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.446715915748303e-09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.311667000227152e-09</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.203387045452728e-09</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.345059913488607e-09</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.203387045452728e-09</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.203387045452728e-09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.325857018975627e-09</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.328979862143126e-09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.203387045452728e-09</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.24811443430994e-09</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.320598924000407e-09</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.307886039731298e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1.360873049305024e-09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.239894765619186e-09</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>1.360873049305023e-09</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.239894765619185e-09</v>
+      </c>
+      <c r="D11" t="n">
         <v>1.374475892327364e-09</v>
       </c>
-      <c r="E9" t="n">
-        <v>1.239894765619186e-09</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.239894765619186e-09</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="E11" t="n">
+        <v>1.239894765619185e-09</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.239894765619185e-09</v>
+      </c>
+      <c r="G11" t="n">
         <v>1.364766345641332e-09</v>
       </c>
-      <c r="H9" t="n">
-        <v>1.368013279188237e-09</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.239894765619186e-09</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.335055725170114e-09</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.364516468391879e-09</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.359420037873465e-09</v>
+      <c r="H11" t="n">
+        <v>1.368013279188238e-09</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.239894765619185e-09</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.335055725170116e-09</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.36451646839188e-09</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.359420037873464e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6779,7 +8059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6847,321 +8127,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.553317424277722e-09</v>
+        <v>1.406575908916958e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.426897077150905e-09</v>
+        <v>1.272194471214412e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>7.004890094333762e-09</v>
+        <v>1.404717236807756e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.426897077150905e-09</v>
+        <v>1.272194471214412e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.426897077150905e-09</v>
+        <v>1.272194471214412e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.954894526542564e-09</v>
+        <v>1.401353644110421e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>6.827707042570464e-09</v>
+        <v>1.403815125725411e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.426897077150905e-09</v>
+        <v>1.272194471214412e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.613205313803434e-08</v>
+        <v>1.415050141273474e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>6.912919018147344e-09</v>
+        <v>1.404772707493725e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>8.50101346282741e-09</v>
+        <v>1.405800674090807e-09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.620602495948404e-10</v>
+        <v>1.41448040157901e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.536909855137633e-10</v>
+        <v>1.280384371926958e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>8.620602495948403e-10</v>
+        <v>1.41448040157901e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>8.585912532506747e-10</v>
+        <v>1.280384371926958e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.585912532506747e-10</v>
+        <v>1.280384371926958e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>8.617839990864856e-10</v>
+        <v>1.411297347528986e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>8.620602495948403e-10</v>
+        <v>1.41448040157901e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>8.614841087556076e-10</v>
+        <v>1.280384371926958e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>8.620602495948404e-10</v>
+        <v>1.41448040157901e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>8.620602495948403e-10</v>
+        <v>1.41448040157901e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>8.620602495948403e-10</v>
+        <v>1.41448040157901e-09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.41136858312515e-09</v>
+        <v>8.553317424277724e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.406758189697033e-09</v>
+        <v>6.42689707715091e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.410656528894213e-09</v>
+        <v>7.004890094333762e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.387207094455308e-09</v>
+        <v>6.42689707715091e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.410742716425334e-09</v>
+        <v>6.42689707715091e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.411092332616796e-09</v>
+        <v>6.954894526542977e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.17903383353883e-09</v>
+        <v>6.827707042570477e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.410792442285918e-09</v>
+        <v>6.42689707715091e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.465911524520897e-09</v>
+        <v>1.61320531380344e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.410820629801999e-09</v>
+        <v>6.912919018147368e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.411323379571549e-09</v>
+        <v>8.501013462827425e-09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.029058383225562e-09</v>
+        <v>8.620602495948388e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.028482242386333e-09</v>
+        <v>8.536909855137634e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>5.028890831340977e-09</v>
+        <v>8.620602495948388e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>5.028754520436607e-09</v>
+        <v>8.585912532506754e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>5.028754520436607e-09</v>
+        <v>8.585912532506755e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>5.028782132717208e-09</v>
+        <v>8.617839990864848e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>5.029058383225562e-09</v>
+        <v>8.620602495948388e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>5.028482242386333e-09</v>
+        <v>8.614841087556075e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>5.029058383225562e-09</v>
+        <v>8.620602495948388e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>5.029058383225562e-09</v>
+        <v>8.620602495948388e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>5.029058383225562e-09</v>
+        <v>8.620602495948388e-10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.613445911800351e-09</v>
+        <v>1.41136858312516e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>7.318112502379531e-09</v>
+        <v>1.406758189697038e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>7.878428503424363e-09</v>
+        <v>1.410656528894223e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>6.57837664807926e-09</v>
+        <v>1.387207094455323e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>4.698852404352964e-09</v>
+        <v>1.410742716425335e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>7.317410333103625e-09</v>
+        <v>1.411092332616796e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>7.317686583612066e-09</v>
+        <v>3.179033833538826e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>7.317110442772748e-09</v>
+        <v>1.410792442285919e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>7.318218044707356e-09</v>
+        <v>1.465911524520895e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.563213252937923e-09</v>
+        <v>1.410820629801993e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.014249209053685e-08</v>
+        <v>1.411323379571553e-09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.467244637906375e-09</v>
+        <v>5.029058383225563e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.32670990917756e-09</v>
+        <v>5.028482242386336e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.32728722883073e-09</v>
+        <v>5.028890831340972e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.319179818302145e-09</v>
+        <v>5.028754520436619e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.326709340977163e-09</v>
+        <v>5.028754520436619e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.327009799508432e-09</v>
+        <v>5.028782132717217e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.327286050016784e-09</v>
+        <v>5.029058383225563e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.32670990917756e-09</v>
+        <v>5.028482242386336e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.327286050016784e-09</v>
+        <v>5.029058383225563e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.808758024474582e-09</v>
+        <v>5.029058383225563e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.327286050016784e-09</v>
+        <v>5.029058383225563e-09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.274900263501109e-09</v>
+        <v>4.613445911800358e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.186880756415788e-09</v>
+        <v>7.31811250237955e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.313917388480342e-09</v>
+        <v>7.878428503424373e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.186880756415788e-09</v>
+        <v>6.578376648079278e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.186880756415788e-09</v>
+        <v>4.698852404352976e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.314839008953767e-09</v>
+        <v>7.31741033310363e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.33442562479273e-09</v>
+        <v>7.317686583612047e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.186880756415788e-09</v>
+        <v>7.317110442772771e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.099834440508994e-09</v>
+        <v>7.318218044707381e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.312814175920202e-09</v>
+        <v>4.563213252937932e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.301981150485822e-09</v>
+        <v>1.014249209053685e-08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.467244637906408e-09</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.326709909177567e-09</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.32728722883074e-09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5.319179818302184e-09</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.326709340977186e-09</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.327009799508465e-09</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.327286050016799e-09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.326709909177567e-09</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.327286050016792e-09</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.808758024474612e-09</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.327286050016792e-09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.274900263501111e-09</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.186880756415791e-09</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.313917388480345e-09</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.186880756415791e-09</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.186880756415791e-09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.314839008953767e-09</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.334425624792732e-09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.186880756415791e-09</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.099834440508997e-09</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.312814175920205e-09</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.301981150485823e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1.343066501276007e-09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.229650028178483e-09</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.358960745372556e-09</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.229650028178483e-09</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.229650028178483e-09</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.357464792664209e-09</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.367389947168215e-09</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.229650028178483e-09</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.271885226269433e-09</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.358514250827932e-09</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.35418521992335e-09</v>
+      <c r="B11" t="n">
+        <v>1.343066501276008e-09</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.229650028178485e-09</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.358960745372557e-09</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.229650028178485e-09</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.229650028178485e-09</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.357464792664207e-09</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.367389947168217e-09</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.229650028178485e-09</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.27188522626943e-09</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.358514250827934e-09</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.354185219923352e-09</v>
       </c>
     </row>
   </sheetData>
@@ -7175,7 +8535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7243,321 +8603,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.597917580912214e-09</v>
+        <v>1.507944918433016e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.356666149219432e-09</v>
+        <v>1.392816165018055e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.294856997556222e-08</v>
+        <v>1.51297939233335e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>6.356666149219432e-09</v>
+        <v>1.392816165018055e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.356666149219432e-09</v>
+        <v>1.392816165018055e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.023044399017391e-08</v>
+        <v>1.505833153093997e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>2.065504370980223e-08</v>
+        <v>1.520310457903039e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.356666149219432e-09</v>
+        <v>1.392816165018055e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.065258088624607e-08</v>
+        <v>1.509577006163922e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>8.360451809732596e-09</v>
+        <v>1.507631412381534e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>8.92915276340468e-09</v>
+        <v>1.522133879616679e-09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.406313779379877e-10</v>
+        <v>1.517985504957345e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>9.272952900809365e-10</v>
+        <v>1.403462467401548e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.406313779379877e-10</v>
+        <v>1.517985504957345e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>9.32972403592901e-10</v>
+        <v>1.403462467401548e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.329724035928911e-10</v>
+        <v>1.403462467401548e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.402801333375602e-10</v>
+        <v>1.514231496206997e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.406313779379877e-10</v>
+        <v>1.517985504957345e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.395895611911601e-10</v>
+        <v>1.403462467401548e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.406313779379877e-10</v>
+        <v>1.517985504957345e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.406313779379877e-10</v>
+        <v>1.517985504957345e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.406313779379877e-10</v>
+        <v>1.517985504957345e-09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.511281550815652e-09</v>
+        <v>8.597917580912207e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.501280118649916e-09</v>
+        <v>6.356666149219183e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.519622197432531e-09</v>
+        <v>1.294856997556225e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.480665441564906e-09</v>
+        <v>6.356666149219183e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.509919980234179e-09</v>
+        <v>6.356666149219183e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.463886672827494e-09</v>
+        <v>1.023044399017443e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.453507079978682e-09</v>
+        <v>2.065504370980237e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.463196100681086e-09</v>
+        <v>6.356666149219183e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45509412672147e-09</v>
+        <v>1.065258088624605e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.509351813859073e-09</v>
+        <v>8.360451809732596e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.516482586225134e-09</v>
+        <v>8.929152763404844e-09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.563590782002518e-09</v>
+        <v>9.406313779379788e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.5625489652557e-09</v>
+        <v>9.272952900809297e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>5.563408795221241e-09</v>
+        <v>9.406313779379788e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>5.562408691447814e-09</v>
+        <v>9.329724035928924e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>5.562408691447814e-09</v>
+        <v>9.329724035928932e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>5.563239537402095e-09</v>
+        <v>9.40280133337562e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>5.563590782002518e-09</v>
+        <v>9.406313779379788e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>5.5625489652557e-09</v>
+        <v>9.395895611911512e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>5.563590782002518e-09</v>
+        <v>9.406313779379788e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>5.563590782002518e-09</v>
+        <v>9.406313779379788e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>5.563590782002518e-09</v>
+        <v>9.406313779379788e-10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.283311943157408e-09</v>
+        <v>1.51128155081565e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>8.409341001262381e-09</v>
+        <v>1.501280118649904e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.057945870735271e-09</v>
+        <v>1.519622197432531e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>7.554186148493198e-09</v>
+        <v>1.480665441564891e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.381395868467272e-09</v>
+        <v>1.509919980234169e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.409323030267243e-09</v>
+        <v>3.463886672827486e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.409674274867561e-09</v>
+        <v>3.453507079978694e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.408632458120821e-09</v>
+        <v>3.46319610068109e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.410288695070855e-09</v>
+        <v>3.455094126721469e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.225238157735415e-09</v>
+        <v>1.509351813859068e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.167542115289555e-08</v>
+        <v>1.516482586225135e-09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.159734629251727e-09</v>
+        <v>5.563590782002522e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.208720925908734e-09</v>
+        <v>5.562548965255693e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.209763945250739e-09</v>
+        <v>5.563408795221246e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.42043106086642e-09</v>
+        <v>5.562408691447826e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.208720021237575e-09</v>
+        <v>5.562408691447826e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.209411498055118e-09</v>
+        <v>5.563239537402101e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.20976274265559e-09</v>
+        <v>5.563590782002522e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.208720925908734e-09</v>
+        <v>5.562548965255693e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.20976274265559e-09</v>
+        <v>5.563590782002522e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.601372835777745e-09</v>
+        <v>5.563590782002522e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.20976274265559e-09</v>
+        <v>5.563590782002522e-09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.39279253365358e-09</v>
+        <v>5.283311943157408e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.324024674877774e-09</v>
+        <v>8.409341001262371e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.287400498660906e-09</v>
+        <v>9.057945870735268e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.324024674877774e-09</v>
+        <v>7.554186148493188e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.324024674877774e-09</v>
+        <v>5.381395868467265e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.355301707001609e-09</v>
+        <v>8.409323030267225e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.141061408923661e-09</v>
+        <v>8.409674274867541e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.324024674877774e-09</v>
+        <v>8.40863245812082e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.359887553369013e-09</v>
+        <v>8.410288695070832e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.399500869719534e-09</v>
+        <v>5.225238157735407e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.102069683207549e-09</v>
+        <v>1.167542115289556e-08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4.159734629251724e-09</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5.208720925908717e-09</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.209763945250734e-09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6.420431060866427e-09</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5.20872002123755e-09</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5.209411498055112e-09</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.209762742655539e-09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.208720925908717e-09</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5.209762742655539e-09</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.601372835777746e-09</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.209762742655539e-09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.392792533653574e-09</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.324024674877771e-09</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.2874004986609e-09</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.324024674877771e-09</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.324024674877771e-09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.355301707001603e-09</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.141061408923654e-09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.324024674877771e-09</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.359887553369014e-09</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.39950086971953e-09</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.102069683207546e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1.45098171752348e-09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.356671716266515e-09</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.40806247963766e-09</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.356671716266515e-09</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.356671716266515e-09</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.433519592526357e-09</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.348808793021887e-09</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.356671716266515e-09</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.437641934362955e-09</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.453720525760197e-09</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.456084587831941e-09</v>
+      <c r="B11" t="n">
+        <v>1.450981717523474e-09</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.356671716266511e-09</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.408062479637657e-09</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.356671716266511e-09</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.356671716266511e-09</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.433519592526353e-09</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.348808793021888e-09</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.356671716266511e-09</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.437641934362952e-09</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.453720525760194e-09</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.45608458783194e-09</v>
       </c>
     </row>
   </sheetData>
@@ -7571,7 +9011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7639,321 +9079,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.248213695147262e-09</v>
+        <v>1.474561544049694e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.819080754183025e-09</v>
+        <v>1.357032971067633e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.033193532371118e-08</v>
+        <v>1.479901503199126e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>5.819080754183025e-09</v>
+        <v>1.357032971067633e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>5.819080754183025e-09</v>
+        <v>1.357032971067633e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>8.117709364201026e-09</v>
+        <v>1.47328383732335e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>8.721624143015259e-09</v>
+        <v>1.476929834916484e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>5.819080754183025e-09</v>
+        <v>1.357032971067633e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.004544491927911e-08</v>
+        <v>1.478507204565036e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>6.236037803633779e-09</v>
+        <v>1.474644072502804e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.710183516096655e-08</v>
+        <v>1.475756474096762e-09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.9205998777698e-10</v>
+        <v>1.486333083960672e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.81565115842001e-10</v>
+        <v>1.367264039541703e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>8.9205998777698e-10</v>
+        <v>1.486333083960672e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>8.86701321731845e-10</v>
+        <v>1.367264039541703e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.867013217318452e-10</v>
+        <v>1.367264039541703e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>8.917484838256806e-10</v>
+        <v>1.482809758835664e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>8.9205998777698e-10</v>
+        <v>1.486333083960672e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>8.912684870594371e-10</v>
+        <v>1.367264039541703e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>8.9205998777698e-10</v>
+        <v>1.486333083960672e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>8.9205998777698e-10</v>
+        <v>1.486333083960672e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>8.9205998777698e-10</v>
+        <v>1.486333083960672e-09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.232269680318493e-09</v>
+        <v>6.24821369514726e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.416946451560687e-09</v>
+        <v>5.819080754183027e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.430384842559815e-09</v>
+        <v>1.033193532371113e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.397690665125992e-09</v>
+        <v>5.819080754183027e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.423102363964701e-09</v>
+        <v>5.819080754183027e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.231958176367207e-09</v>
+        <v>8.117709364201088e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>3.219148769601349e-09</v>
+        <v>8.721624143015269e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.231478179600956e-09</v>
+        <v>5.819080754183027e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.477399336931437e-09</v>
+        <v>1.004544491927909e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.42109864135673e-09</v>
+        <v>6.236037803633778e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.427099148197754e-09</v>
+        <v>1.710183516096651e-08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.16030992864338e-09</v>
+        <v>8.920599877769799e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.159518427925839e-09</v>
+        <v>8.81565115842008e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>5.160140802230104e-09</v>
+        <v>8.920599877769799e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>5.15962781649121e-09</v>
+        <v>8.867013217318463e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>5.15962781649121e-09</v>
+        <v>8.867013217318462e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>5.159998424692089e-09</v>
+        <v>8.91748483825683e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>5.16030992864338e-09</v>
+        <v>8.920599877769799e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>5.159518427925839e-09</v>
+        <v>8.912684870594447e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>5.16030992864338e-09</v>
+        <v>8.920599877769799e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>5.16030992864338e-09</v>
+        <v>8.920599877769799e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>5.16030992864338e-09</v>
+        <v>8.920599877769799e-10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.845530689472122e-09</v>
+        <v>3.232269680318501e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>7.695058352771285e-09</v>
+        <v>1.416946451560682e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.285823552549442e-09</v>
+        <v>1.430384842559814e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>6.915624095814367e-09</v>
+        <v>1.397690665126002e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>4.935228260994246e-09</v>
+        <v>1.423102363964699e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>7.694661601274343e-09</v>
+        <v>3.23195817636721e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>7.694973105225457e-09</v>
+        <v>3.219148769601361e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>7.694181604508104e-09</v>
+        <v>3.231478179600958e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>7.695533102670347e-09</v>
+        <v>1.477399336931446e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.792600833665161e-09</v>
+        <v>1.421098641356741e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.067145397531362e-08</v>
+        <v>1.427099148197761e-09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.702402247060111e-09</v>
+        <v>5.160309928643377e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>4.625701506239013e-09</v>
+        <v>5.159518427925836e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>4.626494220708595e-09</v>
+        <v>5.160140802230105e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.692082916181938e-09</v>
+        <v>5.159627816491225e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>4.625700842003041e-09</v>
+        <v>5.159627816491225e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>4.626181503005236e-09</v>
+        <v>5.159998424692095e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>4.626493006956532e-09</v>
+        <v>5.160309928643377e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>4.625701506239013e-09</v>
+        <v>5.159518427925836e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>4.626493006956532e-09</v>
+        <v>5.160309928643377e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.091071701987563e-09</v>
+        <v>5.160309928643377e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.626493006956532e-09</v>
+        <v>5.160309928643377e-09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.407094104488712e-09</v>
+        <v>4.845530689472132e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.290541311360124e-09</v>
+        <v>7.695058352771318e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.295277051929478e-09</v>
+        <v>8.285823552549476e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.290541311360124e-09</v>
+        <v>6.9156240958144e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.290541311360124e-09</v>
+        <v>4.935228260994274e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.35702994826814e-09</v>
+        <v>7.694661601274366e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.360016327264185e-09</v>
+        <v>7.694973105225494e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.290541311360124e-09</v>
+        <v>7.694181604508127e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.325716277731281e-09</v>
+        <v>7.695533102670384e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.405459764023221e-09</v>
+        <v>4.792600833665177e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.189251678277626e-09</v>
+        <v>1.067145397531366e-08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.702402247060084e-09</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.625701506238977e-09</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.626494220708541e-09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5.692082916181897e-09</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.625700842002999e-09</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.626181503005223e-09</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.626493006956516e-09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.625701506238977e-09</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.626493006956516e-09</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.091071701987556e-09</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.626493006956516e-09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.407094104488713e-09</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.290541311360125e-09</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.295277051929483e-09</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.290541311360125e-09</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.290541311360125e-09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.357029948268146e-09</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.360016327264186e-09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.290541311360125e-09</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.325716277731281e-09</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.405459764023223e-09</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.189251678277629e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1.438507555870305e-09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.322123885244183e-09</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.392970399765482e-09</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.322123885244183e-09</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.322123885244183e-09</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="B11" t="n">
+        <v>1.438507555870307e-09</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.322123885244186e-09</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.392970399765485e-09</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.322123885244186e-09</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.322123885244186e-09</v>
+      </c>
+      <c r="G11" t="n">
         <v>1.416053622678653e-09</v>
       </c>
-      <c r="H9" t="n">
-        <v>1.419455308071964e-09</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.322123885244183e-09</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.40542604587527e-09</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="H11" t="n">
+        <v>1.419455308071966e-09</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.322123885244186e-09</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.405426045875271e-09</v>
+      </c>
+      <c r="K11" t="n">
         <v>1.437846454203284e-09</v>
       </c>
-      <c r="L9" t="n">
-        <v>1.350010399610462e-09</v>
+      <c r="L11" t="n">
+        <v>1.350010399610463e-09</v>
       </c>
     </row>
   </sheetData>
